--- a/ITOG_LOTS_1410.xlsx
+++ b/ITOG_LOTS_1410.xlsx
@@ -909,7 +909,9 @@
       <c r="K6" s="8" t="n">
         <v>2177384</v>
       </c>
-      <c r="L6" s="10" t="n"/>
+      <c r="L6" s="10" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M6" s="11" t="n">
         <v>1478527</v>
       </c>
@@ -1069,7 +1071,9 @@
       <c r="K8" s="8" t="n">
         <v>714880</v>
       </c>
-      <c r="L8" s="10" t="n"/>
+      <c r="L8" s="10" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M8" s="11" t="n">
         <v>449028</v>
       </c>
@@ -1229,7 +1233,9 @@
       <c r="K10" s="8" t="n">
         <v>1630827</v>
       </c>
-      <c r="L10" s="10" t="n"/>
+      <c r="L10" s="10" t="n">
+        <v>0.17</v>
+      </c>
       <c r="M10" s="11" t="n">
         <v>323274</v>
       </c>
@@ -1470,7 +1476,9 @@
       <c r="K13" s="8" t="n">
         <v>609645</v>
       </c>
-      <c r="L13" s="10" t="n"/>
+      <c r="L13" s="10" t="n">
+        <v>0.14</v>
+      </c>
       <c r="M13" s="13" t="n">
         <v>247436</v>
       </c>
@@ -1630,7 +1638,9 @@
       <c r="K15" s="8" t="n">
         <v>266390</v>
       </c>
-      <c r="L15" s="10" t="n"/>
+      <c r="L15" s="10" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M15" s="13" t="n">
         <v>189886</v>
       </c>
@@ -2025,7 +2035,9 @@
       <c r="I20" s="8" t="n"/>
       <c r="J20" s="10" t="n"/>
       <c r="K20" s="8" t="n"/>
-      <c r="L20" s="10" t="n"/>
+      <c r="L20" s="10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
       <c r="M20" s="13" t="n">
         <v>116467</v>
       </c>
@@ -2175,7 +2187,9 @@
       <c r="I22" s="8" t="n"/>
       <c r="J22" s="10" t="n"/>
       <c r="K22" s="8" t="n"/>
-      <c r="L22" s="10" t="n"/>
+      <c r="L22" s="10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
       <c r="M22" s="13" t="n">
         <v>99875</v>
       </c>
@@ -2414,7 +2428,9 @@
       <c r="K25" s="8" t="n">
         <v>153372359</v>
       </c>
-      <c r="L25" s="10" t="n"/>
+      <c r="L25" s="10" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M25" s="11" t="n">
         <v>39758366</v>
       </c>
@@ -2493,7 +2509,9 @@
       <c r="K26" s="8" t="n">
         <v>66162726</v>
       </c>
-      <c r="L26" s="10" t="n"/>
+      <c r="L26" s="10" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M26" s="11" t="n">
         <v>32511680</v>
       </c>
@@ -2528,14 +2546,14 @@
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="17" t="inlineStr"/>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>ИТОГО — обычные условия</t>
-        </is>
-      </c>
+      <c r="B27" s="17" t="inlineStr"/>
       <c r="C27" s="17" t="inlineStr"/>
       <c r="D27" s="17" t="inlineStr"/>
-      <c r="E27" s="17" t="inlineStr"/>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>ИТОГО — обычные условия</t>
+        </is>
+      </c>
       <c r="F27" s="17" t="inlineStr"/>
       <c r="G27" s="17" t="inlineStr"/>
       <c r="H27" s="18" t="n">
@@ -2563,14 +2581,14 @@
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="17" t="inlineStr"/>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>ИТОГО — с крупными (жёсткие условия)</t>
-        </is>
-      </c>
+      <c r="B28" s="17" t="inlineStr"/>
       <c r="C28" s="17" t="inlineStr"/>
       <c r="D28" s="17" t="inlineStr"/>
-      <c r="E28" s="17" t="inlineStr"/>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>ИТОГО — с крупными (жёсткие условия)</t>
+        </is>
+      </c>
       <c r="F28" s="17" t="inlineStr"/>
       <c r="G28" s="17" t="inlineStr"/>
       <c r="H28" s="18" t="n">

--- a/ITOG_LOTS_1410.xlsx
+++ b/ITOG_LOTS_1410.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Итог" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Итог'!$A$3:$S$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Итог'!$A$3:$S$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -49,7 +49,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -69,11 +69,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -103,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -138,16 +133,10 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -530,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S28"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -557,7 +546,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Итоговая таблица лотов (подача с 16.10.2026) — себестоимость, маржинальность, прибыль</t>
+          <t>Итоговая таблица лотов БЕЗ АУКЦИОНОВ (подача с 16.10.2026): запросы котировок, предложений, иные способы, коммерческие</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -808,7 +797,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>44-ФЗ аукцион</t>
+          <t>44-ФЗ запрос котировок</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -950,12 +939,12 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Соль</t>
+          <t>Спецодежда</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>32616447519</t>
+          <t>32616453117</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -965,39 +954,39 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>АО «Волоколамское ПТП РЖКХ», МО</t>
+          <t>ГУП «Салаватводоканал»</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>223-ФЗ запрос предложений</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>16.10 10:00</t>
+          <t>21.10 09:00</t>
         </is>
       </c>
       <c r="H7" s="8" t="n">
-        <v>1593800</v>
+        <v>1500000</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>648700</v>
+        <v>785120</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.5929853181076672</v>
+        <v>0.4765869115363072</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>945100</v>
+        <v>714880</v>
       </c>
       <c r="L7" s="10" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>572785</v>
+        <v>449028</v>
       </c>
       <c r="N7" s="10" t="n">
-        <v>0.5762137232837785</v>
+        <v>0.4550189616913052</v>
       </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
@@ -1011,17 +1000,17 @@
       </c>
       <c r="Q7" s="5" t="inlineStr">
         <is>
-          <t>средняя рыночная с доставкой (завод вагоном / склад авто)</t>
+          <t>средние цены фабрик РФ + доставка ТК</t>
         </is>
       </c>
       <c r="R7" s="5" t="inlineStr">
         <is>
-          <t>«Галит» — уточнить эквивалент | себест. — средняя рыночная с доставкой (не 4 500)</t>
+          <t>Договор по ед. расценкам</t>
         </is>
       </c>
       <c r="S7" s="5" t="inlineStr">
         <is>
-          <t>высокая</t>
+          <t>средняя</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1020,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Спецодежда</t>
+          <t>ПГР</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>32616453117</t>
+          <t>32616449090</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -1046,43 +1035,43 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>ГУП «Салаватводоканал»</t>
+          <t>ГАУК «Мосгортур», Москва</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>223-ФЗ запрос предложений</t>
+          <t>223-ФЗ запрос котировок</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>21.10 09:00</t>
+          <t>19.10 10:00</t>
         </is>
       </c>
       <c r="H8" s="8" t="n">
-        <v>1500000</v>
+        <v>1285964</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>785120</v>
+        <v>553080</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.4765869115363072</v>
+        <v>0.57</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>714880</v>
+        <v>732884</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>449028</v>
+        <v>436102</v>
       </c>
       <c r="N8" s="10" t="n">
-        <v>0.4550189616913052</v>
+        <v>0.55</v>
       </c>
       <c r="O8" s="5" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>— / 3%</t>
         </is>
       </c>
       <c r="P8" s="5" t="inlineStr">
@@ -1092,12 +1081,12 @@
       </c>
       <c r="Q8" s="5" t="inlineStr">
         <is>
-          <t>средние цены фабрик РФ + доставка ТК</t>
+          <t>прайс поставщика ПГР</t>
         </is>
       </c>
       <c r="R8" s="5" t="inlineStr">
         <is>
-          <t>Договор по ед. расценкам</t>
+          <t>Нужен российский реагент с записью ГИСП</t>
         </is>
       </c>
       <c r="S8" s="5" t="inlineStr">
@@ -1112,12 +1101,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>ПГР</t>
+          <t>Соль ⚠ &lt;9 000 ₽/т</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>32616449090</t>
+          <t>0128600006826000407</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -1127,43 +1116,43 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>ГАУК «Мосгортур», Москва</t>
+          <t>МКУ УЖКХ, Струнино</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>223-ФЗ запрос котировок</t>
+          <t>44-ФЗ запрос котировок</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>19.10 10:00</t>
+          <t>19.10</t>
         </is>
       </c>
       <c r="H9" s="8" t="n">
-        <v>1285964</v>
+        <v>1342500</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>553080</v>
+        <v>759000</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.57</v>
+        <v>0.4346368715083799</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>732884</v>
+        <v>583500</v>
       </c>
       <c r="L9" s="10" t="n">
         <v>0.15</v>
       </c>
-      <c r="M9" s="11" t="n">
-        <v>436102</v>
+      <c r="M9" s="12" t="n">
+        <v>295836</v>
       </c>
       <c r="N9" s="10" t="n">
-        <v>0.55</v>
+        <v>0.4113403130762793</v>
       </c>
       <c r="O9" s="5" t="inlineStr">
         <is>
-          <t>— / 3%</t>
+          <t>1% / 5%</t>
         </is>
       </c>
       <c r="P9" s="5" t="inlineStr">
@@ -1173,17 +1162,17 @@
       </c>
       <c r="Q9" s="5" t="inlineStr">
         <is>
-          <t>прайс поставщика ПГР</t>
+          <t>средняя рыночная с доставкой (завод вагоном / склад авто)</t>
         </is>
       </c>
       <c r="R9" s="5" t="inlineStr">
         <is>
-          <t>Нужен российский реагент с записью ГИСП</t>
+          <t>Галит тип С, 8 950 ₽/т | себест. — средняя рыночная с доставкой (не 4 500)</t>
         </is>
       </c>
       <c r="S9" s="5" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>высокая</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1182,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Форма спасателей</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>0358200022926000030</t>
+          <t>32616442935</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -1208,43 +1197,43 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>ГКУ РО «Ростовская ПСС»</t>
+          <t>ПАО «Т Плюс», Н.Новгород</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>44-ФЗ аукцион</t>
+          <t>223-ФЗ иной способ (не аукцион)</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>19.10 09:00</t>
+          <t>16.10 14:00</t>
         </is>
       </c>
       <c r="H10" s="8" t="n">
-        <v>6224421</v>
+        <v>1883587</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>4593594</v>
-      </c>
-      <c r="J10" s="12" t="n">
-        <v>0.2620045749799657</v>
+        <v>1273942</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>0.32</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>1630827</v>
+        <v>609645</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="M10" s="11" t="n">
-        <v>323274</v>
+        <v>0.14</v>
+      </c>
+      <c r="M10" s="12" t="n">
+        <v>247436</v>
       </c>
       <c r="N10" s="10" t="n">
-        <v>0.2315944674310844</v>
+        <v>0.3</v>
       </c>
       <c r="O10" s="5" t="inlineStr">
         <is>
-          <t>1% / 10%</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="P10" s="5" t="inlineStr">
@@ -1254,17 +1243,17 @@
       </c>
       <c r="Q10" s="5" t="inlineStr">
         <is>
-          <t>средние цены фабрик РФ + доставка ТК</t>
+          <t>оценка, цен по позициям нет</t>
         </is>
       </c>
       <c r="R10" s="5" t="inlineStr">
         <is>
-          <t>Пересчёт по фабричным ценам (комбинезоны 3 766 / ~7 100 ₽); пошив с символикой</t>
+          <t>Цен по позициям нет — оценка</t>
         </is>
       </c>
       <c r="S10" s="5" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>низкая</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1263,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Соль</t>
+          <t>Трубы ППУ</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>0318300065126000256</t>
+          <t>32616450774</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -1289,43 +1278,43 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>МКУ «Благоустройство», Абинск</t>
+          <t>МУП «Уфимские инженерные сети»</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>44-ФЗ аукцион</t>
+          <t>223-ФЗ иной способ (не аукцион)</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>19.10 09:00</t>
+          <t>20.10 12:00</t>
         </is>
       </c>
       <c r="H11" s="8" t="n">
-        <v>1368000</v>
+        <v>639849</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>763500</v>
+        <v>373459</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.4418859649122807</v>
+        <v>0.42</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>604500</v>
+        <v>266390</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="M11" s="11" t="n">
-        <v>310162</v>
+        <v>0.1</v>
+      </c>
+      <c r="M11" s="12" t="n">
+        <v>189886</v>
       </c>
       <c r="N11" s="10" t="n">
-        <v>0.4188881152561031</v>
+        <v>0.4</v>
       </c>
       <c r="O11" s="5" t="inlineStr">
         <is>
-          <t>1% / 5%</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="P11" s="5" t="inlineStr">
@@ -1335,17 +1324,17 @@
       </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
-          <t>средняя рыночная с доставкой (завод вагоном / склад авто)</t>
+          <t>оценка по аналогам</t>
         </is>
       </c>
       <c r="R11" s="5" t="inlineStr">
         <is>
-          <t>NaCl 96,5–97,7% | себест. — средняя рыночная с доставкой (не 4 500)</t>
+          <t>Отводы ППУ, тяжёлый груз; оценка</t>
         </is>
       </c>
       <c r="S11" s="5" t="inlineStr">
         <is>
-          <t>высокая</t>
+          <t>низкая</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1344,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Соль ⚠ &lt;9 000 ₽/т</t>
+          <t>Спецодежда (коммерч.)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>0128600006826000407</t>
+          <t>4634447</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -1370,43 +1359,33 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>МКУ УЖКХ, Струнино</t>
+          <t>ООО «Биннофарм Групп» — пул поставщиков</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>Коммерческий запрос предложений</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>19.10</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>1342500</v>
-      </c>
-      <c r="I12" s="8" t="n">
-        <v>759000</v>
-      </c>
-      <c r="J12" s="9" t="n">
-        <v>0.4346368715083799</v>
-      </c>
-      <c r="K12" s="8" t="n">
-        <v>583500</v>
-      </c>
+          <t>26.10 12:00</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="10" t="n"/>
+      <c r="K12" s="8" t="n"/>
       <c r="L12" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="M12" s="13" t="n">
-        <v>295836</v>
-      </c>
-      <c r="N12" s="10" t="n">
-        <v>0.4113403130762793</v>
-      </c>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>116467</v>
+      </c>
+      <c r="N12" s="10" t="n"/>
       <c r="O12" s="5" t="inlineStr">
         <is>
-          <t>1% / 5%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P12" s="5" t="inlineStr">
@@ -1416,17 +1395,17 @@
       </c>
       <c r="Q12" s="5" t="inlineStr">
         <is>
-          <t>средняя рыночная с доставкой (завод вагоном / склад авто)</t>
+          <t>средние цены фабрик РФ + доставка ТК</t>
         </is>
       </c>
       <c r="R12" s="5" t="inlineStr">
         <is>
-          <t>Галит тип С, 8 950 ₽/т | себест. — средняя рыночная с доставкой (не 4 500)</t>
+          <t>Без НМЦК: оценка по типовой корзине</t>
         </is>
       </c>
       <c r="S12" s="5" t="inlineStr">
         <is>
-          <t>высокая</t>
+          <t>низкая</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1415,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Спецодежда (коммерч.)</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>32616442935</t>
+          <t>372-446</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -1451,43 +1430,33 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>ПАО «Т Плюс», Н.Новгород</t>
+          <t>ООО «Благо-Армавир»</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>Коммерческий тендер</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>16.10 14:00</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>1883587</v>
-      </c>
-      <c r="I13" s="8" t="n">
-        <v>1273942</v>
-      </c>
-      <c r="J13" s="12" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="K13" s="8" t="n">
-        <v>609645</v>
-      </c>
+          <t>19.10 17:00</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="10" t="n"/>
+      <c r="K13" s="8" t="n"/>
       <c r="L13" s="10" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="M13" s="13" t="n">
-        <v>247436</v>
-      </c>
-      <c r="N13" s="10" t="n">
-        <v>0.3</v>
-      </c>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="M13" s="12" t="n">
+        <v>99875</v>
+      </c>
+      <c r="N13" s="10" t="n"/>
       <c r="O13" s="5" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P13" s="5" t="inlineStr">
@@ -1497,12 +1466,12 @@
       </c>
       <c r="Q13" s="5" t="inlineStr">
         <is>
-          <t>оценка, цен по позициям нет</t>
+          <t>средние цены фабрик РФ + доставка ТК</t>
         </is>
       </c>
       <c r="R13" s="5" t="inlineStr">
         <is>
-          <t>Цен по позициям нет — оценка</t>
+          <t>Без НМЦК: оценка</t>
         </is>
       </c>
       <c r="S13" s="5" t="inlineStr">
@@ -1517,12 +1486,12 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Пробирки</t>
+          <t>Спецодежда</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>0318300254126000157</t>
+          <t>32616452870</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -1532,43 +1501,43 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>ГБУЗ, Краснодарский край</t>
+          <t>ГУП «Салаватводоканал» (2-й лот)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>44-ФЗ</t>
+          <t>223-ФЗ запрос котировок</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>19.10 08:00</t>
+          <t>21.10 09:00</t>
         </is>
       </c>
       <c r="H14" s="8" t="n">
-        <v>586260</v>
+        <v>700000</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>184320</v>
-      </c>
-      <c r="J14" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>561222</v>
+      </c>
+      <c r="J14" s="13" t="n">
+        <v>0.17</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>401940</v>
+        <v>138778</v>
       </c>
       <c r="L14" s="10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M14" s="13" t="n">
-        <v>208928</v>
+        <v>0.1</v>
+      </c>
+      <c r="M14" s="12" t="n">
+        <v>35517</v>
       </c>
       <c r="N14" s="10" t="n">
-        <v>0.67</v>
+        <v>0.15</v>
       </c>
       <c r="O14" s="5" t="inlineStr">
         <is>
-          <t>— / 5%</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="P14" s="5" t="inlineStr">
@@ -1578,12 +1547,12 @@
       </c>
       <c r="Q14" s="5" t="inlineStr">
         <is>
-          <t>UNIVAC/МиниМед ~9–9,6 ₽/шт</t>
+          <t>средние цены фабрик РФ + доставка ТК</t>
         </is>
       </c>
       <c r="R14" s="5" t="inlineStr">
         <is>
-          <t>Только РФ + РУ; UNIVAC/МиниМед ~9 ₽</t>
+          <t>Костюм от дуги, термобельё, обувь; договор по ед. расценкам</t>
         </is>
       </c>
       <c r="S14" s="5" t="inlineStr">
@@ -1596,14 +1565,14 @@
       <c r="A15" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Трубы ППУ</t>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Спецодежда</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>32616450774</t>
+          <t>32616425363</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -1613,1009 +1582,138 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>МУП «Уфимские инженерные сети»</t>
+          <t>АО «Мособлэнерго»</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>223-ФЗ</t>
+          <t>223-ФЗ иной способ (не аукцион)</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>20.10 12:00</t>
+          <t>16.10 11:00</t>
         </is>
       </c>
       <c r="H15" s="8" t="n">
-        <v>639849</v>
+        <v>200000000</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>373459</v>
-      </c>
-      <c r="J15" s="9" t="n">
-        <v>0.42</v>
+        <v>133837274</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>0.32</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>266390</v>
+        <v>66162726</v>
       </c>
       <c r="L15" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="M15" s="13" t="n">
-        <v>189886</v>
+      <c r="M15" s="11" t="n">
+        <v>32511680</v>
       </c>
       <c r="N15" s="10" t="n">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
       <c r="O15" s="5" t="inlineStr">
         <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="P15" s="5" t="inlineStr">
-        <is>
-          <t>обычные</t>
+          <t>см. документацию</t>
+        </is>
+      </c>
+      <c r="P15" s="14" t="inlineStr">
+        <is>
+          <t>жёсткие</t>
         </is>
       </c>
       <c r="Q15" s="5" t="inlineStr">
         <is>
-          <t>оценка по аналогам</t>
+          <t>средние цены фабрик РФ + доставка ТК</t>
         </is>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>Отводы ППУ, тяжёлый груз; оценка</t>
+          <t>Рамочный; логотип; капитал и гарантии</t>
         </is>
       </c>
       <c r="S15" s="5" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Пробирки</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>0318300100526000190</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>ГБУЗ «Тихорецкая ЦРБ»</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>44-ФЗ</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>19.10 09:00</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>598970</v>
-      </c>
-      <c r="I16" s="8" t="n">
-        <v>254624</v>
-      </c>
-      <c r="J16" s="9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="K16" s="8" t="n">
-        <v>344346</v>
-      </c>
-      <c r="L16" s="10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M16" s="13" t="n">
-        <v>155243</v>
-      </c>
-      <c r="N16" s="10" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="O16" s="5" t="inlineStr">
-        <is>
-          <t>— / 5%</t>
-        </is>
-      </c>
-      <c r="P16" s="5" t="inlineStr">
-        <is>
-          <t>обычные</t>
-        </is>
-      </c>
-      <c r="Q16" s="5" t="inlineStr">
-        <is>
-          <t>UNIVAC/МиниМед ~9–9,6 ₽/шт</t>
-        </is>
-      </c>
-      <c r="R16" s="5" t="inlineStr">
-        <is>
-          <t>Только РФ + РУ</t>
-        </is>
-      </c>
-      <c r="S16" s="5" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
+      <c r="A16" s="15" t="inlineStr"/>
+      <c r="B16" s="15" t="inlineStr"/>
+      <c r="C16" s="15" t="inlineStr"/>
+      <c r="D16" s="15" t="inlineStr"/>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>ИТОГО — обычные условия</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr"/>
+      <c r="G16" s="15" t="inlineStr"/>
+      <c r="H16" s="16" t="n">
+        <v>22113376</v>
+      </c>
+      <c r="I16" s="16" t="n">
+        <v>9437915</v>
+      </c>
+      <c r="J16" s="17" t="n">
+        <v>0.5732033408196017</v>
+      </c>
+      <c r="K16" s="16" t="n">
+        <v>12675461</v>
+      </c>
+      <c r="L16" s="18" t="n"/>
+      <c r="M16" s="16" t="n">
+        <v>8097652</v>
+      </c>
+      <c r="N16" s="18" t="n"/>
+      <c r="O16" s="18" t="n"/>
+      <c r="P16" s="18" t="n"/>
+      <c r="Q16" s="18" t="n"/>
+      <c r="R16" s="18" t="n"/>
+      <c r="S16" s="18" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Пробирки</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>0318300100526000182</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>ГБУЗ «Тихорецкая ЦРБ»</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>44-ФЗ</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>16.10 10:00</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>599240</v>
-      </c>
-      <c r="I17" s="8" t="n">
-        <v>265328</v>
-      </c>
-      <c r="J17" s="9" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="K17" s="8" t="n">
-        <v>333912</v>
-      </c>
-      <c r="L17" s="10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M17" s="13" t="n">
-        <v>146016</v>
-      </c>
-      <c r="N17" s="10" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="O17" s="5" t="inlineStr">
-        <is>
-          <t>— / 5%</t>
-        </is>
-      </c>
-      <c r="P17" s="5" t="inlineStr">
-        <is>
-          <t>обычные</t>
-        </is>
-      </c>
-      <c r="Q17" s="5" t="inlineStr">
-        <is>
-          <t>UNIVAC/МиниМед ~9–9,6 ₽/шт</t>
-        </is>
-      </c>
-      <c r="R17" s="5" t="inlineStr">
-        <is>
-          <t>Только РФ + РУ</t>
-        </is>
-      </c>
-      <c r="S17" s="5" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Пробирки</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>0318300100526000186</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>ГБУЗ «Тихорецкая ЦРБ»</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>44-ФЗ</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>20.10 09:00</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>597406</v>
-      </c>
-      <c r="I18" s="8" t="n">
-        <v>268387</v>
-      </c>
-      <c r="J18" s="9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="K18" s="8" t="n">
-        <v>329019</v>
-      </c>
-      <c r="L18" s="10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M18" s="13" t="n">
-        <v>142170</v>
-      </c>
-      <c r="N18" s="10" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="O18" s="5" t="inlineStr">
-        <is>
-          <t>— / 5%</t>
-        </is>
-      </c>
-      <c r="P18" s="5" t="inlineStr">
-        <is>
-          <t>обычные</t>
-        </is>
-      </c>
-      <c r="Q18" s="5" t="inlineStr">
-        <is>
-          <t>UNIVAC/МиниМед ~9–9,6 ₽/шт</t>
-        </is>
-      </c>
-      <c r="R18" s="5" t="inlineStr">
-        <is>
-          <t>Только РФ + РУ</t>
-        </is>
-      </c>
-      <c r="S18" s="5" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Пробирки</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>0318300100526000191</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>ГБУЗ «Тихорецкая ЦРБ»</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>44-ФЗ</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>21.10 09:00</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>598899</v>
-      </c>
-      <c r="I19" s="8" t="n">
-        <v>273411</v>
-      </c>
-      <c r="J19" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="K19" s="8" t="n">
-        <v>325488</v>
-      </c>
-      <c r="L19" s="10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M19" s="13" t="n">
-        <v>138704</v>
-      </c>
-      <c r="N19" s="10" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="O19" s="5" t="inlineStr">
-        <is>
-          <t>— / 5%</t>
-        </is>
-      </c>
-      <c r="P19" s="5" t="inlineStr">
-        <is>
-          <t>обычные</t>
-        </is>
-      </c>
-      <c r="Q19" s="5" t="inlineStr">
-        <is>
-          <t>UNIVAC/МиниМед ~9–9,6 ₽/шт</t>
-        </is>
-      </c>
-      <c r="R19" s="5" t="inlineStr">
-        <is>
-          <t>Только РФ + РУ</t>
-        </is>
-      </c>
-      <c r="S19" s="5" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Спецодежда (коммерч.)</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>4634447</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>ООО «Биннофарм Групп» — пул поставщиков</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>Коммерческий запрос предложений</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>26.10 12:00</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n"/>
-      <c r="J20" s="10" t="n"/>
-      <c r="K20" s="8" t="n"/>
-      <c r="L20" s="10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="M20" s="13" t="n">
-        <v>116467</v>
-      </c>
-      <c r="N20" s="10" t="n"/>
-      <c r="O20" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P20" s="5" t="inlineStr">
-        <is>
-          <t>обычные</t>
-        </is>
-      </c>
-      <c r="Q20" s="5" t="inlineStr">
-        <is>
-          <t>средние цены фабрик РФ + доставка ТК</t>
-        </is>
-      </c>
-      <c r="R20" s="5" t="inlineStr">
-        <is>
-          <t>Без НМЦК: оценка по типовой корзине</t>
-        </is>
-      </c>
-      <c r="S20" s="5" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>ПГР</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>0372200258526000596</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>СПб ГБУЗ «Больница Св. Георгия»</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>44-ФЗ аукцион</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>20.10</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>404960</v>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>202400</v>
-      </c>
-      <c r="J21" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K21" s="8" t="n">
-        <v>202560</v>
-      </c>
-      <c r="L21" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="M21" s="13" t="n">
-        <v>112547</v>
-      </c>
-      <c r="N21" s="10" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="O21" s="5" t="inlineStr">
-        <is>
-          <t>— / 10%</t>
-        </is>
-      </c>
-      <c r="P21" s="5" t="inlineStr">
-        <is>
-          <t>обычные</t>
-        </is>
-      </c>
-      <c r="Q21" s="5" t="inlineStr">
-        <is>
-          <t>прайс поставщика ПГР</t>
-        </is>
-      </c>
-      <c r="R21" s="5" t="inlineStr">
-        <is>
-          <t>ПГРт с мраморной крошкой; ГИСП</t>
-        </is>
-      </c>
-      <c r="S21" s="5" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Спецодежда (коммерч.)</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>372-446</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>ООО «Благо-Армавир»</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>Коммерческий тендер</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>19.10 17:00</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n"/>
-      <c r="J22" s="10" t="n"/>
-      <c r="K22" s="8" t="n"/>
-      <c r="L22" s="10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="M22" s="13" t="n">
-        <v>99875</v>
-      </c>
-      <c r="N22" s="10" t="n"/>
-      <c r="O22" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P22" s="5" t="inlineStr">
-        <is>
-          <t>обычные</t>
-        </is>
-      </c>
-      <c r="Q22" s="5" t="inlineStr">
-        <is>
-          <t>средние цены фабрик РФ + доставка ТК</t>
-        </is>
-      </c>
-      <c r="R22" s="5" t="inlineStr">
-        <is>
-          <t>Без НМЦК: оценка</t>
-        </is>
-      </c>
-      <c r="S22" s="5" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Соль ⚠ &lt;9 000 ₽/т</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>0131300000626001316</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>МБУ «Комбинат благоустройства», Воронеж</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>44-ФЗ аукцион</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>16.10 09:00</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>3296150</v>
-      </c>
-      <c r="I23" s="8" t="n">
-        <v>2839760</v>
-      </c>
-      <c r="J23" s="14" t="n">
-        <v>0.1384615384615385</v>
-      </c>
-      <c r="K23" s="8" t="n">
-        <v>456390</v>
-      </c>
-      <c r="L23" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="M23" s="15" t="n">
-        <v>-153808</v>
-      </c>
-      <c r="N23" s="10" t="n">
-        <v>0.102960671674768</v>
-      </c>
-      <c r="O23" s="5" t="inlineStr">
-        <is>
-          <t>1% / 10%</t>
-        </is>
-      </c>
-      <c r="P23" s="5" t="inlineStr">
-        <is>
-          <t>обычные</t>
-        </is>
-      </c>
-      <c r="Q23" s="5" t="inlineStr">
-        <is>
-          <t>средняя рыночная с доставкой (завод вагоном / склад авто)</t>
-        </is>
-      </c>
-      <c r="R23" s="5" t="inlineStr">
-        <is>
-          <t>7 150 ₽/т | себест. — средняя рыночная с доставкой (не 4 500)</t>
-        </is>
-      </c>
-      <c r="S23" s="5" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>Соль</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>0142200001326018965</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>МБУ «Благоустройство», Самара</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>44-ФЗ аукцион</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>19.10 11:00</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>121000000</v>
-      </c>
-      <c r="I24" s="8" t="n">
-        <v>42350000</v>
-      </c>
-      <c r="J24" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="K24" s="8" t="n">
-        <v>78650000</v>
-      </c>
-      <c r="L24" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="M24" s="11" t="n">
-        <v>49542141</v>
-      </c>
-      <c r="N24" s="10" t="n">
-        <v>0.6355777728678744</v>
-      </c>
-      <c r="O24" s="5" t="inlineStr">
-        <is>
-          <t>0,5% / 0,5%</t>
-        </is>
-      </c>
-      <c r="P24" s="16" t="inlineStr">
-        <is>
-          <t>жёсткие</t>
-        </is>
-      </c>
-      <c r="Q24" s="5" t="inlineStr">
-        <is>
-          <t>средняя рыночная с доставкой (завод вагоном / склад авто)</t>
-        </is>
-      </c>
-      <c r="R24" s="5" t="inlineStr">
-        <is>
-          <t>Требуется опыт: исполненный контракт от 24,2 млн; 11 000 т | себест. — средняя рыночная с доставкой (не 4 500)</t>
-        </is>
-      </c>
-      <c r="S24" s="5" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>Спецодежда</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>32616425940</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>ГУП «Петербургский метрополитен»</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>223-ФЗ аукцион</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>16.10 10:00</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="n">
-        <v>650000000</v>
-      </c>
-      <c r="I25" s="8" t="n">
-        <v>496627641</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="K25" s="8" t="n">
-        <v>153372359</v>
-      </c>
-      <c r="L25" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M25" s="11" t="n">
-        <v>39758366</v>
-      </c>
-      <c r="N25" s="10" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="O25" s="5" t="inlineStr">
-        <is>
-          <t>см. документацию</t>
-        </is>
-      </c>
-      <c r="P25" s="16" t="inlineStr">
-        <is>
-          <t>жёсткие</t>
-        </is>
-      </c>
-      <c r="Q25" s="5" t="inlineStr">
-        <is>
-          <t>средние цены фабрик РФ + доставка ТК</t>
-        </is>
-      </c>
-      <c r="R25" s="5" t="inlineStr">
-        <is>
-          <t>Рамочный, 1 414 позиций; нужен капитал и гарантии</t>
-        </is>
-      </c>
-      <c r="S25" s="5" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>Спецодежда</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>32616425363</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>АО «Мособлэнерго»</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>223-ФЗ</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>16.10 11:00</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="n">
-        <v>200000000</v>
-      </c>
-      <c r="I26" s="8" t="n">
-        <v>133837274</v>
-      </c>
-      <c r="J26" s="12" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="K26" s="8" t="n">
-        <v>66162726</v>
-      </c>
-      <c r="L26" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M26" s="11" t="n">
-        <v>32511680</v>
-      </c>
-      <c r="N26" s="10" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="O26" s="5" t="inlineStr">
-        <is>
-          <t>см. документацию</t>
-        </is>
-      </c>
-      <c r="P26" s="16" t="inlineStr">
-        <is>
-          <t>жёсткие</t>
-        </is>
-      </c>
-      <c r="Q26" s="5" t="inlineStr">
-        <is>
-          <t>средние цены фабрик РФ + доставка ТК</t>
-        </is>
-      </c>
-      <c r="R26" s="5" t="inlineStr">
-        <is>
-          <t>Рамочный; логотип; капитал и гарантии</t>
-        </is>
-      </c>
-      <c r="S26" s="5" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="17" t="inlineStr"/>
-      <c r="B27" s="17" t="inlineStr"/>
-      <c r="C27" s="17" t="inlineStr"/>
-      <c r="D27" s="17" t="inlineStr"/>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>ИТОГО — обычные условия</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr"/>
-      <c r="G27" s="17" t="inlineStr"/>
-      <c r="H27" s="18" t="n">
-        <v>37281482</v>
-      </c>
-      <c r="I27" s="18" t="n">
-        <v>19170717</v>
-      </c>
-      <c r="J27" s="19" t="n">
-        <v>0.4857844706924472</v>
-      </c>
-      <c r="K27" s="18" t="n">
-        <v>18110765</v>
-      </c>
-      <c r="L27" s="20" t="n"/>
-      <c r="M27" s="18" t="n">
-        <v>10018156</v>
-      </c>
-      <c r="N27" s="20" t="n"/>
-      <c r="O27" s="20" t="n"/>
-      <c r="P27" s="20" t="n"/>
-      <c r="Q27" s="20" t="n"/>
-      <c r="R27" s="20" t="n"/>
-      <c r="S27" s="20" t="n"/>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="17" t="inlineStr"/>
-      <c r="B28" s="17" t="inlineStr"/>
-      <c r="C28" s="17" t="inlineStr"/>
-      <c r="D28" s="17" t="inlineStr"/>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr"/>
+      <c r="B17" s="15" t="inlineStr"/>
+      <c r="C17" s="15" t="inlineStr"/>
+      <c r="D17" s="15" t="inlineStr"/>
+      <c r="E17" s="15" t="inlineStr">
         <is>
           <t>ИТОГО — с крупными (жёсткие условия)</t>
         </is>
       </c>
-      <c r="F28" s="17" t="inlineStr"/>
-      <c r="G28" s="17" t="inlineStr"/>
-      <c r="H28" s="18" t="n">
-        <v>1008281482</v>
-      </c>
-      <c r="I28" s="18" t="n">
-        <v>691985632</v>
-      </c>
-      <c r="J28" s="19" t="n">
-        <v>0.3136979659416179</v>
-      </c>
-      <c r="K28" s="18" t="n">
-        <v>316295850</v>
-      </c>
-      <c r="L28" s="20" t="n"/>
-      <c r="M28" s="18" t="n">
-        <v>131830343</v>
-      </c>
-      <c r="N28" s="20" t="n"/>
-      <c r="O28" s="20" t="n"/>
-      <c r="P28" s="20" t="n"/>
-      <c r="Q28" s="20" t="n"/>
-      <c r="R28" s="20" t="n"/>
-      <c r="S28" s="20" t="n"/>
+      <c r="F17" s="15" t="inlineStr"/>
+      <c r="G17" s="15" t="inlineStr"/>
+      <c r="H17" s="16" t="n">
+        <v>222113376</v>
+      </c>
+      <c r="I17" s="16" t="n">
+        <v>143275189</v>
+      </c>
+      <c r="J17" s="17" t="n">
+        <v>0.3549456967418297</v>
+      </c>
+      <c r="K17" s="16" t="n">
+        <v>78838187</v>
+      </c>
+      <c r="L17" s="18" t="n"/>
+      <c r="M17" s="16" t="n">
+        <v>40609332</v>
+      </c>
+      <c r="N17" s="18" t="n"/>
+      <c r="O17" s="18" t="n"/>
+      <c r="P17" s="18" t="n"/>
+      <c r="Q17" s="18" t="n"/>
+      <c r="R17" s="18" t="n"/>
+      <c r="S17" s="18" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:S26"/>
+  <autoFilter ref="A3:S15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId2"/>
@@ -2629,17 +1727,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/ITOG_LOTS_1410.xlsx
+++ b/ITOG_LOTS_1410.xlsx
@@ -102,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -148,6 +148,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -532,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R105"/>
+  <dimension ref="A1:T105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -552,7 +555,9 @@
     <col width="15" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="55" customWidth="1" min="18" max="18"/>
+    <col width="45" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="40" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -578,6 +583,8 @@
       <c r="P1" s="2" t="n"/>
       <c r="Q1" s="2" t="n"/>
       <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -602,6 +609,8 @@
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="n"/>
       <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="n"/>
     </row>
     <row r="3" ht="51" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -692,6 +701,16 @@
       <c r="R3" s="3" t="inlineStr">
         <is>
           <t>Откуда себестоимость</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>Где цена (ссылка)</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>Ещё источники</t>
         </is>
       </c>
     </row>
@@ -766,6 +785,18 @@
           <t>средняя рыночная с доставкой: завод вагоном / склад авто (SALT_STRATEGY_1410)</t>
         </is>
       </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>esolk.ru</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>https://nsmgr.ru/reagenty/tekhnicheskaya-sol/big-begi
+https://sknerud.ru/reagent/sol-texnicheskaya/
+https://vektor-e.ru/sol/</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="4" t="n">
@@ -836,6 +867,18 @@
       <c r="R5" s="8" t="inlineStr">
         <is>
           <t>средняя рыночная с доставкой: завод вагоном / склад авто (SALT_STRATEGY_1410)</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>esolk.ru</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>https://nsmgr.ru/reagenty/tekhnicheskaya-sol/big-begi
+https://sknerud.ru/reagent/sol-texnicheskaya/
+https://vektor-e.ru/sol/</t>
         </is>
       </c>
     </row>
@@ -898,6 +941,8 @@
           <t>по позициям ниже</t>
         </is>
       </c>
+      <c r="S6" s="4" t="n"/>
+      <c r="T6" s="4" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="13" t="inlineStr"/>
@@ -942,6 +987,17 @@
           <t>справочник: Жилет сигнальный</t>
         </is>
       </c>
+      <c r="S7" s="16" t="inlineStr">
+        <is>
+          <t>fabrikant-textile.ru</t>
+        </is>
+      </c>
+      <c r="T7" s="13" t="inlineStr">
+        <is>
+          <t>https://www.trakt.ru/product/138206/
+https://www.spets.ru/products/spetsodezhda/odezhda_spetsialnaya/</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="13" t="inlineStr"/>
@@ -986,6 +1042,17 @@
           <t>справочник: Жилет утепленный</t>
         </is>
       </c>
+      <c r="S8" s="16" t="inlineStr">
+        <is>
+          <t>ivuniforma.ru</t>
+        </is>
+      </c>
+      <c r="T8" s="13" t="inlineStr">
+        <is>
+          <t>https://www.trakt.ru/product/12021/
+https://www.spets.ru/products/spetsodezhda/odezhda_dlya_okhrannykh_struktur/</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="13" t="inlineStr"/>
@@ -1030,6 +1097,16 @@
           <t>Фабрикант 975 / Ивсотекс 1 250</t>
         </is>
       </c>
+      <c r="S9" s="16" t="inlineStr">
+        <is>
+          <t>fabrikant-textile.ru</t>
+        </is>
+      </c>
+      <c r="T9" s="13" t="inlineStr">
+        <is>
+          <t>https://ivsoteks.ru/specodejda</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="13" t="inlineStr"/>
@@ -1074,6 +1151,17 @@
           <t>справочник: Костюм летний рабочий</t>
         </is>
       </c>
+      <c r="S10" s="16" t="inlineStr">
+        <is>
+          <t>ivuniforma.ru</t>
+        </is>
+      </c>
+      <c r="T10" s="13" t="inlineStr">
+        <is>
+          <t>https://ivsoteks.ru/specodejda
+https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="13" t="inlineStr"/>
@@ -1118,6 +1206,17 @@
           <t>справочник: Костюм летний рабочий</t>
         </is>
       </c>
+      <c r="S11" s="16" t="inlineStr">
+        <is>
+          <t>ivuniforma.ru</t>
+        </is>
+      </c>
+      <c r="T11" s="13" t="inlineStr">
+        <is>
+          <t>https://ivsoteks.ru/specodejda
+https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="13" t="inlineStr"/>
@@ -1162,6 +1261,17 @@
           <t>справочник: Куртка утепленная</t>
         </is>
       </c>
+      <c r="S12" s="16" t="inlineStr">
+        <is>
+          <t>fabrikant-textile.ru</t>
+        </is>
+      </c>
+      <c r="T12" s="13" t="inlineStr">
+        <is>
+          <t>https://www.specteks37.ru/katalog/zimnyaya-spetsodezhda/
+https://www.ivuniforma.ru/catalog/rabochaya-odezhda/zimnjaja/</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="13" t="inlineStr"/>
@@ -1206,6 +1316,17 @@
           <t>справочник: Полукомбинезон / брюки зимние</t>
         </is>
       </c>
+      <c r="S13" s="16" t="inlineStr">
+        <is>
+          <t>fabrikant-textile.ru</t>
+        </is>
+      </c>
+      <c r="T13" s="13" t="inlineStr">
+        <is>
+          <t>https://spec-standart.ru/zimnyaya-specodezhda
+https://www.trakt.ru/</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="13" t="inlineStr"/>
@@ -1250,6 +1371,12 @@
           <t>Спецобъединение «Рефлект-2» 6 112 −10%</t>
         </is>
       </c>
+      <c r="S14" s="16" t="inlineStr">
+        <is>
+          <t>spets.ru</t>
+        </is>
+      </c>
+      <c r="T14" s="13" t="inlineStr"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="13" t="inlineStr"/>
@@ -1276,7 +1403,7 @@
       <c r="J15" s="15" t="n">
         <v>10550</v>
       </c>
-      <c r="K15" s="16" t="n">
+      <c r="K15" s="17" t="n">
         <v>0.310159487203295</v>
       </c>
       <c r="L15" s="15" t="n">
@@ -1294,6 +1421,12 @@
           <t>Спецобъединение «Рефлект-2» зим. 11 621 −10%</t>
         </is>
       </c>
+      <c r="S15" s="16" t="inlineStr">
+        <is>
+          <t>spets.ru</t>
+        </is>
+      </c>
+      <c r="T15" s="13" t="inlineStr"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="13" t="inlineStr"/>
@@ -1338,6 +1471,16 @@
           <t>Тракт 11 253 / Спецобъединение 24 199, среднее −10%</t>
         </is>
       </c>
+      <c r="S16" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T16" s="13" t="inlineStr">
+        <is>
+          <t>https://www.spets.ru/products/spetsodezhda/odezhda_spetsialnaya/</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="13" t="inlineStr"/>
@@ -1382,6 +1525,16 @@
           <t>Тракт 11 253 / Спецобъединение 24 199, среднее −10%</t>
         </is>
       </c>
+      <c r="S17" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T17" s="13" t="inlineStr">
+        <is>
+          <t>https://www.spets.ru/products/spetsodezhda/odezhda_spetsialnaya/</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="13" t="inlineStr"/>
@@ -1426,6 +1579,16 @@
           <t>Тракт 6 731 / Спецобъединение 13 219, среднее −10%</t>
         </is>
       </c>
+      <c r="S18" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T18" s="13" t="inlineStr">
+        <is>
+          <t>https://www.spets.ru/products/spetsodezhda/odezhda_spetsialnaya/</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="13" t="inlineStr"/>
@@ -1470,6 +1633,16 @@
           <t>Тракт 6 731 / Спецобъединение 13 219, среднее −10%</t>
         </is>
       </c>
+      <c r="S19" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T19" s="13" t="inlineStr">
+        <is>
+          <t>https://www.spets.ru/products/spetsodezhda/odezhda_spetsialnaya/</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="13" t="inlineStr"/>
@@ -1514,6 +1687,16 @@
           <t>Тракт 971 / Фабрикант 1 365</t>
         </is>
       </c>
+      <c r="S20" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T20" s="13" t="inlineStr">
+        <is>
+          <t>https://fabrikant-textile.ru/catalog/spetsodezhda/</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="13" t="inlineStr"/>
@@ -1558,6 +1741,17 @@
           <t>справочник: Футболка</t>
         </is>
       </c>
+      <c r="S21" s="16" t="inlineStr">
+        <is>
+          <t>productcenter.ru</t>
+        </is>
+      </c>
+      <c r="T21" s="13" t="inlineStr">
+        <is>
+          <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf
+https://www.trakt.ru/product/12012/</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="13" t="inlineStr"/>
@@ -1602,6 +1796,17 @@
           <t>справочник: Халат рабочий</t>
         </is>
       </c>
+      <c r="S22" s="16" t="inlineStr">
+        <is>
+          <t>fabrikant-textile.ru</t>
+        </is>
+      </c>
+      <c r="T22" s="13" t="inlineStr">
+        <is>
+          <t>https://www.ivuniforma.ru/catalog/rabochaya-odezhda/letnyaya-spetsodezhda/khalati/
+https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="13" t="inlineStr"/>
@@ -1646,6 +1851,17 @@
           <t>справочник: Халат рабочий</t>
         </is>
       </c>
+      <c r="S23" s="16" t="inlineStr">
+        <is>
+          <t>fabrikant-textile.ru</t>
+        </is>
+      </c>
+      <c r="T23" s="13" t="inlineStr">
+        <is>
+          <t>https://www.ivuniforma.ru/catalog/rabochaya-odezhda/letnyaya-spetsodezhda/khalati/
+https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="13" t="inlineStr"/>
@@ -1688,6 +1904,17 @@
       <c r="R24" s="13" t="inlineStr">
         <is>
           <t>справочник: Халат рабочий</t>
+        </is>
+      </c>
+      <c r="S24" s="16" t="inlineStr">
+        <is>
+          <t>fabrikant-textile.ru</t>
+        </is>
+      </c>
+      <c r="T24" s="13" t="inlineStr">
+        <is>
+          <t>https://www.ivuniforma.ru/catalog/rabochaya-odezhda/letnyaya-spetsodezhda/khalati/
+https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf</t>
         </is>
       </c>
     </row>
@@ -1750,6 +1977,8 @@
           <t>по позициям ниже</t>
         </is>
       </c>
+      <c r="S25" s="4" t="n"/>
+      <c r="T25" s="4" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="13" t="inlineStr"/>
@@ -1788,6 +2017,17 @@
           <t>справочник: Костюм зимний рабочий (I–III пояс)</t>
         </is>
       </c>
+      <c r="S26" s="16" t="inlineStr">
+        <is>
+          <t>fabrikant-textile.ru</t>
+        </is>
+      </c>
+      <c r="T26" s="13" t="inlineStr">
+        <is>
+          <t>https://spec-standart.ru/zimnyaya-specodezhda
+https://www.specteks37.ru/katalog/zimnyaya-spetsodezhda/</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="13" t="inlineStr"/>
@@ -1826,6 +2066,17 @@
           <t>справочник: Куртка утепленная</t>
         </is>
       </c>
+      <c r="S27" s="16" t="inlineStr">
+        <is>
+          <t>fabrikant-textile.ru</t>
+        </is>
+      </c>
+      <c r="T27" s="13" t="inlineStr">
+        <is>
+          <t>https://www.specteks37.ru/katalog/zimnyaya-spetsodezhda/
+https://www.ivuniforma.ru/catalog/rabochaya-odezhda/zimnjaja/</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="13" t="inlineStr"/>
@@ -1864,6 +2115,17 @@
           <t>справочник: Полукомбинезон / брюки зимние</t>
         </is>
       </c>
+      <c r="S28" s="16" t="inlineStr">
+        <is>
+          <t>fabrikant-textile.ru</t>
+        </is>
+      </c>
+      <c r="T28" s="13" t="inlineStr">
+        <is>
+          <t>https://spec-standart.ru/zimnyaya-specodezhda
+https://www.trakt.ru/</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="13" t="inlineStr"/>
@@ -1902,6 +2164,17 @@
           <t>справочник: Куртка утепленная</t>
         </is>
       </c>
+      <c r="S29" s="16" t="inlineStr">
+        <is>
+          <t>fabrikant-textile.ru</t>
+        </is>
+      </c>
+      <c r="T29" s="13" t="inlineStr">
+        <is>
+          <t>https://www.specteks37.ru/katalog/zimnyaya-spetsodezhda/
+https://www.ivuniforma.ru/catalog/rabochaya-odezhda/zimnjaja/</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="13" t="inlineStr"/>
@@ -1940,6 +2213,17 @@
           <t>справочник: Полукомбинезон / брюки зимние</t>
         </is>
       </c>
+      <c r="S30" s="16" t="inlineStr">
+        <is>
+          <t>fabrikant-textile.ru</t>
+        </is>
+      </c>
+      <c r="T30" s="13" t="inlineStr">
+        <is>
+          <t>https://spec-standart.ru/zimnyaya-specodezhda
+https://www.trakt.ru/</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="13" t="inlineStr"/>
@@ -1978,6 +2262,17 @@
           <t>справочник: Куртка утепленная</t>
         </is>
       </c>
+      <c r="S31" s="16" t="inlineStr">
+        <is>
+          <t>fabrikant-textile.ru</t>
+        </is>
+      </c>
+      <c r="T31" s="13" t="inlineStr">
+        <is>
+          <t>https://www.specteks37.ru/katalog/zimnyaya-spetsodezhda/
+https://www.ivuniforma.ru/catalog/rabochaya-odezhda/zimnjaja/</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="13" t="inlineStr"/>
@@ -2002,7 +2297,7 @@
       <c r="J32" s="15" t="n">
         <v>1828.1375</v>
       </c>
-      <c r="K32" s="16" t="n">
+      <c r="K32" s="17" t="n">
         <v>0.3946564569536424</v>
       </c>
       <c r="L32" s="15" t="n"/>
@@ -2016,6 +2311,17 @@
           <t>справочник: Полукомбинезон / брюки зимние</t>
         </is>
       </c>
+      <c r="S32" s="16" t="inlineStr">
+        <is>
+          <t>fabrikant-textile.ru</t>
+        </is>
+      </c>
+      <c r="T32" s="13" t="inlineStr">
+        <is>
+          <t>https://spec-standart.ru/zimnyaya-specodezhda
+https://www.trakt.ru/</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="13" t="inlineStr"/>
@@ -2054,6 +2360,12 @@
           <t>Тракт, костюм КЩС утепл. 6 215</t>
         </is>
       </c>
+      <c r="S33" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T33" s="13" t="inlineStr"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="13" t="inlineStr"/>
@@ -2092,6 +2404,17 @@
           <t>справочник: Костюм сварщика</t>
         </is>
       </c>
+      <c r="S34" s="16" t="inlineStr">
+        <is>
+          <t>ivuniforma.ru</t>
+        </is>
+      </c>
+      <c r="T34" s="13" t="inlineStr">
+        <is>
+          <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf
+https://www.trakt.ru/</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="13" t="inlineStr"/>
@@ -2116,7 +2439,7 @@
       <c r="J35" s="15" t="n">
         <v>10550</v>
       </c>
-      <c r="K35" s="17" t="n">
+      <c r="K35" s="18" t="n">
         <v>-0.06490360351266782</v>
       </c>
       <c r="L35" s="15" t="n"/>
@@ -2130,6 +2453,12 @@
           <t>Спецобъединение «Рефлект-2» зим. 11 621 −10%</t>
         </is>
       </c>
+      <c r="S35" s="16" t="inlineStr">
+        <is>
+          <t>spets.ru</t>
+        </is>
+      </c>
+      <c r="T35" s="13" t="inlineStr"/>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="13" t="inlineStr"/>
@@ -2168,6 +2497,17 @@
           <t>справочник: Жилет утепленный</t>
         </is>
       </c>
+      <c r="S36" s="16" t="inlineStr">
+        <is>
+          <t>ivuniforma.ru</t>
+        </is>
+      </c>
+      <c r="T36" s="13" t="inlineStr">
+        <is>
+          <t>https://www.trakt.ru/product/12021/
+https://www.spets.ru/products/spetsodezhda/odezhda_dlya_okhrannykh_struktur/</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="4" t="n">
@@ -2240,6 +2580,12 @@
           <t>прайс «А-Стандарт» −25 °C 22 800 ₽/т + доставка</t>
         </is>
       </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>bicotender.ru</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="4" t="n">
@@ -2312,6 +2658,18 @@
           <t>средняя рыночная с доставкой: завод вагоном / склад авто (SALT_STRATEGY_1410)</t>
         </is>
       </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>esolk.ru</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>https://nsmgr.ru/reagenty/tekhnicheskaya-sol/big-begi
+https://sknerud.ru/reagent/sol-texnicheskaya/
+https://vektor-e.ru/sol/</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="4" t="n">
@@ -2365,7 +2723,7 @@
       <c r="M39" s="9" t="n">
         <v>1273942</v>
       </c>
-      <c r="N39" s="16" t="n">
+      <c r="N39" s="17" t="n">
         <v>0.32</v>
       </c>
       <c r="O39" s="12" t="n">
@@ -2382,6 +2740,16 @@
       <c r="R39" s="8" t="inlineStr">
         <is>
           <t>оценка по дилерским прайсам (цен по позициям нет)</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>specarmatura.ru</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>https://dn.ru/sharovyi-kran/teplosnabzhenie/flantcevyi-kran/standartnyi/ld/st20/dn100</t>
         </is>
       </c>
     </row>
@@ -2456,6 +2824,12 @@
           <t>оценка по аналогам</t>
         </is>
       </c>
+      <c r="S40" s="8" t="inlineStr">
+        <is>
+          <t>нет открытой цены — оценка</t>
+        </is>
+      </c>
+      <c r="T40" s="4" t="n"/>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="4" t="n">
@@ -2508,6 +2882,8 @@
           <t>по позициям ниже</t>
         </is>
       </c>
+      <c r="S41" s="4" t="n"/>
+      <c r="T41" s="4" t="n"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="13" t="inlineStr"/>
@@ -2532,7 +2908,7 @@
       <c r="J42" s="15" t="n">
         <v>1144.5</v>
       </c>
-      <c r="K42" s="18" t="n"/>
+      <c r="K42" s="19" t="n"/>
       <c r="L42" s="15" t="n"/>
       <c r="M42" s="15" t="n">
         <v>343350</v>
@@ -2546,6 +2922,12 @@
           <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf (арт. 3.290 1 091.64 ₽)</t>
         </is>
       </c>
+      <c r="S42" s="16" t="inlineStr">
+        <is>
+          <t>files.technoavia.ru</t>
+        </is>
+      </c>
+      <c r="T42" s="13" t="inlineStr"/>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="13" t="inlineStr"/>
@@ -2570,7 +2952,7 @@
       <c r="J43" s="15" t="n">
         <v>4052.5</v>
       </c>
-      <c r="K43" s="18" t="n"/>
+      <c r="K43" s="19" t="n"/>
       <c r="L43" s="15" t="n"/>
       <c r="M43" s="15" t="n">
         <v>810500</v>
@@ -2582,6 +2964,16 @@
       <c r="R43" s="13" t="inlineStr">
         <is>
           <t>[оценка]: правило клиента 3 500 + антистатическая ткань ~15%</t>
+        </is>
+      </c>
+      <c r="S43" s="16" t="inlineStr">
+        <is>
+          <t>fabrikant-textile.ru</t>
+        </is>
+      </c>
+      <c r="T43" s="13" t="inlineStr">
+        <is>
+          <t>https://spec-standart.ru/zimnyaya-specodezhda</t>
         </is>
       </c>
     </row>
@@ -2608,7 +3000,7 @@
       <c r="J44" s="15" t="n">
         <v>530.5</v>
       </c>
-      <c r="K44" s="18" t="n"/>
+      <c r="K44" s="19" t="n"/>
       <c r="L44" s="15" t="n"/>
       <c r="M44" s="15" t="n">
         <v>106100</v>
@@ -2622,6 +3014,12 @@
           <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf (арт. 4.025 477.84 ₽)</t>
         </is>
       </c>
+      <c r="S44" s="16" t="inlineStr">
+        <is>
+          <t>files.technoavia.ru</t>
+        </is>
+      </c>
+      <c r="T44" s="13" t="inlineStr"/>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="13" t="inlineStr"/>
@@ -2646,7 +3044,7 @@
       <c r="J45" s="15" t="n">
         <v>3070.5</v>
       </c>
-      <c r="K45" s="18" t="n"/>
+      <c r="K45" s="19" t="n"/>
       <c r="L45" s="15" t="n"/>
       <c r="M45" s="15" t="n">
         <v>153525</v>
@@ -2660,6 +3058,12 @@
           <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf (арт. 5.856 «Билд» с мет. носками 3 018.36 ₽)</t>
         </is>
       </c>
+      <c r="S45" s="16" t="inlineStr">
+        <is>
+          <t>files.technoavia.ru</t>
+        </is>
+      </c>
+      <c r="T45" s="13" t="inlineStr"/>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="4" t="n">
@@ -2712,6 +3116,8 @@
           <t>по позициям ниже</t>
         </is>
       </c>
+      <c r="S46" s="4" t="n"/>
+      <c r="T46" s="4" t="n"/>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="13" t="inlineStr"/>
@@ -2736,7 +3142,7 @@
       <c r="J47" s="15" t="n">
         <v>3552.5</v>
       </c>
-      <c r="K47" s="18" t="n"/>
+      <c r="K47" s="19" t="n"/>
       <c r="L47" s="15" t="n"/>
       <c r="M47" s="15" t="n">
         <v>284200</v>
@@ -2748,6 +3154,16 @@
       <c r="R47" s="13" t="inlineStr">
         <is>
           <t>правило клиента: летний комплект 3 500 ₽</t>
+        </is>
+      </c>
+      <c r="S47" s="16" t="inlineStr">
+        <is>
+          <t>fabrikant-textile.ru</t>
+        </is>
+      </c>
+      <c r="T47" s="13" t="inlineStr">
+        <is>
+          <t>https://spec-standart.ru/zimnyaya-specodezhda</t>
         </is>
       </c>
     </row>
@@ -2774,7 +3190,7 @@
       <c r="J48" s="15" t="n">
         <v>5052.5</v>
       </c>
-      <c r="K48" s="18" t="n"/>
+      <c r="K48" s="19" t="n"/>
       <c r="L48" s="15" t="n"/>
       <c r="M48" s="15" t="n">
         <v>202100</v>
@@ -2786,6 +3202,16 @@
       <c r="R48" s="13" t="inlineStr">
         <is>
           <t>правило клиента: зимний комплект 5 000 ₽</t>
+        </is>
+      </c>
+      <c r="S48" s="16" t="inlineStr">
+        <is>
+          <t>fabrikant-textile.ru</t>
+        </is>
+      </c>
+      <c r="T48" s="13" t="inlineStr">
+        <is>
+          <t>https://spec-standart.ru/zimnyaya-specodezhda</t>
         </is>
       </c>
     </row>
@@ -2812,7 +3238,7 @@
       <c r="J49" s="15" t="n">
         <v>3070.5</v>
       </c>
-      <c r="K49" s="18" t="n"/>
+      <c r="K49" s="19" t="n"/>
       <c r="L49" s="15" t="n"/>
       <c r="M49" s="15" t="n">
         <v>245640</v>
@@ -2826,6 +3252,12 @@
           <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf (арт. 5.856 «Билд» с мет. носками 3 018.36 ₽)</t>
         </is>
       </c>
+      <c r="S49" s="16" t="inlineStr">
+        <is>
+          <t>files.technoavia.ru</t>
+        </is>
+      </c>
+      <c r="T49" s="13" t="inlineStr"/>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="13" t="inlineStr"/>
@@ -2850,7 +3282,7 @@
       <c r="J50" s="15" t="n">
         <v>88.5</v>
       </c>
-      <c r="K50" s="18" t="n"/>
+      <c r="K50" s="19" t="n"/>
       <c r="L50" s="15" t="n"/>
       <c r="M50" s="15" t="n">
         <v>132750</v>
@@ -2864,6 +3296,12 @@
           <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf (арт. 7.002 «Строй» 36 ₽)</t>
         </is>
       </c>
+      <c r="S50" s="16" t="inlineStr">
+        <is>
+          <t>files.technoavia.ru</t>
+        </is>
+      </c>
+      <c r="T50" s="13" t="inlineStr"/>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="13" t="inlineStr"/>
@@ -2888,7 +3326,7 @@
       <c r="J51" s="15" t="n">
         <v>1144.5</v>
       </c>
-      <c r="K51" s="18" t="n"/>
+      <c r="K51" s="19" t="n"/>
       <c r="L51" s="15" t="n"/>
       <c r="M51" s="15" t="n">
         <v>34335</v>
@@ -2902,6 +3340,12 @@
           <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf (арт. 3.290 1 091.64 ₽)</t>
         </is>
       </c>
+      <c r="S51" s="16" t="inlineStr">
+        <is>
+          <t>files.technoavia.ru</t>
+        </is>
+      </c>
+      <c r="T51" s="13" t="inlineStr"/>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="4" t="n">
@@ -2943,7 +3387,7 @@
       <c r="M52" s="9" t="n">
         <v>561222</v>
       </c>
-      <c r="N52" s="16" t="n">
+      <c r="N52" s="17" t="n">
         <v>0.17</v>
       </c>
       <c r="O52" s="12" t="n">
@@ -2962,6 +3406,8 @@
           <t>по позициям ниже</t>
         </is>
       </c>
+      <c r="S52" s="4" t="n"/>
+      <c r="T52" s="4" t="n"/>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="13" t="inlineStr"/>
@@ -2986,7 +3432,7 @@
       <c r="J53" s="15" t="n">
         <v>12969.86</v>
       </c>
-      <c r="K53" s="16" t="n">
+      <c r="K53" s="17" t="n">
         <v>0.352532265158122</v>
       </c>
       <c r="L53" s="15" t="n"/>
@@ -3000,6 +3446,12 @@
           <t>https://www.trakt.ru/product/142253/</t>
         </is>
       </c>
+      <c r="S53" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T53" s="13" t="inlineStr"/>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="13" t="inlineStr"/>
@@ -3038,6 +3490,12 @@
           <t>https://www.trakt.ru/product/12922/</t>
         </is>
       </c>
+      <c r="S54" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T54" s="13" t="inlineStr"/>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="13" t="inlineStr"/>
@@ -3076,6 +3534,12 @@
           <t>https://www.trakt.ru/product/13076/</t>
         </is>
       </c>
+      <c r="S55" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T55" s="13" t="inlineStr"/>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="13" t="inlineStr"/>
@@ -3100,7 +3564,7 @@
       <c r="J56" s="15" t="n">
         <v>1078.52</v>
       </c>
-      <c r="K56" s="16" t="n">
+      <c r="K56" s="17" t="n">
         <v>0.1989185415165672</v>
       </c>
       <c r="L56" s="15" t="n"/>
@@ -3114,6 +3578,12 @@
           <t>https://www.trakt.ru/product/61070/</t>
         </is>
       </c>
+      <c r="S56" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T56" s="13" t="inlineStr"/>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="13" t="inlineStr"/>
@@ -3138,7 +3608,7 @@
       <c r="J57" s="15" t="n">
         <v>2047.81</v>
       </c>
-      <c r="K57" s="17" t="n">
+      <c r="K57" s="18" t="n">
         <v>-0.1517491563554556</v>
       </c>
       <c r="L57" s="15" t="n"/>
@@ -3152,6 +3622,12 @@
           <t>https://www.trakt.ru/product/61078/</t>
         </is>
       </c>
+      <c r="S57" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T57" s="13" t="inlineStr"/>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="13" t="inlineStr"/>
@@ -3190,6 +3666,12 @@
           <t>https://www.trakt.ru/product/61033/</t>
         </is>
       </c>
+      <c r="S58" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T58" s="13" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="13" t="inlineStr"/>
@@ -3214,7 +3696,7 @@
       <c r="J59" s="15" t="n">
         <v>5030.1</v>
       </c>
-      <c r="K59" s="17" t="n">
+      <c r="K59" s="18" t="n">
         <v>-0.4501523638743381</v>
       </c>
       <c r="L59" s="15" t="n"/>
@@ -3228,6 +3710,12 @@
           <t>https://www.trakt.ru/product/143889/</t>
         </is>
       </c>
+      <c r="S59" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T59" s="13" t="inlineStr"/>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="13" t="inlineStr"/>
@@ -3252,7 +3740,7 @@
       <c r="J60" s="15" t="n">
         <v>33207.83</v>
       </c>
-      <c r="K60" s="16" t="n">
+      <c r="K60" s="17" t="n">
         <v>0.01643353443314751</v>
       </c>
       <c r="L60" s="15" t="n"/>
@@ -3266,6 +3754,12 @@
           <t>https://www.trakt.ru/product/61043/</t>
         </is>
       </c>
+      <c r="S60" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T60" s="13" t="inlineStr"/>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="13" t="inlineStr"/>
@@ -3304,6 +3798,12 @@
           <t>https://www.trakt.ru/product/16450/</t>
         </is>
       </c>
+      <c r="S61" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T61" s="13" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="4" t="n">
@@ -3345,7 +3845,7 @@
       <c r="M62" s="9" t="n">
         <v>133837274</v>
       </c>
-      <c r="N62" s="16" t="n">
+      <c r="N62" s="17" t="n">
         <v>0.32</v>
       </c>
       <c r="O62" s="12" t="n">
@@ -3364,6 +3864,8 @@
           <t>по позициям ниже</t>
         </is>
       </c>
+      <c r="S62" s="4" t="n"/>
+      <c r="T62" s="4" t="n"/>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="13" t="inlineStr"/>
@@ -3388,7 +3890,7 @@
       <c r="J63" s="15" t="n">
         <v>3552.5</v>
       </c>
-      <c r="K63" s="16" t="n">
+      <c r="K63" s="17" t="n">
         <v>0.2332827584123073</v>
       </c>
       <c r="L63" s="15" t="n"/>
@@ -3402,6 +3904,16 @@
           <t>[правило клиента] летний форменный комплект 3500 ₽</t>
         </is>
       </c>
+      <c r="S63" s="16" t="inlineStr">
+        <is>
+          <t>fabrikant-textile.ru</t>
+        </is>
+      </c>
+      <c r="T63" s="13" t="inlineStr">
+        <is>
+          <t>https://spec-standart.ru/zimnyaya-specodezhda</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="13" t="inlineStr"/>
@@ -3426,7 +3938,7 @@
       <c r="J64" s="15" t="n">
         <v>5521.15</v>
       </c>
-      <c r="K64" s="17" t="n">
+      <c r="K64" s="18" t="n">
         <v>-0.01310337740883049</v>
       </c>
       <c r="L64" s="15" t="n"/>
@@ -3440,6 +3952,12 @@
           <t>https://www.trakt.ru/product/11930/</t>
         </is>
       </c>
+      <c r="S64" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T64" s="13" t="inlineStr"/>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="13" t="inlineStr"/>
@@ -3478,6 +3996,12 @@
           <t>https://www.trakt.ru/product/138206/</t>
         </is>
       </c>
+      <c r="S65" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T65" s="13" t="inlineStr"/>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="13" t="inlineStr"/>
@@ -3516,6 +4040,12 @@
           <t>https://www.trakt.ru/product/11891/</t>
         </is>
       </c>
+      <c r="S66" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T66" s="13" t="inlineStr"/>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="13" t="inlineStr"/>
@@ -3540,7 +4070,7 @@
       <c r="J67" s="15" t="n">
         <v>3552.5</v>
       </c>
-      <c r="K67" s="16" t="n">
+      <c r="K67" s="17" t="n">
         <v>0.241999116643587</v>
       </c>
       <c r="L67" s="15" t="n"/>
@@ -3554,6 +4084,16 @@
           <t>[правило клиента] летний форменный комплект 3500 ₽</t>
         </is>
       </c>
+      <c r="S67" s="16" t="inlineStr">
+        <is>
+          <t>fabrikant-textile.ru</t>
+        </is>
+      </c>
+      <c r="T67" s="13" t="inlineStr">
+        <is>
+          <t>https://spec-standart.ru/zimnyaya-specodezhda</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="13" t="inlineStr"/>
@@ -3578,7 +4118,7 @@
       <c r="J68" s="15" t="n">
         <v>1480.51</v>
       </c>
-      <c r="K68" s="17" t="n">
+      <c r="K68" s="18" t="n">
         <v>-0.1650036983994587</v>
       </c>
       <c r="L68" s="15" t="n"/>
@@ -3592,6 +4132,12 @@
           <t>https://www.trakt.ru/product/135628/</t>
         </is>
       </c>
+      <c r="S68" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T68" s="13" t="inlineStr"/>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="13" t="inlineStr"/>
@@ -3630,6 +4176,12 @@
           <t>[оценка] костюм антипорезный летний 7–11 тыс. ₽</t>
         </is>
       </c>
+      <c r="S69" s="13" t="inlineStr">
+        <is>
+          <t>нет открытой цены — оценка</t>
+        </is>
+      </c>
+      <c r="T69" s="14" t="n"/>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="13" t="inlineStr"/>
@@ -3654,7 +4206,7 @@
       <c r="J70" s="15" t="n">
         <v>5937.17</v>
       </c>
-      <c r="K70" s="16" t="n">
+      <c r="K70" s="17" t="n">
         <v>0.3096137343048311</v>
       </c>
       <c r="L70" s="15" t="n"/>
@@ -3668,6 +4220,12 @@
           <t>https://www.trakt.ru/product/16725/</t>
         </is>
       </c>
+      <c r="S70" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T70" s="13" t="inlineStr"/>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="13" t="inlineStr"/>
@@ -3706,6 +4264,12 @@
           <t>https://www.trakt.ru/product/11992/</t>
         </is>
       </c>
+      <c r="S71" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T71" s="13" t="inlineStr"/>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="13" t="inlineStr"/>
@@ -3744,6 +4308,12 @@
           <t>https://www.trakt.ru/product/11891/</t>
         </is>
       </c>
+      <c r="S72" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T72" s="13" t="inlineStr"/>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="13" t="inlineStr"/>
@@ -3768,7 +4338,7 @@
       <c r="J73" s="15" t="n">
         <v>12912.52</v>
       </c>
-      <c r="K73" s="17" t="n">
+      <c r="K73" s="18" t="n">
         <v>-0.08509665643687174</v>
       </c>
       <c r="L73" s="15" t="n"/>
@@ -3782,6 +4352,12 @@
           <t>https://www.trakt.ru/product/12592/</t>
         </is>
       </c>
+      <c r="S73" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T73" s="13" t="inlineStr"/>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="13" t="inlineStr"/>
@@ -3806,7 +4382,7 @@
       <c r="J74" s="15" t="n">
         <v>84.83</v>
       </c>
-      <c r="K74" s="17" t="n">
+      <c r="K74" s="18" t="n">
         <v>-0.5107747105966162</v>
       </c>
       <c r="L74" s="15" t="n"/>
@@ -3820,6 +4396,12 @@
           <t>https://www.trakt.ru/product/13074/</t>
         </is>
       </c>
+      <c r="S74" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T74" s="13" t="inlineStr"/>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="13" t="inlineStr"/>
@@ -3858,6 +4440,12 @@
           <t>https://www.trakt.ru/product/16651/</t>
         </is>
       </c>
+      <c r="S75" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T75" s="13" t="inlineStr"/>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="13" t="inlineStr"/>
@@ -3882,7 +4470,7 @@
       <c r="J76" s="15" t="n">
         <v>5052.5</v>
       </c>
-      <c r="K76" s="16" t="n">
+      <c r="K76" s="17" t="n">
         <v>0.3670227959489459</v>
       </c>
       <c r="L76" s="15" t="n"/>
@@ -3896,6 +4484,16 @@
           <t>[правило клиента] зимний форменный комплект 5000 ₽</t>
         </is>
       </c>
+      <c r="S76" s="16" t="inlineStr">
+        <is>
+          <t>fabrikant-textile.ru</t>
+        </is>
+      </c>
+      <c r="T76" s="13" t="inlineStr">
+        <is>
+          <t>https://spec-standart.ru/zimnyaya-specodezhda</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="13" t="inlineStr"/>
@@ -3920,7 +4518,7 @@
       <c r="J77" s="15" t="n">
         <v>5052.5</v>
       </c>
-      <c r="K77" s="16" t="n">
+      <c r="K77" s="17" t="n">
         <v>0.383904575628838</v>
       </c>
       <c r="L77" s="15" t="n"/>
@@ -3934,6 +4532,16 @@
           <t>[правило клиента] зимний форменный комплект 5000 ₽</t>
         </is>
       </c>
+      <c r="S77" s="16" t="inlineStr">
+        <is>
+          <t>fabrikant-textile.ru</t>
+        </is>
+      </c>
+      <c r="T77" s="13" t="inlineStr">
+        <is>
+          <t>https://spec-standart.ru/zimnyaya-specodezhda</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="13" t="inlineStr"/>
@@ -3972,6 +4580,12 @@
           <t>https://www.trakt.ru/product/12027/</t>
         </is>
       </c>
+      <c r="S78" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T78" s="13" t="inlineStr"/>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="13" t="inlineStr"/>
@@ -3996,7 +4610,7 @@
       <c r="J79" s="15" t="n">
         <v>1753.18</v>
       </c>
-      <c r="K79" s="17" t="n">
+      <c r="K79" s="18" t="n">
         <v>-0.2528620635442424</v>
       </c>
       <c r="L79" s="15" t="n"/>
@@ -4010,6 +4624,12 @@
           <t>https://www.trakt.ru/product/12520/</t>
         </is>
       </c>
+      <c r="S79" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T79" s="13" t="inlineStr"/>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="13" t="inlineStr"/>
@@ -4048,6 +4668,12 @@
           <t>[оценка] костюм антипорезный утепл. (бензопильщика) 9–14 тыс. ₽ (energocontract.ru/catalog/chain-saw — цены по запросу)</t>
         </is>
       </c>
+      <c r="S80" s="13" t="inlineStr">
+        <is>
+          <t>нет открытой цены — оценка</t>
+        </is>
+      </c>
+      <c r="T80" s="14" t="n"/>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="13" t="inlineStr"/>
@@ -4086,6 +4712,12 @@
           <t>https://www.trakt.ru/product/11812/</t>
         </is>
       </c>
+      <c r="S81" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T81" s="13" t="inlineStr"/>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="13" t="inlineStr"/>
@@ -4110,7 +4742,7 @@
       <c r="J82" s="15" t="n">
         <v>1013.25</v>
       </c>
-      <c r="K82" s="16" t="n">
+      <c r="K82" s="17" t="n">
         <v>0.1551039807881527</v>
       </c>
       <c r="L82" s="15" t="n"/>
@@ -4124,6 +4756,12 @@
           <t>https://www.trakt.ru/catalog/zashhita-ruk/kozhanye-perchatki/ (краги РУССКИЕ ЛЬВЫ утепл.)</t>
         </is>
       </c>
+      <c r="S82" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T82" s="13" t="inlineStr"/>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="13" t="inlineStr"/>
@@ -4162,6 +4800,12 @@
           <t>[оценка] перчатки бензопильщика 1.8–3 тыс. ₽</t>
         </is>
       </c>
+      <c r="S83" s="13" t="inlineStr">
+        <is>
+          <t>нет открытой цены — оценка</t>
+        </is>
+      </c>
+      <c r="T83" s="14" t="n"/>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="13" t="inlineStr"/>
@@ -4186,7 +4830,7 @@
       <c r="J84" s="15" t="n">
         <v>856.48</v>
       </c>
-      <c r="K84" s="17" t="n">
+      <c r="K84" s="18" t="n">
         <v>-0.2165909090909091</v>
       </c>
       <c r="L84" s="15" t="n"/>
@@ -4200,6 +4844,12 @@
           <t>https://www.trakt.ru/product/12001/</t>
         </is>
       </c>
+      <c r="S84" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T84" s="13" t="inlineStr"/>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="13" t="inlineStr"/>
@@ -4238,6 +4888,12 @@
           <t>https://www.trakt.ru/product/12913/</t>
         </is>
       </c>
+      <c r="S85" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T85" s="13" t="inlineStr"/>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="13" t="inlineStr"/>
@@ -4276,6 +4932,12 @@
           <t>[оценка] перчатки бензопильщика утепл. 2–3.5 тыс. ₽</t>
         </is>
       </c>
+      <c r="S86" s="13" t="inlineStr">
+        <is>
+          <t>нет открытой цены — оценка</t>
+        </is>
+      </c>
+      <c r="T86" s="14" t="n"/>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="13" t="inlineStr"/>
@@ -4314,6 +4976,12 @@
           <t>[оценка] перчатки резиновые технические 80–150 ₽</t>
         </is>
       </c>
+      <c r="S87" s="13" t="inlineStr">
+        <is>
+          <t>нет открытой цены — оценка</t>
+        </is>
+      </c>
+      <c r="T87" s="14" t="n"/>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="13" t="inlineStr"/>
@@ -4352,6 +5020,12 @@
           <t>[оценка] нарукавники х/б/ПВХ 100–200 ₽</t>
         </is>
       </c>
+      <c r="S88" s="13" t="inlineStr">
+        <is>
+          <t>нет открытой цены — оценка</t>
+        </is>
+      </c>
+      <c r="T88" s="14" t="n"/>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="13" t="inlineStr"/>
@@ -4376,7 +5050,7 @@
       <c r="J89" s="15" t="n">
         <v>311.14</v>
       </c>
-      <c r="K89" s="16" t="n">
+      <c r="K89" s="17" t="n">
         <v>0.1450788591526076</v>
       </c>
       <c r="L89" s="15" t="n"/>
@@ -4390,6 +5064,12 @@
           <t>https://www.trakt.ru/product/11708/</t>
         </is>
       </c>
+      <c r="S89" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T89" s="13" t="inlineStr"/>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="13" t="inlineStr"/>
@@ -4414,7 +5094,7 @@
       <c r="J90" s="15" t="n">
         <v>366.04</v>
       </c>
-      <c r="K90" s="16" t="n">
+      <c r="K90" s="17" t="n">
         <v>0.3309449826357156</v>
       </c>
       <c r="L90" s="15" t="n"/>
@@ -4428,6 +5108,12 @@
           <t>https://www.trakt.ru/product/11707/</t>
         </is>
       </c>
+      <c r="S90" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T90" s="13" t="inlineStr"/>
     </row>
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="13" t="inlineStr"/>
@@ -4466,6 +5152,12 @@
           <t>[оценка] накомарник х/б 150–300 ₽</t>
         </is>
       </c>
+      <c r="S91" s="13" t="inlineStr">
+        <is>
+          <t>нет открытой цены — оценка</t>
+        </is>
+      </c>
+      <c r="T91" s="14" t="n"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="13" t="inlineStr"/>
@@ -4490,7 +5182,7 @@
       <c r="J92" s="15" t="n">
         <v>317.85</v>
       </c>
-      <c r="K92" s="16" t="n">
+      <c r="K92" s="17" t="n">
         <v>0.2126579142927916</v>
       </c>
       <c r="L92" s="15" t="n"/>
@@ -4504,6 +5196,12 @@
           <t>https://www.trakt.ru/product/13005/</t>
         </is>
       </c>
+      <c r="S92" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T92" s="13" t="inlineStr"/>
     </row>
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="13" t="inlineStr"/>
@@ -4528,7 +5226,7 @@
       <c r="J93" s="15" t="n">
         <v>1028.5</v>
       </c>
-      <c r="K93" s="16" t="n">
+      <c r="K93" s="17" t="n">
         <v>0.2467905294070261</v>
       </c>
       <c r="L93" s="15" t="n"/>
@@ -4542,6 +5240,12 @@
           <t>https://www.trakt.ru/product/61033/</t>
         </is>
       </c>
+      <c r="S93" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T93" s="13" t="inlineStr"/>
     </row>
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="13" t="inlineStr"/>
@@ -4580,6 +5284,12 @@
           <t>[оценка] наплечники брезентовые 200–400 ₽</t>
         </is>
       </c>
+      <c r="S94" s="13" t="inlineStr">
+        <is>
+          <t>нет открытой цены — оценка</t>
+        </is>
+      </c>
+      <c r="T94" s="14" t="n"/>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="13" t="inlineStr"/>
@@ -4618,6 +5328,12 @@
           <t>https://www.trakt.ru/product/11961/</t>
         </is>
       </c>
+      <c r="S95" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T95" s="13" t="inlineStr"/>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="13" t="inlineStr"/>
@@ -4642,7 +5358,7 @@
       <c r="J96" s="15" t="n">
         <v>1028.5</v>
       </c>
-      <c r="K96" s="16" t="n">
+      <c r="K96" s="17" t="n">
         <v>0.3454047861507129</v>
       </c>
       <c r="L96" s="15" t="n"/>
@@ -4656,6 +5372,12 @@
           <t>https://www.trakt.ru/product/61033/</t>
         </is>
       </c>
+      <c r="S96" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T96" s="13" t="inlineStr"/>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="13" t="inlineStr"/>
@@ -4680,7 +5402,7 @@
       <c r="J97" s="15" t="n">
         <v>1786.12</v>
       </c>
-      <c r="K97" s="16" t="n">
+      <c r="K97" s="17" t="n">
         <v>0.1493127327802174</v>
       </c>
       <c r="L97" s="15" t="n"/>
@@ -4694,6 +5416,12 @@
           <t>https://www.trakt.ru/product/12190/</t>
         </is>
       </c>
+      <c r="S97" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T97" s="13" t="inlineStr"/>
     </row>
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="13" t="inlineStr"/>
@@ -4718,7 +5446,7 @@
       <c r="J98" s="15" t="n">
         <v>2477.86</v>
       </c>
-      <c r="K98" s="16" t="n">
+      <c r="K98" s="17" t="n">
         <v>0.3180533423604173</v>
       </c>
       <c r="L98" s="15" t="n"/>
@@ -4732,6 +5460,12 @@
           <t>https://www.trakt.ru/product/13076/</t>
         </is>
       </c>
+      <c r="S98" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T98" s="13" t="inlineStr"/>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="13" t="inlineStr"/>
@@ -4756,7 +5490,7 @@
       <c r="J99" s="15" t="n">
         <v>3541.7</v>
       </c>
-      <c r="K99" s="16" t="n">
+      <c r="K99" s="17" t="n">
         <v>0.2083516807746383</v>
       </c>
       <c r="L99" s="15" t="n"/>
@@ -4770,6 +5504,12 @@
           <t>https://www.trakt.ru/product/61013/</t>
         </is>
       </c>
+      <c r="S99" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T99" s="13" t="inlineStr"/>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="13" t="inlineStr"/>
@@ -4794,7 +5534,7 @@
       <c r="J100" s="15" t="n">
         <v>4516.48</v>
       </c>
-      <c r="K100" s="17" t="n">
+      <c r="K100" s="18" t="n">
         <v>-0.1232985054952706</v>
       </c>
       <c r="L100" s="15" t="n"/>
@@ -4808,6 +5548,12 @@
           <t>https://www.trakt.ru/product/16450/</t>
         </is>
       </c>
+      <c r="S100" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T100" s="13" t="inlineStr"/>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="13" t="inlineStr"/>
@@ -4832,7 +5578,7 @@
       <c r="J101" s="15" t="n">
         <v>1961.19</v>
       </c>
-      <c r="K101" s="16" t="n">
+      <c r="K101" s="17" t="n">
         <v>0.387128125</v>
       </c>
       <c r="L101" s="15" t="n"/>
@@ -4846,6 +5592,12 @@
           <t>https://www.trakt.ru/product/12193/</t>
         </is>
       </c>
+      <c r="S101" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T101" s="13" t="inlineStr"/>
     </row>
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="13" t="inlineStr"/>
@@ -4884,6 +5636,12 @@
           <t>https://www.trakt.ru/product/16585/</t>
         </is>
       </c>
+      <c r="S102" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T102" s="13" t="inlineStr"/>
     </row>
     <row r="103" ht="30" customHeight="1">
       <c r="A103" s="13" t="inlineStr"/>
@@ -4908,7 +5666,7 @@
       <c r="J103" s="15" t="n">
         <v>4545.15</v>
       </c>
-      <c r="K103" s="16" t="n">
+      <c r="K103" s="17" t="n">
         <v>0.2504502097680678</v>
       </c>
       <c r="L103" s="15" t="n"/>
@@ -4922,6 +5680,12 @@
           <t>https://www.trakt.ru/product/13084/</t>
         </is>
       </c>
+      <c r="S103" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T103" s="13" t="inlineStr"/>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="13" t="inlineStr"/>
@@ -4946,7 +5710,7 @@
       <c r="J104" s="15" t="n">
         <v>2156.1</v>
       </c>
-      <c r="K104" s="16" t="n">
+      <c r="K104" s="17" t="n">
         <v>0.2340021884636702</v>
       </c>
       <c r="L104" s="15" t="n"/>
@@ -4960,51 +5724,145 @@
           <t>https://www.trakt.ru/catalog/specobuv/valenki/12196/</t>
         </is>
       </c>
+      <c r="S104" s="16" t="inlineStr">
+        <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T104" s="13" t="inlineStr"/>
     </row>
     <row r="105" ht="30" customHeight="1">
-      <c r="A105" s="19" t="inlineStr"/>
-      <c r="B105" s="19" t="inlineStr">
+      <c r="A105" s="20" t="inlineStr"/>
+      <c r="B105" s="20" t="inlineStr">
         <is>
           <t>ИТОГО — обычные условия</t>
         </is>
       </c>
-      <c r="C105" s="19" t="inlineStr"/>
-      <c r="D105" s="19" t="inlineStr"/>
-      <c r="E105" s="19" t="inlineStr"/>
-      <c r="F105" s="19" t="inlineStr"/>
-      <c r="G105" s="19" t="inlineStr"/>
-      <c r="H105" s="19" t="inlineStr"/>
-      <c r="I105" s="19" t="inlineStr"/>
-      <c r="J105" s="19" t="inlineStr"/>
-      <c r="K105" s="19" t="inlineStr"/>
-      <c r="L105" s="20" t="n">
+      <c r="C105" s="20" t="inlineStr"/>
+      <c r="D105" s="20" t="inlineStr"/>
+      <c r="E105" s="20" t="inlineStr"/>
+      <c r="F105" s="20" t="inlineStr"/>
+      <c r="G105" s="20" t="inlineStr"/>
+      <c r="H105" s="20" t="inlineStr"/>
+      <c r="I105" s="20" t="inlineStr"/>
+      <c r="J105" s="20" t="inlineStr"/>
+      <c r="K105" s="20" t="inlineStr"/>
+      <c r="L105" s="21" t="n">
         <v>22113376</v>
       </c>
-      <c r="M105" s="20" t="n">
+      <c r="M105" s="21" t="n">
         <v>9437915</v>
       </c>
-      <c r="N105" s="21" t="n"/>
-      <c r="O105" s="20" t="n">
+      <c r="N105" s="22" t="n"/>
+      <c r="O105" s="21" t="n">
         <v>8097652</v>
       </c>
-      <c r="P105" s="21" t="n"/>
-      <c r="Q105" s="21" t="n"/>
-      <c r="R105" s="21" t="n"/>
+      <c r="P105" s="22" t="n"/>
+      <c r="Q105" s="22" t="n"/>
+      <c r="R105" s="22" t="n"/>
+      <c r="S105" s="22" t="n"/>
+      <c r="T105" s="22" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S37" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S38" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S39" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S42" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S43" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S44" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S45" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S47" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S48" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S49" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S50" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S51" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S53" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S54" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S55" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S56" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S57" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S58" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S59" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S60" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S61" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S63" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S64" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S65" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S66" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S67" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S68" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S70" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S71" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S72" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S73" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S74" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S75" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S76" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S77" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S78" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S79" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S81" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S82" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S89" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S90" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S92" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S93" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S95" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S96" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S97" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S98" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S99" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S100" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S101" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S102" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S103" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S104" r:id="rId98"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/ITOG_LOTS_1410.xlsx
+++ b/ITOG_LOTS_1410.xlsx
@@ -792,9 +792,7 @@
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>https://nsmgr.ru/reagenty/tekhnicheskaya-sol/big-begi
-https://sknerud.ru/reagent/sol-texnicheskaya/
-https://vektor-e.ru/sol/</t>
+          <t>nsmgr.ru, sknerud.ru, vektor-e.ru</t>
         </is>
       </c>
     </row>
@@ -876,9 +874,7 @@
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>https://nsmgr.ru/reagenty/tekhnicheskaya-sol/big-begi
-https://sknerud.ru/reagent/sol-texnicheskaya/
-https://vektor-e.ru/sol/</t>
+          <t>nsmgr.ru, sknerud.ru, vektor-e.ru</t>
         </is>
       </c>
     </row>
@@ -994,8 +990,7 @@
       </c>
       <c r="T7" s="13" t="inlineStr">
         <is>
-          <t>https://www.trakt.ru/product/138206/
-https://www.spets.ru/products/spetsodezhda/odezhda_spetsialnaya/</t>
+          <t>trakt.ru, spets.ru</t>
         </is>
       </c>
     </row>
@@ -1049,8 +1044,7 @@
       </c>
       <c r="T8" s="13" t="inlineStr">
         <is>
-          <t>https://www.trakt.ru/product/12021/
-https://www.spets.ru/products/spetsodezhda/odezhda_dlya_okhrannykh_struktur/</t>
+          <t>trakt.ru, spets.ru</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1098,7 @@
       </c>
       <c r="T9" s="13" t="inlineStr">
         <is>
-          <t>https://ivsoteks.ru/specodejda</t>
+          <t>ivsoteks.ru</t>
         </is>
       </c>
     </row>
@@ -1158,8 +1152,7 @@
       </c>
       <c r="T10" s="13" t="inlineStr">
         <is>
-          <t>https://ivsoteks.ru/specodejda
-https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf</t>
+          <t>ivsoteks.ru, files.technoavia.ru</t>
         </is>
       </c>
     </row>
@@ -1213,8 +1206,7 @@
       </c>
       <c r="T11" s="13" t="inlineStr">
         <is>
-          <t>https://ivsoteks.ru/specodejda
-https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf</t>
+          <t>ivsoteks.ru, files.technoavia.ru</t>
         </is>
       </c>
     </row>
@@ -1268,8 +1260,7 @@
       </c>
       <c r="T12" s="13" t="inlineStr">
         <is>
-          <t>https://www.specteks37.ru/katalog/zimnyaya-spetsodezhda/
-https://www.ivuniforma.ru/catalog/rabochaya-odezhda/zimnjaja/</t>
+          <t>specteks37.ru, ivuniforma.ru</t>
         </is>
       </c>
     </row>
@@ -1323,8 +1314,7 @@
       </c>
       <c r="T13" s="13" t="inlineStr">
         <is>
-          <t>https://spec-standart.ru/zimnyaya-specodezhda
-https://www.trakt.ru/</t>
+          <t>spec-standart.ru, trakt.ru</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1468,7 @@
       </c>
       <c r="T16" s="13" t="inlineStr">
         <is>
-          <t>https://www.spets.ru/products/spetsodezhda/odezhda_spetsialnaya/</t>
+          <t>spets.ru</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1522,7 @@
       </c>
       <c r="T17" s="13" t="inlineStr">
         <is>
-          <t>https://www.spets.ru/products/spetsodezhda/odezhda_spetsialnaya/</t>
+          <t>spets.ru</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1576,7 @@
       </c>
       <c r="T18" s="13" t="inlineStr">
         <is>
-          <t>https://www.spets.ru/products/spetsodezhda/odezhda_spetsialnaya/</t>
+          <t>spets.ru</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1630,7 @@
       </c>
       <c r="T19" s="13" t="inlineStr">
         <is>
-          <t>https://www.spets.ru/products/spetsodezhda/odezhda_spetsialnaya/</t>
+          <t>spets.ru</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1684,7 @@
       </c>
       <c r="T20" s="13" t="inlineStr">
         <is>
-          <t>https://fabrikant-textile.ru/catalog/spetsodezhda/</t>
+          <t>fabrikant-textile.ru</t>
         </is>
       </c>
     </row>
@@ -1748,8 +1738,7 @@
       </c>
       <c r="T21" s="13" t="inlineStr">
         <is>
-          <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf
-https://www.trakt.ru/product/12012/</t>
+          <t>files.technoavia.ru, trakt.ru</t>
         </is>
       </c>
     </row>
@@ -1803,8 +1792,7 @@
       </c>
       <c r="T22" s="13" t="inlineStr">
         <is>
-          <t>https://www.ivuniforma.ru/catalog/rabochaya-odezhda/letnyaya-spetsodezhda/khalati/
-https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf</t>
+          <t>ivuniforma.ru, files.technoavia.ru</t>
         </is>
       </c>
     </row>
@@ -1858,8 +1846,7 @@
       </c>
       <c r="T23" s="13" t="inlineStr">
         <is>
-          <t>https://www.ivuniforma.ru/catalog/rabochaya-odezhda/letnyaya-spetsodezhda/khalati/
-https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf</t>
+          <t>ivuniforma.ru, files.technoavia.ru</t>
         </is>
       </c>
     </row>
@@ -1913,8 +1900,7 @@
       </c>
       <c r="T24" s="13" t="inlineStr">
         <is>
-          <t>https://www.ivuniforma.ru/catalog/rabochaya-odezhda/letnyaya-spetsodezhda/khalati/
-https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf</t>
+          <t>ivuniforma.ru, files.technoavia.ru</t>
         </is>
       </c>
     </row>
@@ -2024,8 +2010,7 @@
       </c>
       <c r="T26" s="13" t="inlineStr">
         <is>
-          <t>https://spec-standart.ru/zimnyaya-specodezhda
-https://www.specteks37.ru/katalog/zimnyaya-spetsodezhda/</t>
+          <t>spec-standart.ru, specteks37.ru</t>
         </is>
       </c>
     </row>
@@ -2073,8 +2058,7 @@
       </c>
       <c r="T27" s="13" t="inlineStr">
         <is>
-          <t>https://www.specteks37.ru/katalog/zimnyaya-spetsodezhda/
-https://www.ivuniforma.ru/catalog/rabochaya-odezhda/zimnjaja/</t>
+          <t>specteks37.ru, ivuniforma.ru</t>
         </is>
       </c>
     </row>
@@ -2122,8 +2106,7 @@
       </c>
       <c r="T28" s="13" t="inlineStr">
         <is>
-          <t>https://spec-standart.ru/zimnyaya-specodezhda
-https://www.trakt.ru/</t>
+          <t>spec-standart.ru, trakt.ru</t>
         </is>
       </c>
     </row>
@@ -2171,8 +2154,7 @@
       </c>
       <c r="T29" s="13" t="inlineStr">
         <is>
-          <t>https://www.specteks37.ru/katalog/zimnyaya-spetsodezhda/
-https://www.ivuniforma.ru/catalog/rabochaya-odezhda/zimnjaja/</t>
+          <t>specteks37.ru, ivuniforma.ru</t>
         </is>
       </c>
     </row>
@@ -2220,8 +2202,7 @@
       </c>
       <c r="T30" s="13" t="inlineStr">
         <is>
-          <t>https://spec-standart.ru/zimnyaya-specodezhda
-https://www.trakt.ru/</t>
+          <t>spec-standart.ru, trakt.ru</t>
         </is>
       </c>
     </row>
@@ -2269,8 +2250,7 @@
       </c>
       <c r="T31" s="13" t="inlineStr">
         <is>
-          <t>https://www.specteks37.ru/katalog/zimnyaya-spetsodezhda/
-https://www.ivuniforma.ru/catalog/rabochaya-odezhda/zimnjaja/</t>
+          <t>specteks37.ru, ivuniforma.ru</t>
         </is>
       </c>
     </row>
@@ -2318,8 +2298,7 @@
       </c>
       <c r="T32" s="13" t="inlineStr">
         <is>
-          <t>https://spec-standart.ru/zimnyaya-specodezhda
-https://www.trakt.ru/</t>
+          <t>spec-standart.ru, trakt.ru</t>
         </is>
       </c>
     </row>
@@ -2411,8 +2390,7 @@
       </c>
       <c r="T34" s="13" t="inlineStr">
         <is>
-          <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf
-https://www.trakt.ru/</t>
+          <t>files.technoavia.ru, trakt.ru</t>
         </is>
       </c>
     </row>
@@ -2504,8 +2482,7 @@
       </c>
       <c r="T36" s="13" t="inlineStr">
         <is>
-          <t>https://www.trakt.ru/product/12021/
-https://www.spets.ru/products/spetsodezhda/odezhda_dlya_okhrannykh_struktur/</t>
+          <t>trakt.ru, spets.ru</t>
         </is>
       </c>
     </row>
@@ -2665,9 +2642,7 @@
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>https://nsmgr.ru/reagenty/tekhnicheskaya-sol/big-begi
-https://sknerud.ru/reagent/sol-texnicheskaya/
-https://vektor-e.ru/sol/</t>
+          <t>nsmgr.ru, sknerud.ru, vektor-e.ru</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2724,7 @@
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>https://dn.ru/sharovyi-kran/teplosnabzhenie/flantcevyi-kran/standartnyi/ld/st20/dn100</t>
+          <t>dn.ru</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2948,7 @@
       </c>
       <c r="T43" s="13" t="inlineStr">
         <is>
-          <t>https://spec-standart.ru/zimnyaya-specodezhda</t>
+          <t>spec-standart.ru</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3138,7 @@
       </c>
       <c r="T47" s="13" t="inlineStr">
         <is>
-          <t>https://spec-standart.ru/zimnyaya-specodezhda</t>
+          <t>spec-standart.ru</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3186,7 @@
       </c>
       <c r="T48" s="13" t="inlineStr">
         <is>
-          <t>https://spec-standart.ru/zimnyaya-specodezhda</t>
+          <t>spec-standart.ru</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3886,7 @@
       </c>
       <c r="T63" s="13" t="inlineStr">
         <is>
-          <t>https://spec-standart.ru/zimnyaya-specodezhda</t>
+          <t>spec-standart.ru</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4066,7 @@
       </c>
       <c r="T67" s="13" t="inlineStr">
         <is>
-          <t>https://spec-standart.ru/zimnyaya-specodezhda</t>
+          <t>spec-standart.ru</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4466,7 @@
       </c>
       <c r="T76" s="13" t="inlineStr">
         <is>
-          <t>https://spec-standart.ru/zimnyaya-specodezhda</t>
+          <t>spec-standart.ru</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4514,7 @@
       </c>
       <c r="T77" s="13" t="inlineStr">
         <is>
-          <t>https://spec-standart.ru/zimnyaya-specodezhda</t>
+          <t>spec-standart.ru</t>
         </is>
       </c>
     </row>

--- a/ITOG_LOTS_1410.xlsx
+++ b/ITOG_LOTS_1410.xlsx
@@ -782,7 +782,7 @@
       </c>
       <c r="R4" s="8" t="inlineStr">
         <is>
-          <t>средняя рыночная с доставкой: завод вагоном / склад авто (SALT_STRATEGY_1410)</t>
+          <t>средняя рыночная с доставкой: завод вагоном / склад авто (SALT_STRATEGY_1410</t>
         </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="R5" s="8" t="inlineStr">
         <is>
-          <t>средняя рыночная с доставкой: завод вагоном / склад авто (SALT_STRATEGY_1410)</t>
+          <t>средняя рыночная с доставкой: завод вагоном / склад авто (SALT_STRATEGY_1410</t>
         </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
@@ -2000,7 +2000,7 @@
       <c r="Q26" s="13" t="inlineStr"/>
       <c r="R26" s="13" t="inlineStr">
         <is>
-          <t>справочник: Костюм зимний рабочий (I–III пояс)</t>
+          <t>справочник: Костюм зимний рабочий (I–III пояс</t>
         </is>
       </c>
       <c r="S26" s="16" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="R38" s="8" t="inlineStr">
         <is>
-          <t>средняя рыночная с доставкой: завод вагоном / склад авто (SALT_STRATEGY_1410)</t>
+          <t>средняя рыночная с доставкой: завод вагоном / склад авто (SALT_STRATEGY_1410</t>
         </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="R39" s="8" t="inlineStr">
         <is>
-          <t>оценка по дилерским прайсам (цен по позициям нет)</t>
+          <t>оценка по дилерским прайсам (цен по позициям нет</t>
         </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
@@ -2894,7 +2894,7 @@
       <c r="Q42" s="13" t="inlineStr"/>
       <c r="R42" s="13" t="inlineStr">
         <is>
-          <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf (арт. 3.290 1 091.64 ₽)</t>
+          <t>арт. 3.290 1 091.64 ₽</t>
         </is>
       </c>
       <c r="S42" s="16" t="inlineStr">
@@ -2986,7 +2986,7 @@
       <c r="Q44" s="13" t="inlineStr"/>
       <c r="R44" s="13" t="inlineStr">
         <is>
-          <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf (арт. 4.025 477.84 ₽)</t>
+          <t>арт. 4.025 477.84 ₽</t>
         </is>
       </c>
       <c r="S44" s="16" t="inlineStr">
@@ -3030,7 +3030,7 @@
       <c r="Q45" s="13" t="inlineStr"/>
       <c r="R45" s="13" t="inlineStr">
         <is>
-          <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf (арт. 5.856 «Билд» с мет. носками 3 018.36 ₽)</t>
+          <t>арт. 5.856 «Билд» с мет. носками 3 018.36 ₽</t>
         </is>
       </c>
       <c r="S45" s="16" t="inlineStr">
@@ -3224,7 +3224,7 @@
       <c r="Q49" s="13" t="inlineStr"/>
       <c r="R49" s="13" t="inlineStr">
         <is>
-          <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf (арт. 5.856 «Билд» с мет. носками 3 018.36 ₽)</t>
+          <t>арт. 5.856 «Билд» с мет. носками 3 018.36 ₽</t>
         </is>
       </c>
       <c r="S49" s="16" t="inlineStr">
@@ -3268,7 +3268,7 @@
       <c r="Q50" s="13" t="inlineStr"/>
       <c r="R50" s="13" t="inlineStr">
         <is>
-          <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf (арт. 7.002 «Строй» 36 ₽)</t>
+          <t>арт. 7.002 «Строй» 36 ₽</t>
         </is>
       </c>
       <c r="S50" s="16" t="inlineStr">
@@ -3312,7 +3312,7 @@
       <c r="Q51" s="13" t="inlineStr"/>
       <c r="R51" s="13" t="inlineStr">
         <is>
-          <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf (арт. 3.290 1 091.64 ₽)</t>
+          <t>арт. 3.290 1 091.64 ₽</t>
         </is>
       </c>
       <c r="S51" s="16" t="inlineStr">
@@ -3416,11 +3416,7 @@
       <c r="O53" s="14" t="n"/>
       <c r="P53" s="14" t="n"/>
       <c r="Q53" s="13" t="inlineStr"/>
-      <c r="R53" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/142253/</t>
-        </is>
-      </c>
+      <c r="R53" s="13" t="inlineStr"/>
       <c r="S53" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -3460,11 +3456,7 @@
       <c r="O54" s="14" t="n"/>
       <c r="P54" s="14" t="n"/>
       <c r="Q54" s="13" t="inlineStr"/>
-      <c r="R54" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/12922/</t>
-        </is>
-      </c>
+      <c r="R54" s="13" t="inlineStr"/>
       <c r="S54" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -3504,11 +3496,7 @@
       <c r="O55" s="14" t="n"/>
       <c r="P55" s="14" t="n"/>
       <c r="Q55" s="13" t="inlineStr"/>
-      <c r="R55" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/13076/</t>
-        </is>
-      </c>
+      <c r="R55" s="13" t="inlineStr"/>
       <c r="S55" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -3548,11 +3536,7 @@
       <c r="O56" s="14" t="n"/>
       <c r="P56" s="14" t="n"/>
       <c r="Q56" s="13" t="inlineStr"/>
-      <c r="R56" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/61070/</t>
-        </is>
-      </c>
+      <c r="R56" s="13" t="inlineStr"/>
       <c r="S56" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -3592,11 +3576,7 @@
       <c r="O57" s="14" t="n"/>
       <c r="P57" s="14" t="n"/>
       <c r="Q57" s="13" t="inlineStr"/>
-      <c r="R57" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/61078/</t>
-        </is>
-      </c>
+      <c r="R57" s="13" t="inlineStr"/>
       <c r="S57" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -3636,11 +3616,7 @@
       <c r="O58" s="14" t="n"/>
       <c r="P58" s="14" t="n"/>
       <c r="Q58" s="13" t="inlineStr"/>
-      <c r="R58" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/61033/</t>
-        </is>
-      </c>
+      <c r="R58" s="13" t="inlineStr"/>
       <c r="S58" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -3680,11 +3656,7 @@
       <c r="O59" s="14" t="n"/>
       <c r="P59" s="14" t="n"/>
       <c r="Q59" s="13" t="inlineStr"/>
-      <c r="R59" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/143889/</t>
-        </is>
-      </c>
+      <c r="R59" s="13" t="inlineStr"/>
       <c r="S59" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -3724,11 +3696,7 @@
       <c r="O60" s="14" t="n"/>
       <c r="P60" s="14" t="n"/>
       <c r="Q60" s="13" t="inlineStr"/>
-      <c r="R60" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/61043/</t>
-        </is>
-      </c>
+      <c r="R60" s="13" t="inlineStr"/>
       <c r="S60" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -3768,11 +3736,7 @@
       <c r="O61" s="14" t="n"/>
       <c r="P61" s="14" t="n"/>
       <c r="Q61" s="13" t="inlineStr"/>
-      <c r="R61" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/16450/</t>
-        </is>
-      </c>
+      <c r="R61" s="13" t="inlineStr"/>
       <c r="S61" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -3922,11 +3886,7 @@
       <c r="O64" s="14" t="n"/>
       <c r="P64" s="14" t="n"/>
       <c r="Q64" s="13" t="inlineStr"/>
-      <c r="R64" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/11930/</t>
-        </is>
-      </c>
+      <c r="R64" s="13" t="inlineStr"/>
       <c r="S64" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -3966,11 +3926,7 @@
       <c r="O65" s="14" t="n"/>
       <c r="P65" s="14" t="n"/>
       <c r="Q65" s="13" t="inlineStr"/>
-      <c r="R65" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/138206/</t>
-        </is>
-      </c>
+      <c r="R65" s="13" t="inlineStr"/>
       <c r="S65" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -4010,11 +3966,7 @@
       <c r="O66" s="14" t="n"/>
       <c r="P66" s="14" t="n"/>
       <c r="Q66" s="13" t="inlineStr"/>
-      <c r="R66" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/11891/</t>
-        </is>
-      </c>
+      <c r="R66" s="13" t="inlineStr"/>
       <c r="S66" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -4102,11 +4054,7 @@
       <c r="O68" s="14" t="n"/>
       <c r="P68" s="14" t="n"/>
       <c r="Q68" s="13" t="inlineStr"/>
-      <c r="R68" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/135628/</t>
-        </is>
-      </c>
+      <c r="R68" s="13" t="inlineStr"/>
       <c r="S68" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -4190,11 +4138,7 @@
       <c r="O70" s="14" t="n"/>
       <c r="P70" s="14" t="n"/>
       <c r="Q70" s="13" t="inlineStr"/>
-      <c r="R70" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/16725/</t>
-        </is>
-      </c>
+      <c r="R70" s="13" t="inlineStr"/>
       <c r="S70" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -4234,11 +4178,7 @@
       <c r="O71" s="14" t="n"/>
       <c r="P71" s="14" t="n"/>
       <c r="Q71" s="13" t="inlineStr"/>
-      <c r="R71" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/11992/</t>
-        </is>
-      </c>
+      <c r="R71" s="13" t="inlineStr"/>
       <c r="S71" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -4278,11 +4218,7 @@
       <c r="O72" s="14" t="n"/>
       <c r="P72" s="14" t="n"/>
       <c r="Q72" s="13" t="inlineStr"/>
-      <c r="R72" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/11891/</t>
-        </is>
-      </c>
+      <c r="R72" s="13" t="inlineStr"/>
       <c r="S72" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -4322,11 +4258,7 @@
       <c r="O73" s="14" t="n"/>
       <c r="P73" s="14" t="n"/>
       <c r="Q73" s="13" t="inlineStr"/>
-      <c r="R73" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/12592/</t>
-        </is>
-      </c>
+      <c r="R73" s="13" t="inlineStr"/>
       <c r="S73" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -4366,11 +4298,7 @@
       <c r="O74" s="14" t="n"/>
       <c r="P74" s="14" t="n"/>
       <c r="Q74" s="13" t="inlineStr"/>
-      <c r="R74" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/13074/</t>
-        </is>
-      </c>
+      <c r="R74" s="13" t="inlineStr"/>
       <c r="S74" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -4410,11 +4338,7 @@
       <c r="O75" s="14" t="n"/>
       <c r="P75" s="14" t="n"/>
       <c r="Q75" s="13" t="inlineStr"/>
-      <c r="R75" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/16651/</t>
-        </is>
-      </c>
+      <c r="R75" s="13" t="inlineStr"/>
       <c r="S75" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -4550,11 +4474,7 @@
       <c r="O78" s="14" t="n"/>
       <c r="P78" s="14" t="n"/>
       <c r="Q78" s="13" t="inlineStr"/>
-      <c r="R78" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/12027/</t>
-        </is>
-      </c>
+      <c r="R78" s="13" t="inlineStr"/>
       <c r="S78" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -4594,11 +4514,7 @@
       <c r="O79" s="14" t="n"/>
       <c r="P79" s="14" t="n"/>
       <c r="Q79" s="13" t="inlineStr"/>
-      <c r="R79" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/12520/</t>
-        </is>
-      </c>
+      <c r="R79" s="13" t="inlineStr"/>
       <c r="S79" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -4640,7 +4556,7 @@
       <c r="Q80" s="13" t="inlineStr"/>
       <c r="R80" s="13" t="inlineStr">
         <is>
-          <t>[оценка] костюм антипорезный утепл. (бензопильщика) 9–14 тыс. ₽ (energocontract.ru/catalog/chain-saw — цены по запросу)</t>
+          <t>[оценка] костюм антипорезный утепл. (бензопильщика) 9–14 тыс. ₽ (energocontract.ru/ca…</t>
         </is>
       </c>
       <c r="S80" s="13" t="inlineStr">
@@ -4682,11 +4598,7 @@
       <c r="O81" s="14" t="n"/>
       <c r="P81" s="14" t="n"/>
       <c r="Q81" s="13" t="inlineStr"/>
-      <c r="R81" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/11812/</t>
-        </is>
-      </c>
+      <c r="R81" s="13" t="inlineStr"/>
       <c r="S81" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -4728,7 +4640,7 @@
       <c r="Q82" s="13" t="inlineStr"/>
       <c r="R82" s="13" t="inlineStr">
         <is>
-          <t>https://www.trakt.ru/catalog/zashhita-ruk/kozhanye-perchatki/ (краги РУССКИЕ ЛЬВЫ утепл.)</t>
+          <t>краги РУССКИЕ ЛЬВЫ утепл.</t>
         </is>
       </c>
       <c r="S82" s="16" t="inlineStr">
@@ -4814,11 +4726,7 @@
       <c r="O84" s="14" t="n"/>
       <c r="P84" s="14" t="n"/>
       <c r="Q84" s="13" t="inlineStr"/>
-      <c r="R84" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/12001/</t>
-        </is>
-      </c>
+      <c r="R84" s="13" t="inlineStr"/>
       <c r="S84" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -4858,11 +4766,7 @@
       <c r="O85" s="14" t="n"/>
       <c r="P85" s="14" t="n"/>
       <c r="Q85" s="13" t="inlineStr"/>
-      <c r="R85" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/12913/</t>
-        </is>
-      </c>
+      <c r="R85" s="13" t="inlineStr"/>
       <c r="S85" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -5034,11 +4938,7 @@
       <c r="O89" s="14" t="n"/>
       <c r="P89" s="14" t="n"/>
       <c r="Q89" s="13" t="inlineStr"/>
-      <c r="R89" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/11708/</t>
-        </is>
-      </c>
+      <c r="R89" s="13" t="inlineStr"/>
       <c r="S89" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -5078,11 +4978,7 @@
       <c r="O90" s="14" t="n"/>
       <c r="P90" s="14" t="n"/>
       <c r="Q90" s="13" t="inlineStr"/>
-      <c r="R90" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/11707/</t>
-        </is>
-      </c>
+      <c r="R90" s="13" t="inlineStr"/>
       <c r="S90" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -5166,11 +5062,7 @@
       <c r="O92" s="14" t="n"/>
       <c r="P92" s="14" t="n"/>
       <c r="Q92" s="13" t="inlineStr"/>
-      <c r="R92" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/13005/</t>
-        </is>
-      </c>
+      <c r="R92" s="13" t="inlineStr"/>
       <c r="S92" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -5210,11 +5102,7 @@
       <c r="O93" s="14" t="n"/>
       <c r="P93" s="14" t="n"/>
       <c r="Q93" s="13" t="inlineStr"/>
-      <c r="R93" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/61033/</t>
-        </is>
-      </c>
+      <c r="R93" s="13" t="inlineStr"/>
       <c r="S93" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -5298,11 +5186,7 @@
       <c r="O95" s="14" t="n"/>
       <c r="P95" s="14" t="n"/>
       <c r="Q95" s="13" t="inlineStr"/>
-      <c r="R95" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/11961/</t>
-        </is>
-      </c>
+      <c r="R95" s="13" t="inlineStr"/>
       <c r="S95" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -5342,11 +5226,7 @@
       <c r="O96" s="14" t="n"/>
       <c r="P96" s="14" t="n"/>
       <c r="Q96" s="13" t="inlineStr"/>
-      <c r="R96" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/61033/</t>
-        </is>
-      </c>
+      <c r="R96" s="13" t="inlineStr"/>
       <c r="S96" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -5386,11 +5266,7 @@
       <c r="O97" s="14" t="n"/>
       <c r="P97" s="14" t="n"/>
       <c r="Q97" s="13" t="inlineStr"/>
-      <c r="R97" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/12190/</t>
-        </is>
-      </c>
+      <c r="R97" s="13" t="inlineStr"/>
       <c r="S97" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -5430,11 +5306,7 @@
       <c r="O98" s="14" t="n"/>
       <c r="P98" s="14" t="n"/>
       <c r="Q98" s="13" t="inlineStr"/>
-      <c r="R98" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/13076/</t>
-        </is>
-      </c>
+      <c r="R98" s="13" t="inlineStr"/>
       <c r="S98" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -5474,11 +5346,7 @@
       <c r="O99" s="14" t="n"/>
       <c r="P99" s="14" t="n"/>
       <c r="Q99" s="13" t="inlineStr"/>
-      <c r="R99" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/61013/</t>
-        </is>
-      </c>
+      <c r="R99" s="13" t="inlineStr"/>
       <c r="S99" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -5518,11 +5386,7 @@
       <c r="O100" s="14" t="n"/>
       <c r="P100" s="14" t="n"/>
       <c r="Q100" s="13" t="inlineStr"/>
-      <c r="R100" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/16450/</t>
-        </is>
-      </c>
+      <c r="R100" s="13" t="inlineStr"/>
       <c r="S100" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -5562,11 +5426,7 @@
       <c r="O101" s="14" t="n"/>
       <c r="P101" s="14" t="n"/>
       <c r="Q101" s="13" t="inlineStr"/>
-      <c r="R101" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/12193/</t>
-        </is>
-      </c>
+      <c r="R101" s="13" t="inlineStr"/>
       <c r="S101" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -5606,11 +5466,7 @@
       <c r="O102" s="14" t="n"/>
       <c r="P102" s="14" t="n"/>
       <c r="Q102" s="13" t="inlineStr"/>
-      <c r="R102" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/16585/</t>
-        </is>
-      </c>
+      <c r="R102" s="13" t="inlineStr"/>
       <c r="S102" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -5650,11 +5506,7 @@
       <c r="O103" s="14" t="n"/>
       <c r="P103" s="14" t="n"/>
       <c r="Q103" s="13" t="inlineStr"/>
-      <c r="R103" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/product/13084/</t>
-        </is>
-      </c>
+      <c r="R103" s="13" t="inlineStr"/>
       <c r="S103" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
@@ -5694,11 +5546,7 @@
       <c r="O104" s="14" t="n"/>
       <c r="P104" s="14" t="n"/>
       <c r="Q104" s="13" t="inlineStr"/>
-      <c r="R104" s="13" t="inlineStr">
-        <is>
-          <t>https://www.trakt.ru/catalog/specobuv/valenki/12196/</t>
-        </is>
-      </c>
+      <c r="R104" s="13" t="inlineStr"/>
       <c r="S104" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>

--- a/ITOG_LOTS_1410.xlsx
+++ b/ITOG_LOTS_1410.xlsx
@@ -155,10 +155,10 @@
     <xf numFmtId="9" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -589,7 +589,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Строка лота (жирная) — итог по лоту; строки ниже — позиции. Себестоимость за ед. — средняя по открытым ценам фабрик/оптовиков + доставка. Прибыль чистая (УСН 15%) при ожидаемом снижении.</t>
+          <t>Строка лота (жирная) — итог по лоту; строки ниже — позиции. Себестоимость за ед. — медиана опт/прайс 2026 по проверенным ссылкам (Тракт, Спецобъединение, Техноавиа, Фабрикант, ivuniforma…) + доставка. Прибыль чистая (УСН 15%) при ожидаемом снижении.</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -755,25 +755,25 @@
         <v>16810</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>4870</v>
+        <v>5400</v>
       </c>
       <c r="K4" s="10" t="n">
-        <v>0.710291493158834</v>
+        <v>0.6787626412849495</v>
       </c>
       <c r="L4" s="9" t="n">
         <v>6724000</v>
       </c>
       <c r="M4" s="9" t="n">
-        <v>1948000</v>
+        <v>2160000</v>
       </c>
       <c r="N4" s="11" t="n">
-        <v>0.710291493158834</v>
+        <v>0.6787626412849495</v>
       </c>
       <c r="O4" s="12" t="n">
-        <v>3108988</v>
+        <v>2922864</v>
       </c>
       <c r="P4" s="10" t="n">
-        <v>0.6983536591937705</v>
+        <v>0.6655256179971993</v>
       </c>
       <c r="Q4" s="8" t="inlineStr">
         <is>
@@ -782,17 +782,17 @@
       </c>
       <c r="R4" s="8" t="inlineStr">
         <is>
-          <t>средняя рыночная с доставкой: завод вагоном / склад авто (SALT_STRATEGY_1410</t>
+          <t>МО: с доставкой 4 600–5 950 (perevalki.ru, Белкалий МКР) / 4 900–6 000 (mariva.ru); с…</t>
         </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>esolk.ru</t>
+          <t>perevalki.ru</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>nsmgr.ru, sknerud.ru, vektor-e.ru</t>
+          <t>mariva.ru, nsmgr.ru</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Соль: МКУ «Дзержинка», Новосибирск</t>
+          <t>Спецодежда: ФБУ (Госрезерв), 18 позиций</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>0851300006226000106</t>
+          <t>32616431081</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -817,134 +817,106 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>44-ФЗ запрос котировок</t>
+          <t>223-ФЗ, не аукцион</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>16.10 05:00</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>400</v>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="n">
-        <v>11000</v>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>4310</v>
-      </c>
-      <c r="K5" s="10" t="n">
-        <v>0.6081818181818182</v>
-      </c>
+          <t>19.10 08:00</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="9" t="n"/>
+      <c r="J5" s="9" t="n"/>
+      <c r="K5" s="10" t="n"/>
       <c r="L5" s="9" t="n">
-        <v>4400000</v>
+        <v>3637476</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>1724000</v>
+        <v>1366955</v>
       </c>
       <c r="N5" s="11" t="n">
-        <v>0.6081818181818182</v>
+        <v>0.6242022339906012</v>
       </c>
       <c r="O5" s="12" t="n">
-        <v>1639990</v>
+        <v>1560296</v>
       </c>
       <c r="P5" s="10" t="n">
-        <v>0.5920364158598802</v>
+        <v>0.6087169747416499</v>
       </c>
       <c r="Q5" s="8" t="inlineStr">
         <is>
-          <t>1% / 5%</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="R5" s="8" t="inlineStr">
         <is>
-          <t>средняя рыночная с доставкой: завод вагоном / склад авто (SALT_STRATEGY_1410</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>esolk.ru</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>nsmgr.ru, sknerud.ru, vektor-e.ru</t>
-        </is>
-      </c>
+          <t>по позициям ниже</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="n"/>
+      <c r="T5" s="4" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Спецодежда: ФБУ (Госрезерв), 18 позиций</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>32616431081</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>223-ФЗ, не аукцион</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>19.10 08:00</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="9" t="n"/>
-      <c r="J6" s="9" t="n"/>
-      <c r="K6" s="10" t="n"/>
-      <c r="L6" s="9" t="n">
-        <v>3637476</v>
-      </c>
-      <c r="M6" s="9" t="n">
-        <v>1460092</v>
-      </c>
-      <c r="N6" s="11" t="n">
-        <v>0.5985975516644549</v>
-      </c>
-      <c r="O6" s="12" t="n">
-        <v>1478527</v>
-      </c>
-      <c r="P6" s="10" t="n">
-        <v>0.5820572165750648</v>
-      </c>
-      <c r="Q6" s="8" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="R6" s="8" t="inlineStr">
-        <is>
-          <t>по позициям ниже</t>
-        </is>
-      </c>
-      <c r="S6" s="4" t="n"/>
-      <c r="T6" s="4" t="n"/>
+      <c r="A6" s="13" t="inlineStr"/>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Жилет сигнальный</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr"/>
+      <c r="D6" s="13" t="inlineStr"/>
+      <c r="E6" s="13" t="inlineStr"/>
+      <c r="F6" s="13" t="inlineStr"/>
+      <c r="G6" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>900.22</v>
+      </c>
+      <c r="J6" s="15" t="n">
+        <v>321.23</v>
+      </c>
+      <c r="K6" s="11" t="n">
+        <v>0.6431650041101065</v>
+      </c>
+      <c r="L6" s="15" t="n">
+        <v>12603.08</v>
+      </c>
+      <c r="M6" s="15" t="n">
+        <v>4497.22</v>
+      </c>
+      <c r="N6" s="14" t="n"/>
+      <c r="O6" s="14" t="n"/>
+      <c r="P6" s="14" t="n"/>
+      <c r="Q6" s="13" t="inlineStr"/>
+      <c r="R6" s="13" t="inlineStr">
+        <is>
+          <t>медиана опт/прайс 2026: fabrikant-textile.ru 260; techno-avia.ru 396; ivuniforma.ru 2…</t>
+        </is>
+      </c>
+      <c r="S6" s="16" t="inlineStr">
+        <is>
+          <t>fabrikant-textile.ru</t>
+        </is>
+      </c>
+      <c r="T6" s="13" t="inlineStr">
+        <is>
+          <t>files.technoavia.ru, ivuniforma.ru</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="13" t="inlineStr"/>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Жилет сигнальный</t>
+          <t xml:space="preserve">   Жилет утепленный</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr"/>
@@ -952,27 +924,27 @@
       <c r="E7" s="13" t="inlineStr"/>
       <c r="F7" s="13" t="inlineStr"/>
       <c r="G7" s="14" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Штука</t>
         </is>
       </c>
       <c r="I7" s="15" t="n">
-        <v>900.22</v>
+        <v>5316.19</v>
       </c>
       <c r="J7" s="15" t="n">
-        <v>295.25</v>
+        <v>1613.855</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>0.6720246162049277</v>
+        <v>0.6964263880711562</v>
       </c>
       <c r="L7" s="15" t="n">
-        <v>12603.08</v>
+        <v>340236.16</v>
       </c>
       <c r="M7" s="15" t="n">
-        <v>4133.5</v>
+        <v>103286.72</v>
       </c>
       <c r="N7" s="14" t="n"/>
       <c r="O7" s="14" t="n"/>
@@ -980,17 +952,17 @@
       <c r="Q7" s="13" t="inlineStr"/>
       <c r="R7" s="13" t="inlineStr">
         <is>
-          <t>справочник: Жилет сигнальный</t>
+          <t>медиана опт/прайс 2026: techno-avia.ru 1 313; ivuniforma.ru 875; trakt.ru 1 866</t>
         </is>
       </c>
       <c r="S7" s="16" t="inlineStr">
         <is>
-          <t>fabrikant-textile.ru</t>
+          <t>files.technoavia.ru</t>
         </is>
       </c>
       <c r="T7" s="13" t="inlineStr">
         <is>
-          <t>trakt.ru, spets.ru</t>
+          <t>ivuniforma.ru, trakt.ru</t>
         </is>
       </c>
     </row>
@@ -998,7 +970,7 @@
       <c r="A8" s="13" t="inlineStr"/>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Жилет утепленный</t>
+          <t xml:space="preserve">   Костюм летний мужской противоэнцэфалитный</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr"/>
@@ -1006,27 +978,27 @@
       <c r="E8" s="13" t="inlineStr"/>
       <c r="F8" s="13" t="inlineStr"/>
       <c r="G8" s="14" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Комплект</t>
         </is>
       </c>
       <c r="I8" s="15" t="n">
-        <v>5316.19</v>
+        <v>15580.14</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>1305.5</v>
+        <v>3171.7</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>0.754429393983285</v>
+        <v>0.7964267330075339</v>
       </c>
       <c r="L8" s="15" t="n">
-        <v>340236.16</v>
+        <v>15580.14</v>
       </c>
       <c r="M8" s="15" t="n">
-        <v>83552</v>
+        <v>3171.7</v>
       </c>
       <c r="N8" s="14" t="n"/>
       <c r="O8" s="14" t="n"/>
@@ -1034,17 +1006,17 @@
       <c r="Q8" s="13" t="inlineStr"/>
       <c r="R8" s="13" t="inlineStr">
         <is>
-          <t>справочник: Жилет утепленный</t>
+          <t>медиана опт/прайс 2026: fabrikant-textile.ru 975; techno-avia.ru 4 546; specteks37.ru…</t>
         </is>
       </c>
       <c r="S8" s="16" t="inlineStr">
         <is>
-          <t>ivuniforma.ru</t>
+          <t>fabrikant-textile.ru</t>
         </is>
       </c>
       <c r="T8" s="13" t="inlineStr">
         <is>
-          <t>trakt.ru, spets.ru</t>
+          <t>files.technoavia.ru, specteks37.ru</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1024,7 @@
       <c r="A9" s="13" t="inlineStr"/>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Костюм летний мужской противоэнцэфалитный</t>
+          <t xml:space="preserve">   Костюм летний мужской для защиты от механических воздействий и общих производственных загрязнений</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr"/>
@@ -1060,27 +1032,27 @@
       <c r="E9" s="13" t="inlineStr"/>
       <c r="F9" s="13" t="inlineStr"/>
       <c r="G9" s="14" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Комплект</t>
         </is>
       </c>
       <c r="I9" s="15" t="n">
-        <v>15580.14</v>
+        <v>9971.469999999999</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>1147</v>
+        <v>3542</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>0.9263806358607818</v>
+        <v>0.6447865761016179</v>
       </c>
       <c r="L9" s="15" t="n">
-        <v>15580.14</v>
+        <v>229343.81</v>
       </c>
       <c r="M9" s="15" t="n">
-        <v>1147</v>
+        <v>81466</v>
       </c>
       <c r="N9" s="14" t="n"/>
       <c r="O9" s="14" t="n"/>
@@ -1088,7 +1060,7 @@
       <c r="Q9" s="13" t="inlineStr"/>
       <c r="R9" s="13" t="inlineStr">
         <is>
-          <t>Фабрикант 975 / Ивсотекс 1 250</t>
+          <t>ваша себестоимость; рынок 2026: fabrikant-textile.ru 495; fabrikant-textile.ru 850; t…</t>
         </is>
       </c>
       <c r="S9" s="16" t="inlineStr">
@@ -1098,7 +1070,7 @@
       </c>
       <c r="T9" s="13" t="inlineStr">
         <is>
-          <t>ivsoteks.ru</t>
+          <t>fabrikant-textile.ru, files.technoavia.ru</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1078,7 @@
       <c r="A10" s="13" t="inlineStr"/>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Костюм летний мужской для защиты от механических воздействий и общих производственных загрязнений</t>
+          <t xml:space="preserve">   Костюм летний женский для защиты от механических воздействий и общих производственных загрязнений</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr"/>
@@ -1114,11 +1086,11 @@
       <c r="E10" s="13" t="inlineStr"/>
       <c r="F10" s="13" t="inlineStr"/>
       <c r="G10" s="14" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Комплект</t>
         </is>
       </c>
       <c r="I10" s="15" t="n">
@@ -1131,10 +1103,10 @@
         <v>0.6447865761016179</v>
       </c>
       <c r="L10" s="15" t="n">
-        <v>229343.81</v>
+        <v>9971.469999999999</v>
       </c>
       <c r="M10" s="15" t="n">
-        <v>81466</v>
+        <v>3542</v>
       </c>
       <c r="N10" s="14" t="n"/>
       <c r="O10" s="14" t="n"/>
@@ -1142,17 +1114,17 @@
       <c r="Q10" s="13" t="inlineStr"/>
       <c r="R10" s="13" t="inlineStr">
         <is>
-          <t>справочник: Костюм летний рабочий</t>
+          <t>ваша себестоимость; рынок 2026: fabrikant-textile.ru 495; fabrikant-textile.ru 850; t…</t>
         </is>
       </c>
       <c r="S10" s="16" t="inlineStr">
         <is>
-          <t>ivuniforma.ru</t>
+          <t>fabrikant-textile.ru</t>
         </is>
       </c>
       <c r="T10" s="13" t="inlineStr">
         <is>
-          <t>ivsoteks.ru, files.technoavia.ru</t>
+          <t>fabrikant-textile.ru, files.technoavia.ru</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1132,7 @@
       <c r="A11" s="13" t="inlineStr"/>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Костюм летний женский для защиты от механических воздействий и общих производственных загрязнений</t>
+          <t xml:space="preserve">   Куртка зимняя мужской для защиты от механических воздействий и общих производственных загрязнений</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr"/>
@@ -1168,27 +1140,27 @@
       <c r="E11" s="13" t="inlineStr"/>
       <c r="F11" s="13" t="inlineStr"/>
       <c r="G11" s="14" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Штука</t>
         </is>
       </c>
       <c r="I11" s="15" t="n">
-        <v>9971.469999999999</v>
+        <v>8546.92</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>3542</v>
+        <v>2551.1</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0.6447865761016179</v>
+        <v>0.701518207728632</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>9971.469999999999</v>
+        <v>170938.4</v>
       </c>
       <c r="M11" s="15" t="n">
-        <v>3542</v>
+        <v>51022</v>
       </c>
       <c r="N11" s="14" t="n"/>
       <c r="O11" s="14" t="n"/>
@@ -1196,17 +1168,17 @@
       <c r="Q11" s="13" t="inlineStr"/>
       <c r="R11" s="13" t="inlineStr">
         <is>
-          <t>справочник: Костюм летний рабочий</t>
+          <t>медиана опт/прайс 2026: fabrikant-textile.ru 1 125; techno-avia.ru 4 567; specteks37.…</t>
         </is>
       </c>
       <c r="S11" s="16" t="inlineStr">
         <is>
-          <t>ivuniforma.ru</t>
+          <t>fabrikant-textile.ru</t>
         </is>
       </c>
       <c r="T11" s="13" t="inlineStr">
         <is>
-          <t>ivsoteks.ru, files.technoavia.ru</t>
+          <t>files.technoavia.ru, specteks37.ru</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1186,7 @@
       <c r="A12" s="13" t="inlineStr"/>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Куртка зимняя мужской для защиты от механических воздействий и общих производственных загрязнений</t>
+          <t xml:space="preserve">   Полукомбинезон зимний мужской для защиты от механических воздействий и общих производственных загрязнений</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr"/>
@@ -1226,23 +1198,23 @@
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Штука</t>
         </is>
       </c>
       <c r="I12" s="15" t="n">
-        <v>8546.92</v>
+        <v>7973.42</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>2203.333333333333</v>
+        <v>1225</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>0.7422073292679312</v>
+        <v>0.8463645462047653</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>170938.4</v>
+        <v>159468.4</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>44066.66666666666</v>
+        <v>24500</v>
       </c>
       <c r="N12" s="14" t="n"/>
       <c r="O12" s="14" t="n"/>
@@ -1250,7 +1222,7 @@
       <c r="Q12" s="13" t="inlineStr"/>
       <c r="R12" s="13" t="inlineStr">
         <is>
-          <t>справочник: Куртка утепленная</t>
+          <t>медиана опт/прайс 2026: fabrikant-textile.ru 720; techno-avia.ru 2 828; spets.ru 1 019</t>
         </is>
       </c>
       <c r="S12" s="16" t="inlineStr">
@@ -1260,7 +1232,7 @@
       </c>
       <c r="T12" s="13" t="inlineStr">
         <is>
-          <t>specteks37.ru, ivuniforma.ru</t>
+          <t>files.technoavia.ru, spets.ru</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1240,7 @@
       <c r="A13" s="13" t="inlineStr"/>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Полукомбинезон зимний мужской для защиты от механических воздействий и общих производственных загрязнений</t>
+          <t xml:space="preserve">   Костюм летний мужской сигнальный флуоресцентный (ОПЗ)</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr"/>
@@ -1276,27 +1248,27 @@
       <c r="E13" s="13" t="inlineStr"/>
       <c r="F13" s="13" t="inlineStr"/>
       <c r="G13" s="14" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Комплект</t>
         </is>
       </c>
       <c r="I13" s="15" t="n">
-        <v>7973.42</v>
+        <v>12267.73</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>1828.1375</v>
+        <v>3711.905</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>0.770721033132583</v>
+        <v>0.6974252775370832</v>
       </c>
       <c r="L13" s="15" t="n">
-        <v>159468.4</v>
+        <v>49070.92</v>
       </c>
       <c r="M13" s="15" t="n">
-        <v>36562.75</v>
+        <v>14847.62</v>
       </c>
       <c r="N13" s="14" t="n"/>
       <c r="O13" s="14" t="n"/>
@@ -1304,17 +1276,17 @@
       <c r="Q13" s="13" t="inlineStr"/>
       <c r="R13" s="13" t="inlineStr">
         <is>
-          <t>справочник: Полукомбинезон / брюки зимние</t>
+          <t>медиана опт/прайс 2026: techno-avia.ru 4 731; ivuniforma.ru 1 610; spets.ru 3 027</t>
         </is>
       </c>
       <c r="S13" s="16" t="inlineStr">
         <is>
-          <t>fabrikant-textile.ru</t>
+          <t>files.technoavia.ru</t>
         </is>
       </c>
       <c r="T13" s="13" t="inlineStr">
         <is>
-          <t>spec-standart.ru, trakt.ru</t>
+          <t>ivuniforma.ru, spets.ru</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1294,7 @@
       <c r="A14" s="13" t="inlineStr"/>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Костюм летний мужской сигнальный флуоресцентный (ОПЗ)</t>
+          <t xml:space="preserve">   Костюм зимний мужской сигнальный флуоресцентный (ОПЗ)</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr"/>
@@ -1334,23 +1306,23 @@
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Комплект</t>
         </is>
       </c>
       <c r="I14" s="15" t="n">
-        <v>12267.73</v>
+        <v>15293.39</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>5546.5</v>
+        <v>6892.5</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>0.5478788659352627</v>
+        <v>0.5493150962605413</v>
       </c>
       <c r="L14" s="15" t="n">
-        <v>49070.92</v>
+        <v>61173.56</v>
       </c>
       <c r="M14" s="15" t="n">
-        <v>22186</v>
+        <v>27570</v>
       </c>
       <c r="N14" s="14" t="n"/>
       <c r="O14" s="14" t="n"/>
@@ -1358,21 +1330,25 @@
       <c r="Q14" s="13" t="inlineStr"/>
       <c r="R14" s="13" t="inlineStr">
         <is>
-          <t>Спецобъединение «Рефлект-2» 6 112 −10%</t>
+          <t>медиана опт/прайс 2026: techno-avia.ru 10 676; ivuniforma.ru 4 522; trakt.ru 5 368</t>
         </is>
       </c>
       <c r="S14" s="16" t="inlineStr">
         <is>
-          <t>spets.ru</t>
-        </is>
-      </c>
-      <c r="T14" s="13" t="inlineStr"/>
+          <t>files.technoavia.ru</t>
+        </is>
+      </c>
+      <c r="T14" s="13" t="inlineStr">
+        <is>
+          <t>ivuniforma.ru, trakt.ru</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="13" t="inlineStr"/>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Костюм зимний мужской сигнальный флуоресцентный (ОПЗ)</t>
+          <t xml:space="preserve">   Костюм зимний женский для защиты от нефтепродуктов</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr"/>
@@ -1380,27 +1356,27 @@
       <c r="E15" s="13" t="inlineStr"/>
       <c r="F15" s="13" t="inlineStr"/>
       <c r="G15" s="14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Комплект</t>
         </is>
       </c>
       <c r="I15" s="15" t="n">
-        <v>15293.39</v>
+        <v>32058.76</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>10550</v>
-      </c>
-      <c r="K15" s="17" t="n">
-        <v>0.310159487203295</v>
+        <v>13867.85</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>0.5674240051705056</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>61173.56</v>
+        <v>256470.08</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>42200</v>
+        <v>110942.8</v>
       </c>
       <c r="N15" s="14" t="n"/>
       <c r="O15" s="14" t="n"/>
@@ -1408,21 +1384,25 @@
       <c r="Q15" s="13" t="inlineStr"/>
       <c r="R15" s="13" t="inlineStr">
         <is>
-          <t>Спецобъединение «Рефлект-2» зим. 11 621 −10%</t>
+          <t>медиана опт/прайс 2026: trakt.ru 12 616; spets.ru 14 938</t>
         </is>
       </c>
       <c r="S15" s="16" t="inlineStr">
         <is>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T15" s="13" t="inlineStr">
+        <is>
           <t>spets.ru</t>
         </is>
       </c>
-      <c r="T15" s="13" t="inlineStr"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="13" t="inlineStr"/>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Костюм зимний женский для защиты от нефтепродуктов</t>
+          <t xml:space="preserve">   Костюм зимний мужской для защиты от нефтепродуктов</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr"/>
@@ -1430,27 +1410,27 @@
       <c r="E16" s="13" t="inlineStr"/>
       <c r="F16" s="13" t="inlineStr"/>
       <c r="G16" s="14" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Комплект</t>
         </is>
       </c>
       <c r="I16" s="15" t="n">
         <v>32058.76</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>16044</v>
+        <v>13867.85</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>0.4995439623990447</v>
+        <v>0.5674240051705056</v>
       </c>
       <c r="L16" s="15" t="n">
-        <v>256470.08</v>
+        <v>737351.48</v>
       </c>
       <c r="M16" s="15" t="n">
-        <v>128352</v>
+        <v>318960.55</v>
       </c>
       <c r="N16" s="14" t="n"/>
       <c r="O16" s="14" t="n"/>
@@ -1458,7 +1438,7 @@
       <c r="Q16" s="13" t="inlineStr"/>
       <c r="R16" s="13" t="inlineStr">
         <is>
-          <t>Тракт 11 253 / Спецобъединение 24 199, среднее −10%</t>
+          <t>медиана опт/прайс 2026: trakt.ru 12 616; spets.ru 14 938</t>
         </is>
       </c>
       <c r="S16" s="16" t="inlineStr">
@@ -1476,7 +1456,7 @@
       <c r="A17" s="13" t="inlineStr"/>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Костюм зимний мужской для защиты от нефтепродуктов</t>
+          <t xml:space="preserve">   Костюм летний женский для защиты от нефтепродуктов</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr"/>
@@ -1484,27 +1464,27 @@
       <c r="E17" s="13" t="inlineStr"/>
       <c r="F17" s="13" t="inlineStr"/>
       <c r="G17" s="14" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Комплект</t>
         </is>
       </c>
       <c r="I17" s="15" t="n">
-        <v>32058.76</v>
+        <v>19177.56</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>16044</v>
+        <v>7846.889999999999</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>0.4995439623990447</v>
+        <v>0.5908295945886756</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>737351.48</v>
+        <v>287663.4</v>
       </c>
       <c r="M17" s="15" t="n">
-        <v>369012</v>
+        <v>117703.35</v>
       </c>
       <c r="N17" s="14" t="n"/>
       <c r="O17" s="14" t="n"/>
@@ -1512,7 +1492,7 @@
       <c r="Q17" s="13" t="inlineStr"/>
       <c r="R17" s="13" t="inlineStr">
         <is>
-          <t>Тракт 11 253 / Спецобъединение 24 199, среднее −10%</t>
+          <t>медиана опт/прайс 2026: trakt.ru 6 660; spets.ru 8 894</t>
         </is>
       </c>
       <c r="S17" s="16" t="inlineStr">
@@ -1530,7 +1510,7 @@
       <c r="A18" s="13" t="inlineStr"/>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Костюм летний женский для защиты от нефтепродуктов</t>
+          <t xml:space="preserve">   Костюм летний мужской для защиты от нефтепродуктов</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr"/>
@@ -1538,27 +1518,27 @@
       <c r="E18" s="13" t="inlineStr"/>
       <c r="F18" s="13" t="inlineStr"/>
       <c r="G18" s="14" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="H18" s="13" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Комплект</t>
         </is>
       </c>
       <c r="I18" s="15" t="n">
         <v>19177.56</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>9048</v>
+        <v>7846.889999999999</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>0.528198582092821</v>
+        <v>0.5908295945886756</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>287663.4</v>
+        <v>786279.9600000001</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>135720</v>
+        <v>321722.49</v>
       </c>
       <c r="N18" s="14" t="n"/>
       <c r="O18" s="14" t="n"/>
@@ -1566,7 +1546,7 @@
       <c r="Q18" s="13" t="inlineStr"/>
       <c r="R18" s="13" t="inlineStr">
         <is>
-          <t>Тракт 6 731 / Спецобъединение 13 219, среднее −10%</t>
+          <t>медиана опт/прайс 2026: trakt.ru 6 660; spets.ru 8 894</t>
         </is>
       </c>
       <c r="S18" s="16" t="inlineStr">
@@ -1584,7 +1564,7 @@
       <c r="A19" s="13" t="inlineStr"/>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Костюм летний мужской для защиты от нефтепродуктов</t>
+          <t xml:space="preserve">   Плащ для защиты от воды</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr"/>
@@ -1592,27 +1572,27 @@
       <c r="E19" s="13" t="inlineStr"/>
       <c r="F19" s="13" t="inlineStr"/>
       <c r="G19" s="14" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="H19" s="13" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Штука</t>
         </is>
       </c>
       <c r="I19" s="15" t="n">
-        <v>19177.56</v>
+        <v>2764.97</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>9048</v>
+        <v>1040</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>0.528198582092821</v>
+        <v>0.6238657200620621</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>786279.9600000001</v>
+        <v>135483.53</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>370968</v>
+        <v>50960</v>
       </c>
       <c r="N19" s="14" t="n"/>
       <c r="O19" s="14" t="n"/>
@@ -1620,17 +1600,17 @@
       <c r="Q19" s="13" t="inlineStr"/>
       <c r="R19" s="13" t="inlineStr">
         <is>
-          <t>Тракт 6 731 / Спецобъединение 13 219, среднее −10%</t>
+          <t>медиана опт/прайс 2026: techno-avia.ru 1 239; fabrikant-textile.ru 1 365; trakt.ru 858</t>
         </is>
       </c>
       <c r="S19" s="16" t="inlineStr">
         <is>
-          <t>trakt.ru</t>
+          <t>files.technoavia.ru</t>
         </is>
       </c>
       <c r="T19" s="13" t="inlineStr">
         <is>
-          <t>spets.ru</t>
+          <t>fabrikant-textile.ru, trakt.ru</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1618,7 @@
       <c r="A20" s="13" t="inlineStr"/>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Плащ для защиты от воды</t>
+          <t xml:space="preserve">   Футболка красная</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr"/>
@@ -1646,27 +1626,27 @@
       <c r="E20" s="13" t="inlineStr"/>
       <c r="F20" s="13" t="inlineStr"/>
       <c r="G20" s="14" t="n">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Штука</t>
         </is>
       </c>
       <c r="I20" s="15" t="n">
-        <v>2764.97</v>
+        <v>1379.88</v>
       </c>
       <c r="J20" s="15" t="n">
-        <v>1196</v>
+        <v>493.17</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>0.5674455780713714</v>
+        <v>0.6425993564657796</v>
       </c>
       <c r="L20" s="15" t="n">
-        <v>135483.53</v>
+        <v>154546.56</v>
       </c>
       <c r="M20" s="15" t="n">
-        <v>58604</v>
+        <v>55235.04</v>
       </c>
       <c r="N20" s="14" t="n"/>
       <c r="O20" s="14" t="n"/>
@@ -1674,7 +1654,7 @@
       <c r="Q20" s="13" t="inlineStr"/>
       <c r="R20" s="13" t="inlineStr">
         <is>
-          <t>Тракт 971 / Фабрикант 1 365</t>
+          <t>медиана опт/прайс 2026: trakt.ru 484; techno-avia.ru 486; spets.ru 488</t>
         </is>
       </c>
       <c r="S20" s="16" t="inlineStr">
@@ -1684,7 +1664,7 @@
       </c>
       <c r="T20" s="13" t="inlineStr">
         <is>
-          <t>fabrikant-textile.ru</t>
+          <t>files.technoavia.ru, spets.ru</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1672,7 @@
       <c r="A21" s="13" t="inlineStr"/>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Футболка красная</t>
+          <t xml:space="preserve">   Халат белый мужской</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr"/>
@@ -1700,27 +1680,27 @@
       <c r="E21" s="13" t="inlineStr"/>
       <c r="F21" s="13" t="inlineStr"/>
       <c r="G21" s="14" t="n">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="H21" s="13" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Штука</t>
         </is>
       </c>
       <c r="I21" s="15" t="n">
-        <v>1379.88</v>
+        <v>2862.3</v>
       </c>
       <c r="J21" s="15" t="n">
-        <v>247.5</v>
+        <v>969.1</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0.8206365770936603</v>
+        <v>0.6614261258428537</v>
       </c>
       <c r="L21" s="15" t="n">
-        <v>154546.56</v>
+        <v>111629.7</v>
       </c>
       <c r="M21" s="15" t="n">
-        <v>27720</v>
+        <v>37794.9</v>
       </c>
       <c r="N21" s="14" t="n"/>
       <c r="O21" s="14" t="n"/>
@@ -1728,17 +1708,17 @@
       <c r="Q21" s="13" t="inlineStr"/>
       <c r="R21" s="13" t="inlineStr">
         <is>
-          <t>справочник: Футболка</t>
+          <t>медиана опт/прайс 2026: fabrikant-textile.ru 400; techno-avia.ru 3 277; ivuniforma.ru…</t>
         </is>
       </c>
       <c r="S21" s="16" t="inlineStr">
         <is>
-          <t>productcenter.ru</t>
+          <t>fabrikant-textile.ru</t>
         </is>
       </c>
       <c r="T21" s="13" t="inlineStr">
         <is>
-          <t>files.technoavia.ru, trakt.ru</t>
+          <t>files.technoavia.ru, ivuniforma.ru</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1726,7 @@
       <c r="A22" s="13" t="inlineStr"/>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Халат белый мужской</t>
+          <t xml:space="preserve">   Халат белый женский</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr"/>
@@ -1754,27 +1734,27 @@
       <c r="E22" s="13" t="inlineStr"/>
       <c r="F22" s="13" t="inlineStr"/>
       <c r="G22" s="14" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Штука</t>
         </is>
       </c>
       <c r="I22" s="15" t="n">
         <v>2862.3</v>
       </c>
       <c r="J22" s="15" t="n">
-        <v>635.75</v>
+        <v>969.1</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>0.7778884114173916</v>
+        <v>0.6614261258428537</v>
       </c>
       <c r="L22" s="15" t="n">
-        <v>111629.7</v>
+        <v>88731.3</v>
       </c>
       <c r="M22" s="15" t="n">
-        <v>24794.25</v>
+        <v>30042.1</v>
       </c>
       <c r="N22" s="14" t="n"/>
       <c r="O22" s="14" t="n"/>
@@ -1782,7 +1762,7 @@
       <c r="Q22" s="13" t="inlineStr"/>
       <c r="R22" s="13" t="inlineStr">
         <is>
-          <t>справочник: Халат рабочий</t>
+          <t>медиана опт/прайс 2026: fabrikant-textile.ru 400; techno-avia.ru 3 277; ivuniforma.ru…</t>
         </is>
       </c>
       <c r="S22" s="16" t="inlineStr">
@@ -1792,7 +1772,7 @@
       </c>
       <c r="T22" s="13" t="inlineStr">
         <is>
-          <t>ivuniforma.ru, files.technoavia.ru</t>
+          <t>files.technoavia.ru, ivuniforma.ru</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1780,7 @@
       <c r="A23" s="13" t="inlineStr"/>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Халат белый женский</t>
+          <t xml:space="preserve">   Халат синий мужской</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr"/>
@@ -1808,27 +1788,27 @@
       <c r="E23" s="13" t="inlineStr"/>
       <c r="F23" s="13" t="inlineStr"/>
       <c r="G23" s="14" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H23" s="13" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>Штука</t>
         </is>
       </c>
       <c r="I23" s="15" t="n">
-        <v>2862.3</v>
+        <v>3093.44</v>
       </c>
       <c r="J23" s="15" t="n">
-        <v>635.75</v>
+        <v>969.1</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>0.7778884114173916</v>
+        <v>0.6867241646839765</v>
       </c>
       <c r="L23" s="15" t="n">
-        <v>88731.3</v>
+        <v>30934.4</v>
       </c>
       <c r="M23" s="15" t="n">
-        <v>19708.25</v>
+        <v>9691</v>
       </c>
       <c r="N23" s="14" t="n"/>
       <c r="O23" s="14" t="n"/>
@@ -1836,7 +1816,7 @@
       <c r="Q23" s="13" t="inlineStr"/>
       <c r="R23" s="13" t="inlineStr">
         <is>
-          <t>справочник: Халат рабочий</t>
+          <t>медиана опт/прайс 2026: fabrikant-textile.ru 400; techno-avia.ru 3 277; ivuniforma.ru…</t>
         </is>
       </c>
       <c r="S23" s="16" t="inlineStr">
@@ -1846,131 +1826,125 @@
       </c>
       <c r="T23" s="13" t="inlineStr">
         <is>
-          <t>ivuniforma.ru, files.technoavia.ru</t>
+          <t>files.technoavia.ru, ivuniforma.ru</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="13" t="inlineStr"/>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Халат синий мужской</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr"/>
-      <c r="D24" s="13" t="inlineStr"/>
-      <c r="E24" s="13" t="inlineStr"/>
-      <c r="F24" s="13" t="inlineStr"/>
-      <c r="G24" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="H24" s="13" t="inlineStr">
-        <is>
-          <t>шт/компл</t>
-        </is>
-      </c>
-      <c r="I24" s="15" t="n">
-        <v>3093.44</v>
-      </c>
-      <c r="J24" s="15" t="n">
-        <v>635.75</v>
-      </c>
-      <c r="K24" s="11" t="n">
-        <v>0.7944844574325023</v>
-      </c>
-      <c r="L24" s="15" t="n">
-        <v>30934.4</v>
-      </c>
-      <c r="M24" s="15" t="n">
-        <v>6357.5</v>
-      </c>
-      <c r="N24" s="14" t="n"/>
-      <c r="O24" s="14" t="n"/>
-      <c r="P24" s="14" t="n"/>
-      <c r="Q24" s="13" t="inlineStr"/>
-      <c r="R24" s="13" t="inlineStr">
-        <is>
-          <t>справочник: Халат рабочий</t>
-        </is>
-      </c>
-      <c r="S24" s="16" t="inlineStr">
+      <c r="A24" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Спецодежда: ГУП «Салаватводоканал»</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>32616453117</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>открыть</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>223-ФЗ запрос предложений</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>21.10 09:00</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="8" t="inlineStr"/>
+      <c r="I24" s="9" t="n"/>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="10" t="n"/>
+      <c r="L24" s="9" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="M24" s="9" t="n">
+        <v>681523</v>
+      </c>
+      <c r="N24" s="11" t="n">
+        <v>0.5456515118173512</v>
+      </c>
+      <c r="O24" s="12" t="n">
+        <v>539980</v>
+      </c>
+      <c r="P24" s="10" t="n">
+        <v>0.5269294629781853</v>
+      </c>
+      <c r="Q24" s="8" t="inlineStr">
+        <is>
+          <t>не указано</t>
+        </is>
+      </c>
+      <c r="R24" s="8" t="inlineStr">
+        <is>
+          <t>по позициям ниже</t>
+        </is>
+      </c>
+      <c r="S24" s="4" t="n"/>
+      <c r="T24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="13" t="inlineStr"/>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Костюм женский для защиты от пониженных температур, в т.ч. Куртка и полукомбинезон</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr"/>
+      <c r="D25" s="13" t="inlineStr"/>
+      <c r="E25" s="13" t="inlineStr"/>
+      <c r="F25" s="13" t="inlineStr"/>
+      <c r="G25" s="14" t="n"/>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v>10645</v>
+      </c>
+      <c r="J25" s="15" t="n">
+        <v>5091</v>
+      </c>
+      <c r="K25" s="11" t="n">
+        <v>0.5217472992015031</v>
+      </c>
+      <c r="L25" s="15" t="n"/>
+      <c r="M25" s="15" t="n"/>
+      <c r="N25" s="14" t="n"/>
+      <c r="O25" s="14" t="n"/>
+      <c r="P25" s="14" t="n"/>
+      <c r="Q25" s="13" t="inlineStr"/>
+      <c r="R25" s="13" t="inlineStr">
+        <is>
+          <t>ваша себестоимость; рынок 2026: fabrikant-textile.ru 1 845; techno-avia.ru 7 194; spe…</t>
+        </is>
+      </c>
+      <c r="S25" s="16" t="inlineStr">
         <is>
           <t>fabrikant-textile.ru</t>
         </is>
       </c>
-      <c r="T24" s="13" t="inlineStr">
-        <is>
-          <t>ivuniforma.ru, files.technoavia.ru</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Спецодежда: ГУП «Салаватводоканал»</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>32616453117</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>223-ФЗ запрос предложений</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>21.10 09:00</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="n"/>
-      <c r="H25" s="8" t="inlineStr"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n"/>
-      <c r="K25" s="10" t="n"/>
-      <c r="L25" s="9" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="M25" s="9" t="n">
-        <v>785120</v>
-      </c>
-      <c r="N25" s="11" t="n">
-        <v>0.4765869115363072</v>
-      </c>
-      <c r="O25" s="12" t="n">
-        <v>449028</v>
-      </c>
-      <c r="P25" s="10" t="n">
-        <v>0.4550189616913052</v>
-      </c>
-      <c r="Q25" s="8" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="R25" s="8" t="inlineStr">
-        <is>
-          <t>по позициям ниже</t>
-        </is>
-      </c>
-      <c r="S25" s="4" t="n"/>
-      <c r="T25" s="4" t="n"/>
+      <c r="T25" s="13" t="inlineStr">
+        <is>
+          <t>files.technoavia.ru, specteks37.ru</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="13" t="inlineStr"/>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Костюм женский для защиты от пониженных температур, в т.ч. Куртка и полукомбинезон</t>
+          <t xml:space="preserve">   Куртка мужская для защиты от пониженных температур</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr"/>
@@ -1980,17 +1954,17 @@
       <c r="G26" s="14" t="n"/>
       <c r="H26" s="13" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="I26" s="15" t="n">
-        <v>10645</v>
+        <v>4410</v>
       </c>
       <c r="J26" s="15" t="n">
-        <v>5091</v>
+        <v>2551.1</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>0.5217472992015031</v>
+        <v>0.4215192743764172</v>
       </c>
       <c r="L26" s="15" t="n"/>
       <c r="M26" s="15" t="n"/>
@@ -2000,7 +1974,7 @@
       <c r="Q26" s="13" t="inlineStr"/>
       <c r="R26" s="13" t="inlineStr">
         <is>
-          <t>справочник: Костюм зимний рабочий (I–III пояс</t>
+          <t>медиана опт/прайс 2026: fabrikant-textile.ru 1 125; techno-avia.ru 4 567; specteks37.…</t>
         </is>
       </c>
       <c r="S26" s="16" t="inlineStr">
@@ -2010,7 +1984,7 @@
       </c>
       <c r="T26" s="13" t="inlineStr">
         <is>
-          <t>spec-standart.ru, specteks37.ru</t>
+          <t>files.technoavia.ru, specteks37.ru</t>
         </is>
       </c>
     </row>
@@ -2018,7 +1992,7 @@
       <c r="A27" s="13" t="inlineStr"/>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Куртка мужская для защиты от пониженных температур</t>
+          <t xml:space="preserve">   Полукомбинезон мужской зимний</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr"/>
@@ -2028,17 +2002,17 @@
       <c r="G27" s="14" t="n"/>
       <c r="H27" s="13" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="I27" s="15" t="n">
-        <v>4410</v>
+        <v>3723.33</v>
       </c>
       <c r="J27" s="15" t="n">
-        <v>2203.333333333333</v>
+        <v>1225</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>0.5003779289493576</v>
+        <v>0.6709934386691483</v>
       </c>
       <c r="L27" s="15" t="n"/>
       <c r="M27" s="15" t="n"/>
@@ -2048,7 +2022,7 @@
       <c r="Q27" s="13" t="inlineStr"/>
       <c r="R27" s="13" t="inlineStr">
         <is>
-          <t>справочник: Куртка утепленная</t>
+          <t>медиана опт/прайс 2026: fabrikant-textile.ru 720; techno-avia.ru 2 828; spets.ru 1 019</t>
         </is>
       </c>
       <c r="S27" s="16" t="inlineStr">
@@ -2058,7 +2032,7 @@
       </c>
       <c r="T27" s="13" t="inlineStr">
         <is>
-          <t>specteks37.ru, ivuniforma.ru</t>
+          <t>files.technoavia.ru, spets.ru</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2040,7 @@
       <c r="A28" s="13" t="inlineStr"/>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Полукомбинезон мужской зимний</t>
+          <t xml:space="preserve">   Куртка мужская для защиты от пониженных температур</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr"/>
@@ -2076,17 +2050,17 @@
       <c r="G28" s="14" t="n"/>
       <c r="H28" s="13" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="I28" s="15" t="n">
-        <v>3723.33</v>
+        <v>7856.33</v>
       </c>
       <c r="J28" s="15" t="n">
-        <v>1828.1375</v>
+        <v>2551.1</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>0.5090047081510368</v>
+        <v>0.6752809517930127</v>
       </c>
       <c r="L28" s="15" t="n"/>
       <c r="M28" s="15" t="n"/>
@@ -2096,7 +2070,7 @@
       <c r="Q28" s="13" t="inlineStr"/>
       <c r="R28" s="13" t="inlineStr">
         <is>
-          <t>справочник: Полукомбинезон / брюки зимние</t>
+          <t>медиана опт/прайс 2026: fabrikant-textile.ru 1 125; techno-avia.ru 4 567; specteks37.…</t>
         </is>
       </c>
       <c r="S28" s="16" t="inlineStr">
@@ -2106,7 +2080,7 @@
       </c>
       <c r="T28" s="13" t="inlineStr">
         <is>
-          <t>spec-standart.ru, trakt.ru</t>
+          <t>files.technoavia.ru, specteks37.ru</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2088,7 @@
       <c r="A29" s="13" t="inlineStr"/>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Куртка мужская для защиты от пониженных температур</t>
+          <t xml:space="preserve">   Брюки мужские от защиты от пониженных температур</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr"/>
@@ -2124,17 +2098,17 @@
       <c r="G29" s="14" t="n"/>
       <c r="H29" s="13" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="I29" s="15" t="n">
-        <v>7856.33</v>
+        <v>5011.33</v>
       </c>
       <c r="J29" s="15" t="n">
-        <v>2203.333333333333</v>
+        <v>1225</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>0.719546743411576</v>
+        <v>0.7555539148289975</v>
       </c>
       <c r="L29" s="15" t="n"/>
       <c r="M29" s="15" t="n"/>
@@ -2144,7 +2118,7 @@
       <c r="Q29" s="13" t="inlineStr"/>
       <c r="R29" s="13" t="inlineStr">
         <is>
-          <t>справочник: Куртка утепленная</t>
+          <t>медиана опт/прайс 2026: fabrikant-textile.ru 720; techno-avia.ru 2 828; spets.ru 1 019</t>
         </is>
       </c>
       <c r="S29" s="16" t="inlineStr">
@@ -2154,7 +2128,7 @@
       </c>
       <c r="T29" s="13" t="inlineStr">
         <is>
-          <t>specteks37.ru, ivuniforma.ru</t>
+          <t>files.technoavia.ru, spets.ru</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2136,7 @@
       <c r="A30" s="13" t="inlineStr"/>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Брюки мужские от защиты от пониженных температур</t>
+          <t xml:space="preserve">   Куртка женская для защиты от пониженных температур</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr"/>
@@ -2172,17 +2146,17 @@
       <c r="G30" s="14" t="n"/>
       <c r="H30" s="13" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="I30" s="15" t="n">
-        <v>5011.33</v>
+        <v>4727.67</v>
       </c>
       <c r="J30" s="15" t="n">
-        <v>1828.1375</v>
+        <v>2551.1</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>0.635199138751589</v>
+        <v>0.4603895787988587</v>
       </c>
       <c r="L30" s="15" t="n"/>
       <c r="M30" s="15" t="n"/>
@@ -2192,7 +2166,7 @@
       <c r="Q30" s="13" t="inlineStr"/>
       <c r="R30" s="13" t="inlineStr">
         <is>
-          <t>справочник: Полукомбинезон / брюки зимние</t>
+          <t>медиана опт/прайс 2026: fabrikant-textile.ru 1 125; techno-avia.ru 4 567; specteks37.…</t>
         </is>
       </c>
       <c r="S30" s="16" t="inlineStr">
@@ -2202,7 +2176,7 @@
       </c>
       <c r="T30" s="13" t="inlineStr">
         <is>
-          <t>spec-standart.ru, trakt.ru</t>
+          <t>files.technoavia.ru, specteks37.ru</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2184,7 @@
       <c r="A31" s="13" t="inlineStr"/>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Куртка женская для защиты от пониженных температур</t>
+          <t xml:space="preserve">   Брюки женские от защиты от пониженных температур</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr"/>
@@ -2220,17 +2194,17 @@
       <c r="G31" s="14" t="n"/>
       <c r="H31" s="13" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="I31" s="15" t="n">
-        <v>4727.67</v>
+        <v>3020</v>
       </c>
       <c r="J31" s="15" t="n">
-        <v>2203.333333333333</v>
+        <v>1225</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0.5339494225837816</v>
+        <v>0.5943708609271523</v>
       </c>
       <c r="L31" s="15" t="n"/>
       <c r="M31" s="15" t="n"/>
@@ -2240,7 +2214,7 @@
       <c r="Q31" s="13" t="inlineStr"/>
       <c r="R31" s="13" t="inlineStr">
         <is>
-          <t>справочник: Куртка утепленная</t>
+          <t>медиана опт/прайс 2026: fabrikant-textile.ru 720; techno-avia.ru 2 828; spets.ru 1 019</t>
         </is>
       </c>
       <c r="S31" s="16" t="inlineStr">
@@ -2250,7 +2224,7 @@
       </c>
       <c r="T31" s="13" t="inlineStr">
         <is>
-          <t>specteks37.ru, ivuniforma.ru</t>
+          <t>files.technoavia.ru, spets.ru</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2232,7 @@
       <c r="A32" s="13" t="inlineStr"/>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Брюки женские от защиты от пониженных температур</t>
+          <t xml:space="preserve">   Костюм мужской для защиты от кислот и щелочей, пониженных температур, от воздействия статического электричества</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr"/>
@@ -2268,17 +2242,17 @@
       <c r="G32" s="14" t="n"/>
       <c r="H32" s="13" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="I32" s="15" t="n">
-        <v>3020</v>
+        <v>14527</v>
       </c>
       <c r="J32" s="15" t="n">
-        <v>1828.1375</v>
-      </c>
-      <c r="K32" s="17" t="n">
-        <v>0.3946564569536424</v>
+        <v>4783.440000000001</v>
+      </c>
+      <c r="K32" s="11" t="n">
+        <v>0.6707207269222826</v>
       </c>
       <c r="L32" s="15" t="n"/>
       <c r="M32" s="15" t="n"/>
@@ -2288,17 +2262,17 @@
       <c r="Q32" s="13" t="inlineStr"/>
       <c r="R32" s="13" t="inlineStr">
         <is>
-          <t>справочник: Полукомбинезон / брюки зимние</t>
+          <t>медиана опт/прайс 2026: techno-avia.ru 6 306; ivuniforma.ru 2 660; spets.ru 3 184</t>
         </is>
       </c>
       <c r="S32" s="16" t="inlineStr">
         <is>
-          <t>fabrikant-textile.ru</t>
+          <t>files.technoavia.ru</t>
         </is>
       </c>
       <c r="T32" s="13" t="inlineStr">
         <is>
-          <t>spec-standart.ru, trakt.ru</t>
+          <t>ivuniforma.ru, spets.ru</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2280,7 @@
       <c r="A33" s="13" t="inlineStr"/>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Костюм мужской для защиты от кислот и щелочей, пониженных температур, от воздействия статического электричества</t>
+          <t xml:space="preserve">   Костюм сварщика зимний комбинированный со спилком</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr"/>
@@ -2316,17 +2290,17 @@
       <c r="G33" s="14" t="n"/>
       <c r="H33" s="13" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="I33" s="15" t="n">
-        <v>14527</v>
+        <v>12543.67</v>
       </c>
       <c r="J33" s="15" t="n">
-        <v>6299</v>
+        <v>5989.67</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0.5663936118950919</v>
+        <v>0.5224946128206498</v>
       </c>
       <c r="L33" s="15" t="n"/>
       <c r="M33" s="15" t="n"/>
@@ -2336,21 +2310,25 @@
       <c r="Q33" s="13" t="inlineStr"/>
       <c r="R33" s="13" t="inlineStr">
         <is>
-          <t>Тракт, костюм КЩС утепл. 6 215</t>
+          <t>медиана опт/прайс 2026: spets.ru 3 562; techno-avia.ru 3 801; trakt.ru 5 511</t>
         </is>
       </c>
       <c r="S33" s="16" t="inlineStr">
         <is>
-          <t>trakt.ru</t>
-        </is>
-      </c>
-      <c r="T33" s="13" t="inlineStr"/>
+          <t>spets.ru</t>
+        </is>
+      </c>
+      <c r="T33" s="13" t="inlineStr">
+        <is>
+          <t>files.technoavia.ru, trakt.ru</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="13" t="inlineStr"/>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Костюм сварщика зимний комбинированный со спилком</t>
+          <t xml:space="preserve">   Костюм сигнальный для защиты от пониженных температур</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr"/>
@@ -2360,17 +2338,17 @@
       <c r="G34" s="14" t="n"/>
       <c r="H34" s="13" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="I34" s="15" t="n">
-        <v>12543.67</v>
+        <v>9907</v>
       </c>
       <c r="J34" s="15" t="n">
-        <v>5785.35</v>
-      </c>
-      <c r="K34" s="11" t="n">
-        <v>0.5387833066399227</v>
+        <v>6892.5</v>
+      </c>
+      <c r="K34" s="17" t="n">
+        <v>0.3042798021600888</v>
       </c>
       <c r="L34" s="15" t="n"/>
       <c r="M34" s="15" t="n"/>
@@ -2380,17 +2358,17 @@
       <c r="Q34" s="13" t="inlineStr"/>
       <c r="R34" s="13" t="inlineStr">
         <is>
-          <t>справочник: Костюм сварщика</t>
+          <t>медиана опт/прайс 2026: techno-avia.ru 10 676; ivuniforma.ru 4 522; trakt.ru 5 368</t>
         </is>
       </c>
       <c r="S34" s="16" t="inlineStr">
         <is>
-          <t>ivuniforma.ru</t>
+          <t>files.technoavia.ru</t>
         </is>
       </c>
       <c r="T34" s="13" t="inlineStr">
         <is>
-          <t>files.technoavia.ru, trakt.ru</t>
+          <t>ivuniforma.ru, trakt.ru</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2376,7 @@
       <c r="A35" s="13" t="inlineStr"/>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Костюм сигнальный для защиты от пониженных температур</t>
+          <t xml:space="preserve">   Жилет утепленный</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr"/>
@@ -2408,17 +2386,17 @@
       <c r="G35" s="14" t="n"/>
       <c r="H35" s="13" t="inlineStr">
         <is>
-          <t>шт/компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="I35" s="15" t="n">
-        <v>9907</v>
+        <v>2200</v>
       </c>
       <c r="J35" s="15" t="n">
-        <v>10550</v>
-      </c>
-      <c r="K35" s="18" t="n">
-        <v>-0.06490360351266782</v>
+        <v>1613.855</v>
+      </c>
+      <c r="K35" s="17" t="n">
+        <v>0.2664295454545454</v>
       </c>
       <c r="L35" s="15" t="n"/>
       <c r="M35" s="15" t="n"/>
@@ -2428,61 +2406,99 @@
       <c r="Q35" s="13" t="inlineStr"/>
       <c r="R35" s="13" t="inlineStr">
         <is>
-          <t>Спецобъединение «Рефлект-2» зим. 11 621 −10%</t>
+          <t>медиана опт/прайс 2026: techno-avia.ru 1 313; ivuniforma.ru 875; trakt.ru 1 866</t>
         </is>
       </c>
       <c r="S35" s="16" t="inlineStr">
         <is>
-          <t>spets.ru</t>
-        </is>
-      </c>
-      <c r="T35" s="13" t="inlineStr"/>
+          <t>files.technoavia.ru</t>
+        </is>
+      </c>
+      <c r="T35" s="13" t="inlineStr">
+        <is>
+          <t>ivuniforma.ru, trakt.ru</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="13" t="inlineStr"/>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Жилет утепленный</t>
-        </is>
-      </c>
-      <c r="C36" s="13" t="inlineStr"/>
-      <c r="D36" s="13" t="inlineStr"/>
-      <c r="E36" s="13" t="inlineStr"/>
-      <c r="F36" s="13" t="inlineStr"/>
-      <c r="G36" s="14" t="n"/>
-      <c r="H36" s="13" t="inlineStr">
-        <is>
-          <t>шт/компл</t>
-        </is>
-      </c>
-      <c r="I36" s="15" t="n">
-        <v>2200</v>
-      </c>
-      <c r="J36" s="15" t="n">
-        <v>1305.5</v>
-      </c>
-      <c r="K36" s="11" t="n">
-        <v>0.4065909090909091</v>
-      </c>
-      <c r="L36" s="15" t="n"/>
-      <c r="M36" s="15" t="n"/>
-      <c r="N36" s="14" t="n"/>
-      <c r="O36" s="14" t="n"/>
-      <c r="P36" s="14" t="n"/>
-      <c r="Q36" s="13" t="inlineStr"/>
-      <c r="R36" s="13" t="inlineStr">
-        <is>
-          <t>справочник: Жилет утепленный</t>
-        </is>
-      </c>
-      <c r="S36" s="16" t="inlineStr">
-        <is>
-          <t>ivuniforma.ru</t>
-        </is>
-      </c>
-      <c r="T36" s="13" t="inlineStr">
-        <is>
-          <t>trakt.ru, spets.ru</t>
+      <c r="A36" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>ПГР: ГАУК «Мосгортур», Москва</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>32616449090</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>открыть</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>223-ФЗ запрос котировок</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>19.10 10:00</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="n">
+        <v>54490</v>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>23435.59322033898</v>
+      </c>
+      <c r="K36" s="10" t="n">
+        <v>0.5699101996634431</v>
+      </c>
+      <c r="L36" s="9" t="n">
+        <v>1285964</v>
+      </c>
+      <c r="M36" s="9" t="n">
+        <v>553080</v>
+      </c>
+      <c r="N36" s="11" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="O36" s="12" t="n">
+        <v>436102</v>
+      </c>
+      <c r="P36" s="10" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q36" s="8" t="inlineStr">
+        <is>
+          <t>— / 3%</t>
+        </is>
+      </c>
+      <c r="R36" s="8" t="inlineStr">
+        <is>
+          <t>прайс «А-Стандарт» −20/−25 °C 2026: 19 000–22 000 ₽/т (masterkrowli, grunt-market), B…</t>
+        </is>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>masterkrowli.ru</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>grunt-market.ru, bionord.store</t>
         </is>
       </c>
     </row>
@@ -2492,12 +2508,12 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>ПГР: ГАУК «Мосгортур», Москва</t>
+          <t>Соль: МКУ «Дзержинка», Новосибирск</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>32616449090</t>
+          <t>0851300006226000106</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
@@ -2507,16 +2523,16 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>223-ФЗ запрос котировок</t>
+          <t>44-ФЗ запрос котировок</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>19.10 10:00</t>
+          <t>16.10 05:00</t>
         </is>
       </c>
       <c r="G37" s="4" t="n">
-        <v>23.6</v>
+        <v>400</v>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
@@ -2524,45 +2540,49 @@
         </is>
       </c>
       <c r="I37" s="9" t="n">
-        <v>54490</v>
+        <v>11000</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>23435.59322033898</v>
+        <v>8200</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>0.5699101996634431</v>
+        <v>0.2545454545454545</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>1285964</v>
+        <v>4400000</v>
       </c>
       <c r="M37" s="9" t="n">
-        <v>553080</v>
-      </c>
-      <c r="N37" s="11" t="n">
-        <v>0.57</v>
+        <v>3280000</v>
+      </c>
+      <c r="N37" s="17" t="n">
+        <v>0.2545454545454545</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>436102</v>
+        <v>273908</v>
       </c>
       <c r="P37" s="10" t="n">
-        <v>0.55</v>
+        <v>0.2238279837705378</v>
       </c>
       <c r="Q37" s="8" t="inlineStr">
         <is>
-          <t>— / 3%</t>
+          <t>1% / 5%</t>
         </is>
       </c>
       <c r="R37" s="8" t="inlineStr">
         <is>
-          <t>прайс «А-Стандарт» −25 °C 22 800 ₽/т + доставка</t>
+          <t>Новосибирск: 7 900 ₽/т от 69 т МКР (Полевской Мрамор, отгрузка с Урала) + местная дос…</t>
         </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>bicotender.ru</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr"/>
+          <t>polevskoi-mramor.com</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>smola38.ru</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="4" t="n">
@@ -2570,12 +2590,12 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Соль ⚠ &lt;9 000 ₽/т: МКУ УЖКХ, Струнино</t>
+          <t>Арматура: ПАО «Т Плюс», Н.Новгород</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>0128600006826000407</t>
+          <t>32616442935</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
@@ -2585,64 +2605,64 @@
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>44-ФЗ запрос котировок</t>
+          <t>223-ФЗ иной способ (не аукцион)</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>19.10</t>
+          <t>16.10 14:00</t>
         </is>
       </c>
       <c r="G38" s="4" t="n">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>т</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="I38" s="9" t="n">
-        <v>8950</v>
+        <v>14831.3937007874</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>5060</v>
+        <v>10031.03937007874</v>
       </c>
       <c r="K38" s="10" t="n">
-        <v>0.4346368715083799</v>
+        <v>0.3236617156521041</v>
       </c>
       <c r="L38" s="9" t="n">
-        <v>1342500</v>
+        <v>1883587</v>
       </c>
       <c r="M38" s="9" t="n">
-        <v>759000</v>
-      </c>
-      <c r="N38" s="11" t="n">
-        <v>0.4346368715083799</v>
+        <v>1273942</v>
+      </c>
+      <c r="N38" s="17" t="n">
+        <v>0.32</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>295836</v>
+        <v>247436</v>
       </c>
       <c r="P38" s="10" t="n">
-        <v>0.4113403130762793</v>
+        <v>0.3</v>
       </c>
       <c r="Q38" s="8" t="inlineStr">
         <is>
-          <t>1% / 5%</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="R38" s="8" t="inlineStr">
         <is>
-          <t>средняя рыночная с доставкой: завод вагоном / склад авто (SALT_STRATEGY_1410</t>
+          <t>оценка по дилерским прайсам (цен по позициям нет</t>
         </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>esolk.ru</t>
+          <t>specarmatura.ru</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>nsmgr.ru, sknerud.ru, vektor-e.ru</t>
+          <t>dn.ru</t>
         </is>
       </c>
     </row>
@@ -2652,12 +2672,12 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Арматура: ПАО «Т Плюс», Н.Новгород</t>
+          <t>Спецодежда (коммерч.): ООО «Биннофарм Групп» — пул поставщиков</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>32616442935</t>
+          <t>4634447</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
@@ -2667,204 +2687,146 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>223-ФЗ иной способ (не аукцион)</t>
+          <t>Коммерческий запрос предложений</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>16.10 14:00</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>127</v>
-      </c>
-      <c r="H39" s="8" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="I39" s="9" t="n">
-        <v>14831.3937007874</v>
-      </c>
-      <c r="J39" s="9" t="n">
-        <v>10031.03937007874</v>
-      </c>
-      <c r="K39" s="10" t="n">
-        <v>0.3236617156521041</v>
-      </c>
-      <c r="L39" s="9" t="n">
-        <v>1883587</v>
-      </c>
+          <t>26.10 12:00</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n"/>
+      <c r="H39" s="8" t="inlineStr"/>
+      <c r="I39" s="9" t="n"/>
+      <c r="J39" s="9" t="n"/>
+      <c r="K39" s="10" t="n"/>
+      <c r="L39" s="9" t="n"/>
       <c r="M39" s="9" t="n">
-        <v>1273942</v>
+        <v>1209448</v>
       </c>
       <c r="N39" s="17" t="n">
-        <v>0.32</v>
+        <v>0.25</v>
       </c>
       <c r="O39" s="12" t="n">
-        <v>247436</v>
+        <v>202731</v>
       </c>
       <c r="P39" s="10" t="n">
-        <v>0.3</v>
+        <v>0.2190952275740168</v>
       </c>
       <c r="Q39" s="8" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>—</t>
         </is>
       </c>
       <c r="R39" s="8" t="inlineStr">
         <is>
-          <t>оценка по дилерским прайсам (цен по позициям нет</t>
-        </is>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>specarmatura.ru</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>dn.ru</t>
-        </is>
-      </c>
+          <t>по позициям ниже</t>
+        </is>
+      </c>
+      <c r="S39" s="4" t="n"/>
+      <c r="T39" s="4" t="n"/>
     </row>
     <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>Трубы ППУ: МУП «Уфимские инженерные сети»</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>32616450774</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>223-ФЗ иной способ (не аукцион)</t>
-        </is>
-      </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t>20.10 12:00</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="I40" s="9" t="n">
-        <v>71094.33333333333</v>
-      </c>
-      <c r="J40" s="9" t="n">
-        <v>41495.44444444445</v>
-      </c>
-      <c r="K40" s="10" t="n">
-        <v>0.416332603473632</v>
-      </c>
-      <c r="L40" s="9" t="n">
-        <v>639849</v>
-      </c>
-      <c r="M40" s="9" t="n">
-        <v>373459</v>
-      </c>
-      <c r="N40" s="11" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="O40" s="12" t="n">
-        <v>189886</v>
-      </c>
-      <c r="P40" s="10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q40" s="8" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="R40" s="8" t="inlineStr">
-        <is>
-          <t>оценка по аналогам</t>
-        </is>
-      </c>
-      <c r="S40" s="8" t="inlineStr">
-        <is>
-          <t>нет открытой цены — оценка</t>
-        </is>
-      </c>
-      <c r="T40" s="4" t="n"/>
+      <c r="A40" s="13" t="inlineStr"/>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Халат х/б (бязь)</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr"/>
+      <c r="D40" s="13" t="inlineStr"/>
+      <c r="E40" s="13" t="inlineStr"/>
+      <c r="F40" s="13" t="inlineStr"/>
+      <c r="G40" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="H40" s="13" t="inlineStr">
+        <is>
+          <t>шт/пар/компл</t>
+        </is>
+      </c>
+      <c r="I40" s="15" t="n"/>
+      <c r="J40" s="15" t="n">
+        <v>959.1</v>
+      </c>
+      <c r="K40" s="18" t="n"/>
+      <c r="L40" s="15" t="n"/>
+      <c r="M40" s="15" t="n">
+        <v>287730</v>
+      </c>
+      <c r="N40" s="14" t="n"/>
+      <c r="O40" s="14" t="n"/>
+      <c r="P40" s="14" t="n"/>
+      <c r="Q40" s="13" t="inlineStr"/>
+      <c r="R40" s="13" t="inlineStr">
+        <is>
+          <t>медиана опт/прайс 2026: fabrikant-textile.ru 400; techno-avia.ru 3 277; ivuniforma.ru…</t>
+        </is>
+      </c>
+      <c r="S40" s="16" t="inlineStr">
+        <is>
+          <t>fabrikant-textile.ru</t>
+        </is>
+      </c>
+      <c r="T40" s="13" t="inlineStr">
+        <is>
+          <t>files.technoavia.ru, ivuniforma.ru</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>Спецодежда (коммерч.): ООО «Биннофарм Групп» — пул поставщиков</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>4634447</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>Коммерческий запрос предложений</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>26.10 12:00</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="n"/>
-      <c r="H41" s="8" t="inlineStr"/>
-      <c r="I41" s="9" t="n"/>
-      <c r="J41" s="9" t="n"/>
-      <c r="K41" s="10" t="n"/>
-      <c r="L41" s="9" t="n"/>
-      <c r="M41" s="9" t="n"/>
-      <c r="N41" s="10" t="n"/>
-      <c r="O41" s="12" t="n">
-        <v>116467</v>
-      </c>
-      <c r="P41" s="10" t="n"/>
-      <c r="Q41" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R41" s="8" t="inlineStr">
-        <is>
-          <t>по позициям ниже</t>
-        </is>
-      </c>
-      <c r="S41" s="4" t="n"/>
-      <c r="T41" s="4" t="n"/>
+      <c r="A41" s="13" t="inlineStr"/>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Костюм для защиты от общих загрязнений и мех. воздействий (антистатический, 2 класс)</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr"/>
+      <c r="D41" s="13" t="inlineStr"/>
+      <c r="E41" s="13" t="inlineStr"/>
+      <c r="F41" s="13" t="inlineStr"/>
+      <c r="G41" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="H41" s="13" t="inlineStr">
+        <is>
+          <t>шт/пар/компл</t>
+        </is>
+      </c>
+      <c r="I41" s="15" t="n"/>
+      <c r="J41" s="15" t="n">
+        <v>3518</v>
+      </c>
+      <c r="K41" s="18" t="n"/>
+      <c r="L41" s="15" t="n"/>
+      <c r="M41" s="15" t="n">
+        <v>703600</v>
+      </c>
+      <c r="N41" s="14" t="n"/>
+      <c r="O41" s="14" t="n"/>
+      <c r="P41" s="14" t="n"/>
+      <c r="Q41" s="13" t="inlineStr"/>
+      <c r="R41" s="13" t="inlineStr">
+        <is>
+          <t>ваша себестоимость; рынок 2026: fabrikant-textile.ru 495; fabrikant-textile.ru 850; t…</t>
+        </is>
+      </c>
+      <c r="S41" s="16" t="inlineStr">
+        <is>
+          <t>fabrikant-textile.ru</t>
+        </is>
+      </c>
+      <c r="T41" s="13" t="inlineStr">
+        <is>
+          <t>fabrikant-textile.ru, files.technoavia.ru</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="13" t="inlineStr"/>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Халат х/б (бязь)</t>
+          <t xml:space="preserve">   Футболка х/б</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr"/>
@@ -2872,7 +2834,7 @@
       <c r="E42" s="13" t="inlineStr"/>
       <c r="F42" s="13" t="inlineStr"/>
       <c r="G42" s="14" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H42" s="13" t="inlineStr">
         <is>
@@ -2881,12 +2843,12 @@
       </c>
       <c r="I42" s="15" t="n"/>
       <c r="J42" s="15" t="n">
-        <v>1144.5</v>
-      </c>
-      <c r="K42" s="19" t="n"/>
+        <v>489.17</v>
+      </c>
+      <c r="K42" s="18" t="n"/>
       <c r="L42" s="15" t="n"/>
       <c r="M42" s="15" t="n">
-        <v>343350</v>
+        <v>97834</v>
       </c>
       <c r="N42" s="14" t="n"/>
       <c r="O42" s="14" t="n"/>
@@ -2894,21 +2856,25 @@
       <c r="Q42" s="13" t="inlineStr"/>
       <c r="R42" s="13" t="inlineStr">
         <is>
-          <t>арт. 3.290 1 091.64 ₽</t>
+          <t>медиана опт/прайс 2026: trakt.ru 484; techno-avia.ru 486; spets.ru 488</t>
         </is>
       </c>
       <c r="S42" s="16" t="inlineStr">
         <is>
-          <t>files.technoavia.ru</t>
-        </is>
-      </c>
-      <c r="T42" s="13" t="inlineStr"/>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T42" s="13" t="inlineStr">
+        <is>
+          <t>files.technoavia.ru, spets.ru</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="13" t="inlineStr"/>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Костюм для защиты от общих загрязнений и мех. воздействий (антистатический, 2 класс)</t>
+          <t xml:space="preserve">   Ботинки кожаные с МП</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr"/>
@@ -2916,7 +2882,7 @@
       <c r="E43" s="13" t="inlineStr"/>
       <c r="F43" s="13" t="inlineStr"/>
       <c r="G43" s="14" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="H43" s="13" t="inlineStr">
         <is>
@@ -2925,12 +2891,12 @@
       </c>
       <c r="I43" s="15" t="n"/>
       <c r="J43" s="15" t="n">
-        <v>4052.5</v>
-      </c>
-      <c r="K43" s="19" t="n"/>
+        <v>2405.68</v>
+      </c>
+      <c r="K43" s="18" t="n"/>
       <c r="L43" s="15" t="n"/>
       <c r="M43" s="15" t="n">
-        <v>810500</v>
+        <v>120284</v>
       </c>
       <c r="N43" s="14" t="n"/>
       <c r="O43" s="14" t="n"/>
@@ -2938,107 +2904,179 @@
       <c r="Q43" s="13" t="inlineStr"/>
       <c r="R43" s="13" t="inlineStr">
         <is>
-          <t>[оценка]: правило клиента 3 500 + антистатическая ткань ~15%</t>
+          <t>медиана опт/прайс 2026: spets.ru 1 812; spets.ru 1 964; trakt.ru 2 034</t>
         </is>
       </c>
       <c r="S43" s="16" t="inlineStr">
         <is>
-          <t>fabrikant-textile.ru</t>
+          <t>spets.ru</t>
         </is>
       </c>
       <c r="T43" s="13" t="inlineStr">
         <is>
-          <t>spec-standart.ru</t>
+          <t>spets.ru, trakt.ru</t>
         </is>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="13" t="inlineStr"/>
-      <c r="B44" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Футболка х/б</t>
-        </is>
-      </c>
-      <c r="C44" s="13" t="inlineStr"/>
-      <c r="D44" s="13" t="inlineStr"/>
-      <c r="E44" s="13" t="inlineStr"/>
-      <c r="F44" s="13" t="inlineStr"/>
-      <c r="G44" s="14" t="n">
-        <v>200</v>
-      </c>
-      <c r="H44" s="13" t="inlineStr">
-        <is>
-          <t>шт/пар/компл</t>
-        </is>
-      </c>
-      <c r="I44" s="15" t="n"/>
-      <c r="J44" s="15" t="n">
-        <v>530.5</v>
-      </c>
-      <c r="K44" s="19" t="n"/>
-      <c r="L44" s="15" t="n"/>
-      <c r="M44" s="15" t="n">
-        <v>106100</v>
-      </c>
-      <c r="N44" s="14" t="n"/>
-      <c r="O44" s="14" t="n"/>
-      <c r="P44" s="14" t="n"/>
-      <c r="Q44" s="13" t="inlineStr"/>
-      <c r="R44" s="13" t="inlineStr">
-        <is>
-          <t>арт. 4.025 477.84 ₽</t>
-        </is>
-      </c>
-      <c r="S44" s="16" t="inlineStr">
-        <is>
-          <t>files.technoavia.ru</t>
-        </is>
-      </c>
-      <c r="T44" s="13" t="inlineStr"/>
+      <c r="A44" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Соль ⚠ &lt;9 000 ₽/т: МКУ УЖКХ, Струнино</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>0128600006826000407</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>открыть</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ запрос котировок</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>19.10</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="I44" s="9" t="n">
+        <v>8950</v>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>5800</v>
+      </c>
+      <c r="K44" s="10" t="n">
+        <v>0.3519553072625698</v>
+      </c>
+      <c r="L44" s="9" t="n">
+        <v>1342500</v>
+      </c>
+      <c r="M44" s="9" t="n">
+        <v>870000</v>
+      </c>
+      <c r="N44" s="17" t="n">
+        <v>0.3519553072625698</v>
+      </c>
+      <c r="O44" s="12" t="n">
+        <v>198384</v>
+      </c>
+      <c r="P44" s="10" t="n">
+        <v>0.3252517422613478</v>
+      </c>
+      <c r="Q44" s="8" t="inlineStr">
+        <is>
+          <t>1% / 5%</t>
+        </is>
+      </c>
+      <c r="R44" s="8" t="inlineStr">
+        <is>
+          <t>Струнино (~100 км от МКАД): МО с доставкой ≈5 400 + удлинение плеча ~400; Владимир/Ка…</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>perevalki.ru</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>tehsalt.ru, icemelt33.ru</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="13" t="inlineStr"/>
-      <c r="B45" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Ботинки кожаные с МП</t>
-        </is>
-      </c>
-      <c r="C45" s="13" t="inlineStr"/>
-      <c r="D45" s="13" t="inlineStr"/>
-      <c r="E45" s="13" t="inlineStr"/>
-      <c r="F45" s="13" t="inlineStr"/>
-      <c r="G45" s="14" t="n">
-        <v>50</v>
-      </c>
-      <c r="H45" s="13" t="inlineStr">
-        <is>
-          <t>шт/пар/компл</t>
-        </is>
-      </c>
-      <c r="I45" s="15" t="n"/>
-      <c r="J45" s="15" t="n">
-        <v>3070.5</v>
-      </c>
-      <c r="K45" s="19" t="n"/>
-      <c r="L45" s="15" t="n"/>
-      <c r="M45" s="15" t="n">
-        <v>153525</v>
-      </c>
-      <c r="N45" s="14" t="n"/>
-      <c r="O45" s="14" t="n"/>
-      <c r="P45" s="14" t="n"/>
-      <c r="Q45" s="13" t="inlineStr"/>
-      <c r="R45" s="13" t="inlineStr">
-        <is>
-          <t>арт. 5.856 «Билд» с мет. носками 3 018.36 ₽</t>
-        </is>
-      </c>
-      <c r="S45" s="16" t="inlineStr">
-        <is>
-          <t>files.technoavia.ru</t>
-        </is>
-      </c>
-      <c r="T45" s="13" t="inlineStr"/>
+      <c r="A45" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Трубы ППУ: МУП «Уфимские инженерные сети»</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>32616450774</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>открыть</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>223-ФЗ иной способ (не аукцион)</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>20.10 12:00</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="n">
+        <v>71094.33333333333</v>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>41495.44444444445</v>
+      </c>
+      <c r="K45" s="10" t="n">
+        <v>0.416332603473632</v>
+      </c>
+      <c r="L45" s="9" t="n">
+        <v>639849</v>
+      </c>
+      <c r="M45" s="9" t="n">
+        <v>373459</v>
+      </c>
+      <c r="N45" s="11" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="O45" s="12" t="n">
+        <v>189886</v>
+      </c>
+      <c r="P45" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q45" s="8" t="inlineStr">
+        <is>
+          <t>не указано</t>
+        </is>
+      </c>
+      <c r="R45" s="8" t="inlineStr">
+        <is>
+          <t>оценка по аналогам</t>
+        </is>
+      </c>
+      <c r="S45" s="8" t="inlineStr">
+        <is>
+          <t>нет открытой цены — оценка</t>
+        </is>
+      </c>
+      <c r="T45" s="4" t="n"/>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="4" t="n">
@@ -3075,12 +3113,18 @@
       <c r="J46" s="9" t="n"/>
       <c r="K46" s="10" t="n"/>
       <c r="L46" s="9" t="n"/>
-      <c r="M46" s="9" t="n"/>
-      <c r="N46" s="10" t="n"/>
+      <c r="M46" s="9" t="n">
+        <v>757377</v>
+      </c>
+      <c r="N46" s="17" t="n">
+        <v>0.25</v>
+      </c>
       <c r="O46" s="12" t="n">
-        <v>99875</v>
-      </c>
-      <c r="P46" s="10" t="n"/>
+        <v>126954</v>
+      </c>
+      <c r="P46" s="10" t="n">
+        <v>0.2190952275740167</v>
+      </c>
       <c r="Q46" s="8" t="inlineStr">
         <is>
           <t>—</t>
@@ -3115,12 +3159,12 @@
       </c>
       <c r="I47" s="15" t="n"/>
       <c r="J47" s="15" t="n">
-        <v>3552.5</v>
-      </c>
-      <c r="K47" s="19" t="n"/>
+        <v>3542</v>
+      </c>
+      <c r="K47" s="18" t="n"/>
       <c r="L47" s="15" t="n"/>
       <c r="M47" s="15" t="n">
-        <v>284200</v>
+        <v>283360</v>
       </c>
       <c r="N47" s="14" t="n"/>
       <c r="O47" s="14" t="n"/>
@@ -3128,7 +3172,7 @@
       <c r="Q47" s="13" t="inlineStr"/>
       <c r="R47" s="13" t="inlineStr">
         <is>
-          <t>правило клиента: летний комплект 3 500 ₽</t>
+          <t>ваша себестоимость; рынок 2026: fabrikant-textile.ru 495; fabrikant-textile.ru 850; t…</t>
         </is>
       </c>
       <c r="S47" s="16" t="inlineStr">
@@ -3138,7 +3182,7 @@
       </c>
       <c r="T47" s="13" t="inlineStr">
         <is>
-          <t>spec-standart.ru</t>
+          <t>fabrikant-textile.ru, files.technoavia.ru</t>
         </is>
       </c>
     </row>
@@ -3163,12 +3207,12 @@
       </c>
       <c r="I48" s="15" t="n"/>
       <c r="J48" s="15" t="n">
-        <v>5052.5</v>
-      </c>
-      <c r="K48" s="19" t="n"/>
+        <v>5091</v>
+      </c>
+      <c r="K48" s="18" t="n"/>
       <c r="L48" s="15" t="n"/>
       <c r="M48" s="15" t="n">
-        <v>202100</v>
+        <v>203640</v>
       </c>
       <c r="N48" s="14" t="n"/>
       <c r="O48" s="14" t="n"/>
@@ -3176,7 +3220,7 @@
       <c r="Q48" s="13" t="inlineStr"/>
       <c r="R48" s="13" t="inlineStr">
         <is>
-          <t>правило клиента: зимний комплект 5 000 ₽</t>
+          <t>ваша себестоимость; рынок 2026: fabrikant-textile.ru 1 845; techno-avia.ru 7 194; spe…</t>
         </is>
       </c>
       <c r="S48" s="16" t="inlineStr">
@@ -3186,7 +3230,7 @@
       </c>
       <c r="T48" s="13" t="inlineStr">
         <is>
-          <t>spec-standart.ru</t>
+          <t>files.technoavia.ru, specteks37.ru</t>
         </is>
       </c>
     </row>
@@ -3211,12 +3255,12 @@
       </c>
       <c r="I49" s="15" t="n"/>
       <c r="J49" s="15" t="n">
-        <v>3070.5</v>
-      </c>
-      <c r="K49" s="19" t="n"/>
+        <v>2437.68</v>
+      </c>
+      <c r="K49" s="18" t="n"/>
       <c r="L49" s="15" t="n"/>
       <c r="M49" s="15" t="n">
-        <v>245640</v>
+        <v>195014.4</v>
       </c>
       <c r="N49" s="14" t="n"/>
       <c r="O49" s="14" t="n"/>
@@ -3224,15 +3268,19 @@
       <c r="Q49" s="13" t="inlineStr"/>
       <c r="R49" s="13" t="inlineStr">
         <is>
-          <t>арт. 5.856 «Билд» с мет. носками 3 018.36 ₽</t>
+          <t>медиана опт/прайс 2026: spets.ru 1 812; spets.ru 1 964; trakt.ru 2 034</t>
         </is>
       </c>
       <c r="S49" s="16" t="inlineStr">
         <is>
-          <t>files.technoavia.ru</t>
-        </is>
-      </c>
-      <c r="T49" s="13" t="inlineStr"/>
+          <t>spets.ru</t>
+        </is>
+      </c>
+      <c r="T49" s="13" t="inlineStr">
+        <is>
+          <t>spets.ru, trakt.ru</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="13" t="inlineStr"/>
@@ -3255,12 +3303,12 @@
       </c>
       <c r="I50" s="15" t="n"/>
       <c r="J50" s="15" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="K50" s="19" t="n"/>
+        <v>30.86</v>
+      </c>
+      <c r="K50" s="18" t="n"/>
       <c r="L50" s="15" t="n"/>
       <c r="M50" s="15" t="n">
-        <v>132750</v>
+        <v>46290</v>
       </c>
       <c r="N50" s="14" t="n"/>
       <c r="O50" s="14" t="n"/>
@@ -3268,15 +3316,19 @@
       <c r="Q50" s="13" t="inlineStr"/>
       <c r="R50" s="13" t="inlineStr">
         <is>
-          <t>арт. 7.002 «Строй» 36 ₽</t>
+          <t>медиана опт/прайс 2026: trakt.ru 17; spets.ru 20; spets.ru 24</t>
         </is>
       </c>
       <c r="S50" s="16" t="inlineStr">
         <is>
-          <t>files.technoavia.ru</t>
-        </is>
-      </c>
-      <c r="T50" s="13" t="inlineStr"/>
+          <t>trakt.ru</t>
+        </is>
+      </c>
+      <c r="T50" s="13" t="inlineStr">
+        <is>
+          <t>spets.ru</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="13" t="inlineStr"/>
@@ -3299,12 +3351,12 @@
       </c>
       <c r="I51" s="15" t="n"/>
       <c r="J51" s="15" t="n">
-        <v>1144.5</v>
-      </c>
-      <c r="K51" s="19" t="n"/>
+        <v>969.1</v>
+      </c>
+      <c r="K51" s="18" t="n"/>
       <c r="L51" s="15" t="n"/>
       <c r="M51" s="15" t="n">
-        <v>34335</v>
+        <v>29073</v>
       </c>
       <c r="N51" s="14" t="n"/>
       <c r="O51" s="14" t="n"/>
@@ -3312,15 +3364,19 @@
       <c r="Q51" s="13" t="inlineStr"/>
       <c r="R51" s="13" t="inlineStr">
         <is>
-          <t>арт. 3.290 1 091.64 ₽</t>
+          <t>медиана опт/прайс 2026: fabrikant-textile.ru 400; techno-avia.ru 3 277; ivuniforma.ru…</t>
         </is>
       </c>
       <c r="S51" s="16" t="inlineStr">
         <is>
-          <t>files.technoavia.ru</t>
-        </is>
-      </c>
-      <c r="T51" s="13" t="inlineStr"/>
+          <t>fabrikant-textile.ru</t>
+        </is>
+      </c>
+      <c r="T51" s="13" t="inlineStr">
+        <is>
+          <t>files.technoavia.ru, ivuniforma.ru</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="4" t="n">
@@ -3360,16 +3416,16 @@
         <v>700000</v>
       </c>
       <c r="M52" s="9" t="n">
-        <v>561222</v>
+        <v>558596</v>
       </c>
       <c r="N52" s="17" t="n">
-        <v>0.17</v>
+        <v>0.2020060660588239</v>
       </c>
       <c r="O52" s="12" t="n">
-        <v>35517</v>
+        <v>40800</v>
       </c>
       <c r="P52" s="10" t="n">
-        <v>0.15</v>
+        <v>0.169123638157801</v>
       </c>
       <c r="Q52" s="8" t="inlineStr">
         <is>
@@ -3405,10 +3461,10 @@
         <v>20031.67</v>
       </c>
       <c r="J53" s="15" t="n">
-        <v>12969.86</v>
+        <v>17078.02</v>
       </c>
       <c r="K53" s="17" t="n">
-        <v>0.352532265158122</v>
+        <v>0.147449014485562</v>
       </c>
       <c r="L53" s="15" t="n"/>
       <c r="M53" s="15" t="n"/>
@@ -3416,13 +3472,21 @@
       <c r="O53" s="14" t="n"/>
       <c r="P53" s="14" t="n"/>
       <c r="Q53" s="13" t="inlineStr"/>
-      <c r="R53" s="13" t="inlineStr"/>
+      <c r="R53" s="13" t="inlineStr">
+        <is>
+          <t>медиана опт/прайс 2026: trakt.ru 12 917; spets.ru 16 836; trakt.ru 17 008</t>
+        </is>
+      </c>
       <c r="S53" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
         </is>
       </c>
-      <c r="T53" s="13" t="inlineStr"/>
+      <c r="T53" s="13" t="inlineStr">
+        <is>
+          <t>spets.ru, trakt.ru</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="13" t="inlineStr"/>
@@ -3445,10 +3509,10 @@
         <v>5235</v>
       </c>
       <c r="J54" s="15" t="n">
-        <v>2944.51</v>
+        <v>2906.01</v>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.4375339063992359</v>
+        <v>0.4448882521489971</v>
       </c>
       <c r="L54" s="15" t="n"/>
       <c r="M54" s="15" t="n"/>
@@ -3456,13 +3520,21 @@
       <c r="O54" s="14" t="n"/>
       <c r="P54" s="14" t="n"/>
       <c r="Q54" s="13" t="inlineStr"/>
-      <c r="R54" s="13" t="inlineStr"/>
+      <c r="R54" s="13" t="inlineStr">
+        <is>
+          <t>медиана опт/прайс 2026: spets.ru 1 525; trakt.ru 2 892; spets.ru 2 989</t>
+        </is>
+      </c>
       <c r="S54" s="16" t="inlineStr">
         <is>
-          <t>trakt.ru</t>
-        </is>
-      </c>
-      <c r="T54" s="13" t="inlineStr"/>
+          <t>spets.ru</t>
+        </is>
+      </c>
+      <c r="T54" s="13" t="inlineStr">
+        <is>
+          <t>trakt.ru, spets.ru</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="13" t="inlineStr"/>
@@ -3485,10 +3557,10 @@
         <v>5811.33</v>
       </c>
       <c r="J55" s="15" t="n">
-        <v>2477.86</v>
+        <v>2437.68</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>0.5736156783386935</v>
+        <v>0.5805297582481118</v>
       </c>
       <c r="L55" s="15" t="n"/>
       <c r="M55" s="15" t="n"/>
@@ -3496,13 +3568,21 @@
       <c r="O55" s="14" t="n"/>
       <c r="P55" s="14" t="n"/>
       <c r="Q55" s="13" t="inlineStr"/>
-      <c r="R55" s="13" t="inlineStr"/>
+      <c r="R55" s="13" t="inlineStr">
+        <is>
+          <t>медиана опт/прайс 2026: spets.ru 1 812; spets.ru 1 964; trakt.ru 2 034</t>
+        </is>
+      </c>
       <c r="S55" s="16" t="inlineStr">
         <is>
-          <t>trakt.ru</t>
-        </is>
-      </c>
-      <c r="T55" s="13" t="inlineStr"/>
+          <t>spets.ru</t>
+        </is>
+      </c>
+      <c r="T55" s="13" t="inlineStr">
+        <is>
+          <t>spets.ru, trakt.ru</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="13" t="inlineStr"/>
@@ -3525,10 +3605,10 @@
         <v>1346.33</v>
       </c>
       <c r="J56" s="15" t="n">
-        <v>1078.52</v>
+        <v>912.08</v>
       </c>
       <c r="K56" s="17" t="n">
-        <v>0.1989185415165672</v>
+        <v>0.3225435071639196</v>
       </c>
       <c r="L56" s="15" t="n"/>
       <c r="M56" s="15" t="n"/>
@@ -3536,13 +3616,21 @@
       <c r="O56" s="14" t="n"/>
       <c r="P56" s="14" t="n"/>
       <c r="Q56" s="13" t="inlineStr"/>
-      <c r="R56" s="13" t="inlineStr"/>
+      <c r="R56" s="13" t="inlineStr">
+        <is>
+          <t>медиана опт/прайс 2026: trakt.ru 411; spets.ru 470; techno-avia.ru 801</t>
+        </is>
+      </c>
       <c r="S56" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
         </is>
       </c>
-      <c r="T56" s="13" t="inlineStr"/>
+      <c r="T56" s="13" t="inlineStr">
+        <is>
+          <t>spets.ru, files.technoavia.ru</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="13" t="inlineStr"/>
@@ -3565,10 +3653,10 @@
         <v>1778</v>
       </c>
       <c r="J57" s="15" t="n">
-        <v>2047.81</v>
-      </c>
-      <c r="K57" s="18" t="n">
-        <v>-0.1517491563554556</v>
+        <v>346.93</v>
+      </c>
+      <c r="K57" s="11" t="n">
+        <v>0.8048762654668166</v>
       </c>
       <c r="L57" s="15" t="n"/>
       <c r="M57" s="15" t="n"/>
@@ -3576,13 +3664,21 @@
       <c r="O57" s="14" t="n"/>
       <c r="P57" s="14" t="n"/>
       <c r="Q57" s="13" t="inlineStr"/>
-      <c r="R57" s="13" t="inlineStr"/>
+      <c r="R57" s="13" t="inlineStr">
+        <is>
+          <t>медиана опт/прайс 2026: spets.ru 204; trakt.ru 259; techno-avia.ru 343</t>
+        </is>
+      </c>
       <c r="S57" s="16" t="inlineStr">
         <is>
-          <t>trakt.ru</t>
-        </is>
-      </c>
-      <c r="T57" s="13" t="inlineStr"/>
+          <t>spets.ru</t>
+        </is>
+      </c>
+      <c r="T57" s="13" t="inlineStr">
+        <is>
+          <t>trakt.ru, files.technoavia.ru</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="13" t="inlineStr"/>
@@ -3605,10 +3701,10 @@
         <v>1833.33</v>
       </c>
       <c r="J58" s="15" t="n">
-        <v>1028.5</v>
+        <v>306.8</v>
       </c>
       <c r="K58" s="11" t="n">
-        <v>0.4389989799981454</v>
+        <v>0.8326542411895295</v>
       </c>
       <c r="L58" s="15" t="n"/>
       <c r="M58" s="15" t="n"/>
@@ -3616,13 +3712,21 @@
       <c r="O58" s="14" t="n"/>
       <c r="P58" s="14" t="n"/>
       <c r="Q58" s="13" t="inlineStr"/>
-      <c r="R58" s="13" t="inlineStr"/>
+      <c r="R58" s="13" t="inlineStr">
+        <is>
+          <t>медиана опт/прайс 2026: trakt.ru 226; trakt.ru 293; spets.ru 293</t>
+        </is>
+      </c>
       <c r="S58" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
         </is>
       </c>
-      <c r="T58" s="13" t="inlineStr"/>
+      <c r="T58" s="13" t="inlineStr">
+        <is>
+          <t>trakt.ru, spets.ru</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="13" t="inlineStr"/>
@@ -3645,10 +3749,10 @@
         <v>3468.67</v>
       </c>
       <c r="J59" s="15" t="n">
-        <v>5030.1</v>
-      </c>
-      <c r="K59" s="18" t="n">
-        <v>-0.4501523638743381</v>
+        <v>335</v>
+      </c>
+      <c r="K59" s="11" t="n">
+        <v>0.9034211960203767</v>
       </c>
       <c r="L59" s="15" t="n"/>
       <c r="M59" s="15" t="n"/>
@@ -3656,13 +3760,21 @@
       <c r="O59" s="14" t="n"/>
       <c r="P59" s="14" t="n"/>
       <c r="Q59" s="13" t="inlineStr"/>
-      <c r="R59" s="13" t="inlineStr"/>
+      <c r="R59" s="13" t="inlineStr">
+        <is>
+          <t>медиана опт/прайс 2026: trakt.ru 305; spets.ru 305; techno-avia.ru 321</t>
+        </is>
+      </c>
       <c r="S59" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
         </is>
       </c>
-      <c r="T59" s="13" t="inlineStr"/>
+      <c r="T59" s="13" t="inlineStr">
+        <is>
+          <t>spets.ru, files.technoavia.ru</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="13" t="inlineStr"/>
@@ -3685,10 +3797,10 @@
         <v>33762.67</v>
       </c>
       <c r="J60" s="15" t="n">
-        <v>33207.83</v>
-      </c>
-      <c r="K60" s="17" t="n">
-        <v>0.01643353443314751</v>
+        <v>36312.16</v>
+      </c>
+      <c r="K60" s="19" t="n">
+        <v>-0.07551209664401558</v>
       </c>
       <c r="L60" s="15" t="n"/>
       <c r="M60" s="15" t="n"/>
@@ -3696,13 +3808,21 @@
       <c r="O60" s="14" t="n"/>
       <c r="P60" s="14" t="n"/>
       <c r="Q60" s="13" t="inlineStr"/>
-      <c r="R60" s="13" t="inlineStr"/>
+      <c r="R60" s="13" t="inlineStr">
+        <is>
+          <t>медиана опт/прайс 2026: trakt.ru 33 155; techno-avia.ru 36 207; spets.ru 53 070</t>
+        </is>
+      </c>
       <c r="S60" s="16" t="inlineStr">
         <is>
           <t>trakt.ru</t>
         </is>
       </c>
-      <c r="T60" s="13" t="inlineStr"/>
+      <c r="T60" s="13" t="inlineStr">
+        <is>
+          <t>files.technoavia.ru, spets.ru</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="13" t="inlineStr"/>
@@ -3725,10 +3845,10 @@
         <v>7592.75</v>
       </c>
       <c r="J61" s="15" t="n">
-        <v>4516.48</v>
+        <v>3890.91</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0.405158868657601</v>
+        <v>0.487549306904613</v>
       </c>
       <c r="L61" s="15" t="n"/>
       <c r="M61" s="15" t="n"/>
@@ -3736,13 +3856,21 @@
       <c r="O61" s="14" t="n"/>
       <c r="P61" s="14" t="n"/>
       <c r="Q61" s="13" t="inlineStr"/>
-      <c r="R61" s="13" t="inlineStr"/>
+      <c r="R61" s="13" t="inlineStr">
+        <is>
+          <t>медиана опт/прайс 2026: spets.ru 2 458; spets.ru 3 509; trakt.ru 3 787</t>
+        </is>
+      </c>
       <c r="S61" s="16" t="inlineStr">
         <is>
-          <t>trakt.ru</t>
-        </is>
-      </c>
-      <c r="T61" s="13" t="inlineStr"/>
+          <t>spets.ru</t>
+        </is>
+      </c>
+      <c r="T61" s="13" t="inlineStr">
+        <is>
+          <t>spets.ru, trakt.ru</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="4" t="n">
@@ -3877,7 +4005,7 @@
       <c r="J64" s="15" t="n">
         <v>5521.15</v>
       </c>
-      <c r="K64" s="18" t="n">
+      <c r="K64" s="19" t="n">
         <v>-0.01310337740883049</v>
       </c>
       <c r="L64" s="15" t="n"/>
@@ -4045,7 +4173,7 @@
       <c r="J68" s="15" t="n">
         <v>1480.51</v>
       </c>
-      <c r="K68" s="18" t="n">
+      <c r="K68" s="19" t="n">
         <v>-0.1650036983994587</v>
       </c>
       <c r="L68" s="15" t="n"/>
@@ -4249,7 +4377,7 @@
       <c r="J73" s="15" t="n">
         <v>12912.52</v>
       </c>
-      <c r="K73" s="18" t="n">
+      <c r="K73" s="19" t="n">
         <v>-0.08509665643687174</v>
       </c>
       <c r="L73" s="15" t="n"/>
@@ -4289,7 +4417,7 @@
       <c r="J74" s="15" t="n">
         <v>84.83</v>
       </c>
-      <c r="K74" s="18" t="n">
+      <c r="K74" s="19" t="n">
         <v>-0.5107747105966162</v>
       </c>
       <c r="L74" s="15" t="n"/>
@@ -4505,7 +4633,7 @@
       <c r="J79" s="15" t="n">
         <v>1753.18</v>
       </c>
-      <c r="K79" s="18" t="n">
+      <c r="K79" s="19" t="n">
         <v>-0.2528620635442424</v>
       </c>
       <c r="L79" s="15" t="n"/>
@@ -4717,7 +4845,7 @@
       <c r="J84" s="15" t="n">
         <v>856.48</v>
       </c>
-      <c r="K84" s="18" t="n">
+      <c r="K84" s="19" t="n">
         <v>-0.2165909090909091</v>
       </c>
       <c r="L84" s="15" t="n"/>
@@ -5377,7 +5505,7 @@
       <c r="J100" s="15" t="n">
         <v>4516.48</v>
       </c>
-      <c r="K100" s="18" t="n">
+      <c r="K100" s="19" t="n">
         <v>-0.1232985054952706</v>
       </c>
       <c r="L100" s="15" t="n"/>
@@ -5574,11 +5702,11 @@
         <v>22113376</v>
       </c>
       <c r="M105" s="21" t="n">
-        <v>9437915</v>
+        <v>11117555</v>
       </c>
       <c r="N105" s="22" t="n"/>
       <c r="O105" s="21" t="n">
-        <v>8097652</v>
+        <v>6739341</v>
       </c>
       <c r="P105" s="22" t="n"/>
       <c r="Q105" s="22" t="n"/>
@@ -5591,50 +5719,50 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S30" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S34" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S37" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S38" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S39" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S42" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S43" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S40" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S41" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S42" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S43" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S44" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S45" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S47" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S48" r:id="rId50"/>
